--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAD88FF-7E03-48FF-927D-556F4F8D1000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50187E9C-4070-4A6F-B910-0FB190C9C8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,117 +56,78 @@
     <t>1415 W Porter St, Philadelphia, PA 19145, United States</t>
   </si>
   <si>
-    <t>+1 215-389-4252</t>
-  </si>
-  <si>
     <t>Bistro La Baia BYOB</t>
   </si>
   <si>
     <t>1700 Lombard St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 267-687-1561</t>
-  </si>
-  <si>
     <t>Kei Sushi</t>
   </si>
   <si>
     <t>1711 South St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 215-309-2925</t>
-  </si>
-  <si>
     <t>Thai Square Restaurant</t>
   </si>
   <si>
     <t>2521 Christian St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 215-454-6683</t>
-  </si>
-  <si>
     <t>Kichi Omakase</t>
   </si>
   <si>
     <t>112 S 12th St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
-    <t>+1 215-359-6099</t>
-  </si>
-  <si>
     <t>La Sera Italiana BYOB</t>
   </si>
   <si>
     <t>1608 South St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 267-930-7805</t>
-  </si>
-  <si>
     <t>L'Anima</t>
   </si>
   <si>
     <t>1001 S 17th St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 215-595-2500</t>
-  </si>
-  <si>
     <t>Luna BYOB</t>
   </si>
   <si>
     <t>227 S 20th St, Philadelphia, PA 19103, United States</t>
   </si>
   <si>
-    <t>+1 215-693-2220</t>
-  </si>
-  <si>
     <t>Giorgio On Pine</t>
   </si>
   <si>
     <t>1328 Pine St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
-    <t>+1 215-545-6265</t>
-  </si>
-  <si>
     <t>Giorgio on Pine II</t>
   </si>
   <si>
     <t>1334 Pine St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
-    <t>+1 215-545-2482</t>
-  </si>
-  <si>
     <t>Trattoria Carina</t>
   </si>
   <si>
     <t>2201 Spruce St, Philadelphia, PA 19103, United States</t>
   </si>
   <si>
-    <t>+1 215-732-5818</t>
-  </si>
-  <si>
     <t>La Viola Bistro</t>
   </si>
   <si>
     <t>253 S 16th St, Philadelphia, PA 19102, United States</t>
   </si>
   <si>
-    <t>+1 215-735-8630</t>
-  </si>
-  <si>
     <t>Melograno</t>
   </si>
   <si>
     <t>2012 Sansom St, Philadelphia, PA 19103, United States</t>
   </si>
   <si>
-    <t>+1 215-875-8116</t>
-  </si>
-  <si>
     <t>ILLATA</t>
   </si>
   <si>
@@ -179,61 +140,256 @@
     <t>231 S 24th St, Philadelphia, PA 19103, United States</t>
   </si>
   <si>
-    <t>+1 215-703-2010</t>
-  </si>
-  <si>
     <t>Nori Sushi</t>
   </si>
   <si>
     <t>1636 South St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 215-735-6668</t>
-  </si>
-  <si>
     <t>Burrata</t>
   </si>
   <si>
     <t>1247 S 13th St, Philadelphia, PA 19147, United States</t>
   </si>
   <si>
-    <t>+1 215-465-2200</t>
-  </si>
-  <si>
     <t>Mercato</t>
   </si>
   <si>
     <t>1216 Spruce St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
-    <t>+1 215-985-2962</t>
-  </si>
-  <si>
     <t>Sawatdee</t>
   </si>
   <si>
     <t>534 S 15th St, Philadelphia, PA 19146, United States</t>
   </si>
   <si>
-    <t>+1 215-790-1299</t>
-  </si>
-  <si>
     <t>Kinme</t>
   </si>
   <si>
     <t>1117 Locust St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
-    <t>+1 215-982-1722</t>
-  </si>
-  <si>
     <t>Helm</t>
   </si>
   <si>
     <t>1303 N 5th St, Philadelphia, PA 19122, United States</t>
   </si>
   <si>
-    <t>+1 215-309-2211</t>
+    <t>Stina</t>
+  </si>
+  <si>
+    <t>1705 Snyder Ave, Philadelphia, PA 19145</t>
+  </si>
+  <si>
+    <t>(215) 337-3455</t>
+  </si>
+  <si>
+    <t>KINTO Cozy &amp; Authentic Georgian Restaurant</t>
+  </si>
+  <si>
+    <t>1144 Frankford Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t>(267) 857-9500</t>
+  </si>
+  <si>
+    <t>Nakama Japanese Cuisines &amp; Omakase</t>
+  </si>
+  <si>
+    <t>45 N 13th St, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t>(267) 876-7080</t>
+  </si>
+  <si>
+    <t>A Mano</t>
+  </si>
+  <si>
+    <t>2244 Fairmount Ave, Philadelphia, PA 19130</t>
+  </si>
+  <si>
+    <t>(215) 236-1114</t>
+  </si>
+  <si>
+    <t>El Chingon Philly</t>
+  </si>
+  <si>
+    <t>1524 S 10th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(267) 239-2131</t>
+  </si>
+  <si>
+    <t>Little Fish BYOB</t>
+  </si>
+  <si>
+    <t>746 S 6th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(267) 455-0172</t>
+  </si>
+  <si>
+    <t>Paffuto</t>
+  </si>
+  <si>
+    <t>1009 S 8th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 282-7262</t>
+  </si>
+  <si>
+    <t>Casa Nostra</t>
+  </si>
+  <si>
+    <t>775 S Front St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 975-0055</t>
+  </si>
+  <si>
+    <t>Scannicchio's</t>
+  </si>
+  <si>
+    <t>2500 S Broad St, Philadelphia, PA 19145</t>
+  </si>
+  <si>
+    <t>(215) 468-3900</t>
+  </si>
+  <si>
+    <t>Adoro Restaurant</t>
+  </si>
+  <si>
+    <t>769 E Passyunk Ave, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 627-1454</t>
+  </si>
+  <si>
+    <t>Mawn</t>
+  </si>
+  <si>
+    <t>764 S 9th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>Rice &amp; Sambal</t>
+  </si>
+  <si>
+    <t>1911 E Passyunk Ave, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>(215) 279-7052</t>
+  </si>
+  <si>
+    <t>Vic Sushi Bar</t>
+  </si>
+  <si>
+    <t>2035 Sansom St, Philadelphia, PA 19103</t>
+  </si>
+  <si>
+    <t>(215) 564-4339</t>
+  </si>
+  <si>
+    <t>CHAR</t>
+  </si>
+  <si>
+    <t>310 Master St, Philadelphia, PA 19122</t>
+  </si>
+  <si>
+    <t>(215) 964-9874</t>
+  </si>
+  <si>
+    <t>Elma</t>
+  </si>
+  <si>
+    <t>431 E Girard Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t>Pera Turkish Cuisine</t>
+  </si>
+  <si>
+    <t>944 N 2nd St, Philadelphia, PA 19123</t>
+  </si>
+  <si>
+    <t>(215) 660-9471</t>
+  </si>
+  <si>
+    <t>Hikari Sushi</t>
+  </si>
+  <si>
+    <t>1040 N American St #701, Philadelphia, PA 19123</t>
+  </si>
+  <si>
+    <t>(215) 923-2654</t>
+  </si>
+  <si>
+    <t>Vientiane Café</t>
+  </si>
+  <si>
+    <t>4728 Baltimore Ave, Philadelphia, PA 19143</t>
+  </si>
+  <si>
+    <t>(215) 726-1095</t>
+  </si>
+  <si>
+    <t>(215) 703-2010</t>
+  </si>
+  <si>
+    <t>(267) 687-1561</t>
+  </si>
+  <si>
+    <t>(215) 465-2200</t>
+  </si>
+  <si>
+    <t>(215) 545-6265</t>
+  </si>
+  <si>
+    <t>(215) 545-2482</t>
+  </si>
+  <si>
+    <t>(215) 309-2211</t>
+  </si>
+  <si>
+    <t>(215) 309-2925</t>
+  </si>
+  <si>
+    <t>(215) 359-6099</t>
+  </si>
+  <si>
+    <t>(215) 982-1722</t>
+  </si>
+  <si>
+    <t>(267) 930-7805</t>
+  </si>
+  <si>
+    <t>(215) 735-8630</t>
+  </si>
+  <si>
+    <t>(215) 389-4252</t>
+  </si>
+  <si>
+    <t>(215) 595-2500</t>
+  </si>
+  <si>
+    <t>(215) 693-2220</t>
+  </si>
+  <si>
+    <t>(215) 875-8116</t>
+  </si>
+  <si>
+    <t>(215) 985-2962</t>
+  </si>
+  <si>
+    <t>(215) 735-6668</t>
+  </si>
+  <si>
+    <t>(215) 790-1299</t>
+  </si>
+  <si>
+    <t>(215) 454-6683</t>
+  </si>
+  <si>
+    <t>(215) 732-5818</t>
   </si>
 </sst>
 </file>
@@ -628,10 +784,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="1"/>
@@ -650,233 +806,428 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
+    <sortCondition ref="A2:A40"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50187E9C-4070-4A6F-B910-0FB190C9C8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C38AEAD-B133-44D8-AD3A-6633B6CB509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -390,6 +390,16 @@
   </si>
   <si>
     <t>(215) 732-5818</t>
+  </si>
+  <si>
+    <t>Olea</t>
+  </si>
+  <si>
+    <t>232 Arch St, Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t>(267) 519-8315</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -784,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1224,6 +1234,17 @@
         <v>96</v>
       </c>
     </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
     <sortCondition ref="A2:A40"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C38AEAD-B133-44D8-AD3A-6633B6CB509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA160B36-93E0-41A9-B573-1B6142ED79A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -399,6 +399,16 @@
   </si>
   <si>
     <t>(267) 519-8315</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La Nonna</t>
+  </si>
+  <si>
+    <t>214 South St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(267) 928-3262</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -794,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1245,6 +1255,17 @@
         <v>119</v>
       </c>
     </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
     <sortCondition ref="A2:A40"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA160B36-93E0-41A9-B573-1B6142ED79A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4112CAA6-E206-404F-B4BF-4B31647BE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -409,6 +409,16 @@
   </si>
   <si>
     <t>(267) 928-3262</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tamalex Restaurant</t>
+  </si>
+  <si>
+    <t>1163 S 7th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 465-1665</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -804,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1018,257 +1028,268 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>18</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>122</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
-    <sortCondition ref="A2:A40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C43">
+    <sortCondition ref="A2:A43"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4112CAA6-E206-404F-B4BF-4B31647BE967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455A74A7-AE91-48D4-B12A-BFC9501C6963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -420,6 +420,15 @@
   <si>
     <t>(215) 465-1665</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Porcini</t>
+  </si>
+  <si>
+    <t>2048 Sansom St, Philadelphia, PA 19103</t>
+  </si>
+  <si>
+    <t>(215) 751-1175</t>
   </si>
 </sst>
 </file>
@@ -814,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1190,106 +1199,117 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C43">
-    <sortCondition ref="A2:A43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C44">
+    <sortCondition ref="A2:A44"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455A74A7-AE91-48D4-B12A-BFC9501C6963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73CFE49-74CF-403B-910C-A810362828DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73CFE49-74CF-403B-910C-A810362828DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4099E768-0EDC-45E5-B3C2-54FA0CFF337F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -429,6 +429,234 @@
   </si>
   <si>
     <t>(215) 751-1175</t>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Umai Umai</t>
+  </si>
+  <si>
+    <t>533 N 22nd St, Philadelphia, PA 19130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 988-0707 </t>
+  </si>
+  <si>
+    <t>La Trattoria</t>
+  </si>
+  <si>
+    <t>7131 Germantown Ave, Philadelphia, PA 19119</t>
+  </si>
+  <si>
+    <t>(267) 430-0007</t>
+  </si>
+  <si>
+    <t>Hardena</t>
+  </si>
+  <si>
+    <t>1754 S Hicks St #2217, Philadelphia, PA 19145</t>
+  </si>
+  <si>
+    <t>(215) 271-9442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heavy Metal Sausage</t>
+  </si>
+  <si>
+    <t>1527 W Porter St, Philadelphia, PA 19145</t>
+  </si>
+  <si>
+    <t>Tabachoy</t>
+  </si>
+  <si>
+    <t>932 S 10th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 315-8720</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pizza Richmond</t>
+  </si>
+  <si>
+    <t>3136 Richmond St, Philadelphia, PA 19134</t>
+  </si>
+  <si>
+    <t>(267) 804-7745</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tacconelli's Pizza</t>
+  </si>
+  <si>
+    <t>2604 E Somerset St, Philadelphia, PA 19134</t>
+  </si>
+  <si>
+    <t>(215) 425-4983</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winkel</t>
+  </si>
+  <si>
+    <t>1119 Locust St, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t>(267) 639-3453</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Golden Gates Restaurant</t>
+  </si>
+  <si>
+    <t>11058 Rennard St, Philadelphia, PA 19116</t>
+  </si>
+  <si>
+    <t>(215) 677-9337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kanella</t>
+  </si>
+  <si>
+    <t>1001 Spruce St, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t>(267) 928-2085</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aroma on 3rd</t>
+  </si>
+  <si>
+    <t>1245 S 3rd St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(267) 314-5315</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cucina Maria South Philly</t>
+  </si>
+  <si>
+    <t>768 S 8th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 408-0020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gnocchi Restaurant</t>
+  </si>
+  <si>
+    <t>613 E Passyunk Ave, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 592-8300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tonalli Philly</t>
+  </si>
+  <si>
+    <t>100 Morris St, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>(215) 608-8145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buca D'oro Ristorante</t>
+  </si>
+  <si>
+    <t>711 Locust St, Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t>Osteria Ama Philly</t>
+  </si>
+  <si>
+    <t>1905 Chestnut St, Philadelphia, PA 19103</t>
+  </si>
+  <si>
+    <t>Sakana Omakase Sushi</t>
+  </si>
+  <si>
+    <t>616 S 2nd St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>La Canasta Mexican Food</t>
+  </si>
+  <si>
+    <t>2341 S 4th St, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>Los Gallos</t>
+  </si>
+  <si>
+    <t>951 Wolf St, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>La Fontana Della Citta</t>
+  </si>
+  <si>
+    <t>1701 Spruce St, Philadelphia, PA 19103</t>
+  </si>
+  <si>
+    <t>Bricco Coal Fired Pizza</t>
+  </si>
+  <si>
+    <t>128 Haddon Ave, Haddon Township, NJ 08108</t>
+  </si>
+  <si>
+    <t>Figs</t>
+  </si>
+  <si>
+    <t>2501 Meredith St, Philadelphia, PA 19130</t>
+  </si>
+  <si>
+    <t>México Lindo Y Que Rico Restaurant</t>
+  </si>
+  <si>
+    <t>700 Moore St, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>Cilantro Mediterranean Cuisine</t>
+  </si>
+  <si>
+    <t>613 S 4th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 928-0556  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(484) 355-4133  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 922-2149  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 639-4060  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 551-1245  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 875-9990  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(856) 477-2233  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 978-8440  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 755-1005  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 761-9609  </t>
   </si>
 </sst>
 </file>
@@ -482,11 +710,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -823,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -832,7 +1063,7 @@
     <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,8 +1073,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
@@ -853,8 +1087,11 @@
       <c r="C2" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -864,8 +1101,11 @@
       <c r="C3" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -875,8 +1115,11 @@
       <c r="C4" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -886,8 +1129,11 @@
       <c r="C5" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -897,8 +1143,11 @@
       <c r="C6" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
@@ -908,8 +1157,11 @@
       <c r="C7" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
@@ -919,8 +1171,11 @@
       <c r="C8" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
@@ -930,16 +1185,22 @@
       <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -949,8 +1210,11 @@
       <c r="C11" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -960,8 +1224,11 @@
       <c r="C12" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
@@ -971,8 +1238,11 @@
       <c r="C13" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
@@ -982,16 +1252,22 @@
       <c r="C14" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,8 +1277,11 @@
       <c r="C16" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1012,8 +1291,11 @@
       <c r="C17" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -1023,8 +1305,11 @@
       <c r="C18" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -1034,8 +1319,11 @@
       <c r="C19" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>120</v>
       </c>
@@ -1045,271 +1333,679 @@
       <c r="C20" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" s="2">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>96</v>
+      <c r="D57" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D61" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D62" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="2">
+        <v>45977</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C44">
-    <sortCondition ref="A2:A44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C43">
+    <sortCondition ref="A2:A43"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4099E768-0EDC-45E5-B3C2-54FA0CFF337F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909C8657-236C-483F-804F-502AE19FD15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{888A9BF0-2D43-4E31-B177-D5314CD5866A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -657,6 +657,32 @@
   </si>
   <si>
     <t xml:space="preserve">(267) 761-9609  </t>
+  </si>
+  <si>
+    <t>Chateau Rouge</t>
+  </si>
+  <si>
+    <t>2108 South St, Philadelphia, PA 19146</t>
+  </si>
+  <si>
+    <t>Baby's Kusina + Market</t>
+  </si>
+  <si>
+    <t>2816 W Girard Ave, Philadelphia, PA 19130</t>
+  </si>
+  <si>
+    <t>Yuhiro Omakase Sushi</t>
+  </si>
+  <si>
+    <t>2146 E Susquehanna Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t>(445) 223-4110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(267) 876-7062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -710,7 +736,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -720,6 +746,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1054,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E0B387-5980-4442-AEA4-4B4F0537B43A}">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1658,13 +1685,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D44" s="2">
         <v>45977</v>
@@ -1672,13 +1699,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="D45" s="2">
         <v>45977</v>
@@ -1686,13 +1713,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="D46" s="2">
         <v>45977</v>
@@ -1700,10 +1727,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>140</v>
+        <v>190</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="D47" s="2">
         <v>45977</v>
@@ -1711,13 +1741,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="D48" s="2">
         <v>45977</v>
@@ -1725,13 +1755,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="D49" s="2">
         <v>45977</v>
@@ -1739,13 +1769,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D50" s="2">
         <v>45977</v>
@@ -1753,13 +1783,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D51" s="2">
         <v>45977</v>
@@ -1767,13 +1797,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D52" s="2">
         <v>45977</v>
@@ -1781,13 +1811,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D53" s="2">
         <v>45977</v>
@@ -1795,13 +1822,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D54" s="2">
         <v>45977</v>
@@ -1809,13 +1836,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D55" s="2">
         <v>45977</v>
@@ -1823,13 +1850,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="D56" s="2">
         <v>45977</v>
@@ -1851,13 +1878,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D58" s="2">
         <v>45977</v>
@@ -1865,13 +1892,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D59" s="2">
         <v>45977</v>
@@ -1879,13 +1906,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D60" s="2">
         <v>45977</v>
@@ -1893,13 +1920,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D61" s="2">
         <v>45977</v>
@@ -1907,13 +1934,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="D62" s="2">
         <v>45977</v>
@@ -1921,13 +1948,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D63" s="2">
         <v>45977</v>
@@ -1935,77 +1962,143 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="D64" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="D65" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="D66" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="D67" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="D68" s="2">
         <v>45977</v>
       </c>
     </row>
+    <row r="69" spans="1:13" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D69" s="2">
+        <v>45978</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:13" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D70" s="2">
+        <v>45978</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:13" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="2">
+        <v>45978</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C43">
-    <sortCondition ref="A2:A43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A44:D68">
+    <sortCondition ref="A44:A68"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1B80F8-6A21-46DF-BBE0-39537DFF8D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E036343-B496-4D28-A0DA-03B4723932D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="585">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -1650,6 +1650,147 @@
   </si>
   <si>
     <t>Breakfast &amp; Brunch, Comfort Food</t>
+  </si>
+  <si>
+    <t>The Choice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>845 W Lancaster Ave Bryn Mawr, PA 19010</t>
+  </si>
+  <si>
+    <t>(484) 383-3230</t>
+  </si>
+  <si>
+    <t>https://thechoice-restaurant.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/the-choice-bryn-mawr</t>
+  </si>
+  <si>
+    <t>Modern European</t>
+  </si>
+  <si>
+    <t>Amma's South Indian Cuisine</t>
+  </si>
+  <si>
+    <t>Indian</t>
+  </si>
+  <si>
+    <t>https://ammasrestaurants.com/university-city/</t>
+  </si>
+  <si>
+    <t>103 S 39th St UNIT 3, PA 19104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(808) 762 6627</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/amma-s-south-indian-cuisine-philadelphia</t>
+  </si>
+  <si>
+    <t>info@ammasusa.com</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terakawa Ramen</t>
+  </si>
+  <si>
+    <t>204 North 9th street, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t>125 South 40th Street, Philadelphia, PA 19104</t>
+  </si>
+  <si>
+    <t>(267) 687-1355</t>
+  </si>
+  <si>
+    <t>(215) 516-6818</t>
+  </si>
+  <si>
+    <t>https://terakawaramen.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/terakawa-ramen-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/terakawa-ramen-philadelphia-2</t>
+  </si>
+  <si>
+    <t>Chu Shang Spicy</t>
+  </si>
+  <si>
+    <t>925 Arch St, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t>(215) 928-9999</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/chu-shang-spicy-%E5%8E%A8%E5%B0%9A%E9%BA%BB%E8%BE%A3-philadelphia</t>
+  </si>
+  <si>
+    <t>Tiffin Indian Cuisine Fairmount</t>
+  </si>
+  <si>
+    <t>1921 Fairmount Ave, Philadelphia, PA 19130</t>
+  </si>
+  <si>
+    <t>(215) 337-3381</t>
+  </si>
+  <si>
+    <t>https://www.tiffin.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/tiffin-fairmount-philadelphia</t>
+  </si>
+  <si>
+    <t>Desserts, Vegan, Indian</t>
+  </si>
+  <si>
+    <t>catering@tiffin.com</t>
+  </si>
+  <si>
+    <t>Elwood </t>
+  </si>
+  <si>
+    <t>1007 Frankford Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t>(215) 279-7427</t>
+  </si>
+  <si>
+    <t>https://www.elwoodrestaurant.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/elwood-philadelphia-2</t>
+  </si>
+  <si>
+    <t>New American, Tea Rooms</t>
+  </si>
+  <si>
+    <t>info@elwoodrestaurant.com</t>
+  </si>
+  <si>
+    <t>Radicchio Cafe</t>
+  </si>
+  <si>
+    <t>info@radicchiocafe.com</t>
+  </si>
+  <si>
+    <t>402 Wood St Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t>(215) 627-6850</t>
+  </si>
+  <si>
+    <t>https://www.radicchiocafe.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/radicchio-cafe-philadelphia</t>
+  </si>
+  <si>
+    <t>Italian, Cafes</t>
   </si>
 </sst>
 </file>
@@ -1714,32 +1855,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2037,7 +2164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T86"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -5624,6 +5751,247 @@
         <v>377</v>
       </c>
     </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>539</v>
+      </c>
+      <c r="C87" t="s">
+        <v>540</v>
+      </c>
+      <c r="D87" t="s">
+        <v>541</v>
+      </c>
+      <c r="E87" t="s">
+        <v>542</v>
+      </c>
+      <c r="F87" t="s">
+        <v>543</v>
+      </c>
+      <c r="G87" t="s">
+        <v>544</v>
+      </c>
+      <c r="I87" t="s">
+        <v>468</v>
+      </c>
+      <c r="N87" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>545</v>
+      </c>
+      <c r="C88" t="s">
+        <v>548</v>
+      </c>
+      <c r="D88" t="s">
+        <v>549</v>
+      </c>
+      <c r="E88" t="s">
+        <v>547</v>
+      </c>
+      <c r="F88" t="s">
+        <v>550</v>
+      </c>
+      <c r="G88" t="s">
+        <v>546</v>
+      </c>
+      <c r="I88" t="s">
+        <v>468</v>
+      </c>
+      <c r="N88" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>45997</v>
+      </c>
+      <c r="R88" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>552</v>
+      </c>
+      <c r="C89" t="s">
+        <v>553</v>
+      </c>
+      <c r="D89" t="s">
+        <v>555</v>
+      </c>
+      <c r="E89" t="s">
+        <v>557</v>
+      </c>
+      <c r="F89" t="s">
+        <v>558</v>
+      </c>
+      <c r="G89" t="s">
+        <v>479</v>
+      </c>
+      <c r="I89" t="s">
+        <v>468</v>
+      </c>
+      <c r="N89" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>552</v>
+      </c>
+      <c r="C90" t="s">
+        <v>554</v>
+      </c>
+      <c r="D90" t="s">
+        <v>556</v>
+      </c>
+      <c r="E90" t="s">
+        <v>557</v>
+      </c>
+      <c r="F90" t="s">
+        <v>559</v>
+      </c>
+      <c r="G90" t="s">
+        <v>479</v>
+      </c>
+      <c r="I90" t="s">
+        <v>468</v>
+      </c>
+      <c r="N90" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>560</v>
+      </c>
+      <c r="C91" t="s">
+        <v>561</v>
+      </c>
+      <c r="D91" t="s">
+        <v>562</v>
+      </c>
+      <c r="F91" t="s">
+        <v>563</v>
+      </c>
+      <c r="G91" t="s">
+        <v>501</v>
+      </c>
+      <c r="I91" t="s">
+        <v>468</v>
+      </c>
+      <c r="N91" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>564</v>
+      </c>
+      <c r="C92" t="s">
+        <v>565</v>
+      </c>
+      <c r="D92" t="s">
+        <v>566</v>
+      </c>
+      <c r="E92" t="s">
+        <v>567</v>
+      </c>
+      <c r="F92" t="s">
+        <v>568</v>
+      </c>
+      <c r="G92" t="s">
+        <v>569</v>
+      </c>
+      <c r="I92" t="s">
+        <v>468</v>
+      </c>
+      <c r="N92" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>45997</v>
+      </c>
+      <c r="R92" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>571</v>
+      </c>
+      <c r="C93" t="s">
+        <v>572</v>
+      </c>
+      <c r="D93" t="s">
+        <v>573</v>
+      </c>
+      <c r="E93" t="s">
+        <v>574</v>
+      </c>
+      <c r="F93" t="s">
+        <v>575</v>
+      </c>
+      <c r="G93" t="s">
+        <v>576</v>
+      </c>
+      <c r="I93" t="s">
+        <v>468</v>
+      </c>
+      <c r="N93" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>45997</v>
+      </c>
+      <c r="R93" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>578</v>
+      </c>
+      <c r="C94" t="s">
+        <v>580</v>
+      </c>
+      <c r="D94" t="s">
+        <v>581</v>
+      </c>
+      <c r="E94" t="s">
+        <v>582</v>
+      </c>
+      <c r="F94" t="s">
+        <v>583</v>
+      </c>
+      <c r="G94" t="s">
+        <v>584</v>
+      </c>
+      <c r="I94" t="s">
+        <v>468</v>
+      </c>
+      <c r="N94" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>45997</v>
+      </c>
+      <c r="R94" t="s">
+        <v>579</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T86">
     <sortCondition ref="A2:A86"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E036343-B496-4D28-A0DA-03B4723932D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BB5322-6432-4257-9EC9-AC71D11A9850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="592">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -53,6 +40,30 @@
     <t>Yelp_URL</t>
   </si>
   <si>
+    <t>philly_restaurant_type</t>
+  </si>
+  <si>
+    <t>philly_restaurant_type_other_note</t>
+  </si>
+  <si>
+    <t>philly_corkage_fee</t>
+  </si>
+  <si>
+    <t>corkage_fee_amount</t>
+  </si>
+  <si>
+    <t>other_corkage_policy</t>
+  </si>
+  <si>
+    <t>wine_service_equipment</t>
+  </si>
+  <si>
+    <t>philly_equipment_other_note</t>
+  </si>
+  <si>
+    <t>byob_service_level</t>
+  </si>
+  <si>
     <t>Latitude</t>
   </si>
   <si>
@@ -71,6 +82,414 @@
     <t>Email_3</t>
   </si>
   <si>
+    <t>Email_4</t>
+  </si>
+  <si>
+    <t>Email_5</t>
+  </si>
+  <si>
+    <t>Email_6</t>
+  </si>
+  <si>
+    <t>Email_7</t>
+  </si>
+  <si>
+    <t>Email_8</t>
+  </si>
+  <si>
+    <t>Email_9</t>
+  </si>
+  <si>
+    <t>Email_10</t>
+  </si>
+  <si>
+    <t>Burrata</t>
+  </si>
+  <si>
+    <t>1247 S 13th St, Philadelphia, PA 19147, United States</t>
+  </si>
+  <si>
+    <t>(215) 465-2200</t>
+  </si>
+  <si>
+    <t>http://www.burrataphilly.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/burrata-philadelphia</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>wine glasses, opener/corkscrew, Ice bucket</t>
+  </si>
+  <si>
+    <t>self_service</t>
+  </si>
+  <si>
+    <t>contact@sansoxygen.com</t>
+  </si>
+  <si>
+    <t>burrataphilly@gmail.com</t>
+  </si>
+  <si>
+    <t>White yak</t>
+  </si>
+  <si>
+    <t> 6118 Ridge Ave, Philadelphia, PA 19128 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 483-0764  </t>
+  </si>
+  <si>
+    <t>https://whiteyakrestaurant.com/?utm_source=google</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/white-yak-philadelphia</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Tibetan</t>
+  </si>
+  <si>
+    <t>: -- 請選擇 --</t>
+  </si>
+  <si>
+    <t>La Nonna</t>
+  </si>
+  <si>
+    <t>214 South St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(267) 928-3262</t>
+  </si>
+  <si>
+    <t>http://ristorantelanonna.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/la-nonna-philadelphia</t>
+  </si>
+  <si>
+    <t>basic_service</t>
+  </si>
+  <si>
+    <t>Vientiane Bistro</t>
+  </si>
+  <si>
+    <t>2537 Kensington Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 703-8199  </t>
+  </si>
+  <si>
+    <t>https://www.vientianebistro.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/vientiane-bistro-philadelphia</t>
+  </si>
+  <si>
+    <t>Thai, other</t>
+  </si>
+  <si>
+    <t>Laotian</t>
+  </si>
+  <si>
+    <t>wine glasses</t>
+  </si>
+  <si>
+    <t>astigma@astigmatic.com</t>
+  </si>
+  <si>
+    <t>Yamitsuki</t>
+  </si>
+  <si>
+    <t>1028 Arch St , Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 629-3888  </t>
+  </si>
+  <si>
+    <t>https://yamitsuki1028.wixsite.com/yamitsukiramen</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/yamitsuki-ramen-philadelphia</t>
+  </si>
+  <si>
+    <t>Asian, other</t>
+  </si>
+  <si>
+    <t>Ramen</t>
+  </si>
+  <si>
+    <t>Idk</t>
+  </si>
+  <si>
+    <t>Idk I just walked in here with beers</t>
+  </si>
+  <si>
+    <t>no_service</t>
+  </si>
+  <si>
+    <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
+  </si>
+  <si>
+    <t>yamitsuki1028@gmail.com</t>
+  </si>
+  <si>
+    <t>Sakartvelo</t>
+  </si>
+  <si>
+    <t>705 Chestnut St, Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 319-1631  </t>
+  </si>
+  <si>
+    <t>https://sakartvelopa.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/sakartvelo-philadelphia</t>
+  </si>
+  <si>
+    <t>Georgian</t>
+  </si>
+  <si>
+    <t>test@email.com</t>
+  </si>
+  <si>
+    <t>Apricot Stone</t>
+  </si>
+  <si>
+    <t>428 W Girard Ave, Philadelphia, PA 19123 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 606-6596  </t>
+  </si>
+  <si>
+    <t>http://www.apricotstonephilly.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/apricot-stone-philadelphia-4</t>
+  </si>
+  <si>
+    <t>Mediterranean, other</t>
+  </si>
+  <si>
+    <t>Armenian/Syrian</t>
+  </si>
+  <si>
+    <t>info@apricotstonephilly.com</t>
+  </si>
+  <si>
+    <t>Chabba Thai bistro</t>
+  </si>
+  <si>
+    <t>4343 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 483-1979  </t>
+  </si>
+  <si>
+    <t>https://chabaathai.com/</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
+    <t>corkage_fee</t>
+  </si>
+  <si>
+    <t>wine glasses, opener/corkscrew</t>
+  </si>
+  <si>
+    <t>Yanako restaurant</t>
+  </si>
+  <si>
+    <t>4345 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 297-8151  </t>
+  </si>
+  <si>
+    <t>https://theyanako.com/</t>
+  </si>
+  <si>
+    <t>Japanese, other</t>
+  </si>
+  <si>
+    <t>Sushi Bars</t>
+  </si>
+  <si>
+    <t>Fiorino</t>
+  </si>
+  <si>
+    <t>3572 Indian Queen Ln, Philadelphia, PA 19129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 843-1500  </t>
+  </si>
+  <si>
+    <t>https://www.fiorino.us/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/fiorino-philadelphia-2</t>
+  </si>
+  <si>
+    <t>Santucci's Original Square Pizza</t>
+  </si>
+  <si>
+    <t>901 S 10th St Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t>(215) 825-5304</t>
+  </si>
+  <si>
+    <t>https://santuccispizza.com/santuccis-roxborough/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/santuccis-original-square-pizza-philadelphia-2</t>
+  </si>
+  <si>
+    <t>Italian, other</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Han dynasty (manayunk)</t>
+  </si>
+  <si>
+    <t>4356 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 508-2066  </t>
+  </si>
+  <si>
+    <t>http://www.handynasty.net/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/the-towpath-philadelphia</t>
+  </si>
+  <si>
+    <t>Asian</t>
+  </si>
+  <si>
+    <t>Casablanca Mediterranean Grill</t>
+  </si>
+  <si>
+    <t>947 Federal St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 324-5165  </t>
+  </si>
+  <si>
+    <t>http://www.casablanca-grill.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/casablanca-mediterranean-grill-philadelphia</t>
+  </si>
+  <si>
+    <t>Mediterranean</t>
+  </si>
+  <si>
+    <t>wine glasses, shot glasses, opener/corkscrew, Ice bucket</t>
+  </si>
+  <si>
+    <t>casablancamg947@gmail.com</t>
+  </si>
+  <si>
+    <t>Alyan’s Middle Eastern &amp; Mediterranean Restaurant</t>
+  </si>
+  <si>
+    <t>603 S 4th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 922-3553  </t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Zeppoli</t>
+  </si>
+  <si>
+    <t>618 Collings Ave, Collingswood NJ 08107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(856) 854-2670  </t>
+  </si>
+  <si>
+    <t>http://www.zeppolirestaurant.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/zeppoli-collingswood</t>
+  </si>
+  <si>
+    <t>Italian, Mediterranean</t>
+  </si>
+  <si>
+    <t>June BYOB</t>
+  </si>
+  <si>
+    <t> 690 Haddon Ave, Collingswood, NJ 08108 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(856) 240-7041  </t>
+  </si>
+  <si>
+    <t>http://www.junebyob.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/june-byob-collingswood</t>
+  </si>
+  <si>
+    <t>French, Fine dining</t>
+  </si>
+  <si>
+    <t>info@junebyob.com</t>
+  </si>
+  <si>
+    <t>Scampi</t>
+  </si>
+  <si>
+    <t> 617 S 3rd St, Philadelphia, PA 19147 </t>
+  </si>
+  <si>
+    <t>https://www.scampiphilly.com/menu</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/scampi-philadelphia</t>
+  </si>
+  <si>
+    <t>wine glasses, opener/corkscrew, wine storage locker service</t>
+  </si>
+  <si>
+    <t>full_service</t>
+  </si>
+  <si>
+    <t>Kung Fu Hot Pot</t>
+  </si>
+  <si>
+    <t>1008 Cherry St 3rd floor, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 606-1899  </t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/kungfu-hotpot-philadelphia</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>I think you just need to bring a bottle opener</t>
+  </si>
+  <si>
     <t>A Mano</t>
   </si>
   <si>
@@ -104,6 +523,9 @@
     <t>https://www.yelp.com/biz/adoro-restaurant-philadelphia</t>
   </si>
   <si>
+    <t>Sandwiches</t>
+  </si>
+  <si>
     <t>Ambrosia Ristorante</t>
   </si>
   <si>
@@ -119,6 +541,9 @@
     <t>https://www.yelp.com/biz/ambrosia-ristorante-byob-philadelphia</t>
   </si>
   <si>
+    <t>Breakfast &amp; Brunch</t>
+  </si>
+  <si>
     <t>Bistro La Baia BYOB</t>
   </si>
   <si>
@@ -131,30 +556,12 @@
     <t>http://www.bistrolabaia.com/</t>
   </si>
   <si>
+    <t>Italian, Mediterranean, Seafood</t>
+  </si>
+  <si>
     <t>1700bistrolabaia@gmail.com</t>
   </si>
   <si>
-    <t>Burrata</t>
-  </si>
-  <si>
-    <t>1247 S 13th St, Philadelphia, PA 19147, United States</t>
-  </si>
-  <si>
-    <t>(215) 465-2200</t>
-  </si>
-  <si>
-    <t>http://www.burrataphilly.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/burrata-philadelphia</t>
-  </si>
-  <si>
-    <t>contact@sansoxygen.com</t>
-  </si>
-  <si>
-    <t>burrataphilly@gmail.com</t>
-  </si>
-  <si>
     <t>Casa Nostra</t>
   </si>
   <si>
@@ -170,6 +577,12 @@
     <t>https://www.yelp.com/biz/casa-nostra-philadelphia</t>
   </si>
   <si>
+    <t>Italian, Seafood, other</t>
+  </si>
+  <si>
+    <t>Pasta Shops</t>
+  </si>
+  <si>
     <t>casanostraphilly@gmail.com</t>
   </si>
   <si>
@@ -188,6 +601,9 @@
     <t>https://www.yelp.com/biz/char-philadelphia</t>
   </si>
   <si>
+    <t>Pizza, Desserts</t>
+  </si>
+  <si>
     <t>hospitality@char.pizza</t>
   </si>
   <si>
@@ -206,6 +622,12 @@
     <t>https://www.elchingonphilly.com/</t>
   </si>
   <si>
+    <t>Mexican, other</t>
+  </si>
+  <si>
+    <t>Sandwiches, Tacos</t>
+  </si>
+  <si>
     <t>info@elchingonphilly.com</t>
   </si>
   <si>
@@ -266,6 +688,9 @@
     <t>https://www.yelp.com/biz/helm-philadelphia</t>
   </si>
   <si>
+    <t>New American</t>
+  </si>
+  <si>
     <t>Hikari Sushi</t>
   </si>
   <si>
@@ -296,6 +721,9 @@
     <t>https://www.yelp.com/biz/illata-philadelphia</t>
   </si>
   <si>
+    <t>Italian, American, Seafood</t>
+  </si>
+  <si>
     <t>info@illataphl.com</t>
   </si>
   <si>
@@ -314,6 +742,9 @@
     <t>https://www.yelp.com/biz/kei-sushi-restaurant-philadelphia</t>
   </si>
   <si>
+    <t>Seafood, Japanese, other</t>
+  </si>
+  <si>
     <t>Kichi Omakase</t>
   </si>
   <si>
@@ -353,21 +784,6 @@
     <t>https://kintophilly.com/</t>
   </si>
   <si>
-    <t>La Nonna</t>
-  </si>
-  <si>
-    <t>214 South St, Philadelphia, PA 19147</t>
-  </si>
-  <si>
-    <t>(267) 928-3262</t>
-  </si>
-  <si>
-    <t>http://ristorantelanonna.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/la-nonna-philadelphia</t>
-  </si>
-  <si>
     <t>La Viola Bistro</t>
   </si>
   <si>
@@ -422,6 +838,9 @@
     <t>https://www.littlefishbyob.com/</t>
   </si>
   <si>
+    <t>Seafood</t>
+  </si>
+  <si>
     <t>hello@littlefishbyob.com</t>
   </si>
   <si>
@@ -458,6 +877,9 @@
     <t>https://www.yelp.com/biz/mawn-philadelphia</t>
   </si>
   <si>
+    <t>Cambodian</t>
+  </si>
+  <si>
     <t>Melograno</t>
   </si>
   <si>
@@ -512,6 +934,9 @@
     <t>https://www.yelp.com/biz/nakama-japanese-cuisines-and-omakase-philadelphia</t>
   </si>
   <si>
+    <t>Ramen, Sushi Bars</t>
+  </si>
+  <si>
     <t>Nori Sushi</t>
   </si>
   <si>
@@ -542,6 +967,9 @@
     <t>https://www.yelp.com/biz/olea-philadelphia</t>
   </si>
   <si>
+    <t>Tapas/Small Plates</t>
+  </si>
+  <si>
     <t>luis.oleaphilly@gmail.com</t>
   </si>
   <si>
@@ -560,6 +988,9 @@
     <t>https://www.yelp.com/biz/paffuto-philadelphia</t>
   </si>
   <si>
+    <t>Pop-Up Restaurants</t>
+  </si>
+  <si>
     <t>paffutophl@gmail.com</t>
   </si>
   <si>
@@ -578,6 +1009,12 @@
     <t>https://www.yelp.com/biz/pera-turkish-cuisine-philadelphia</t>
   </si>
   <si>
+    <t>Mediterranean, Seafood, other</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
     <t>peraphiladelphia@gmail.com</t>
   </si>
   <si>
@@ -608,6 +1045,9 @@
     <t>https://www.yelp.com/biz/rice-and-sambal-philadelphia</t>
   </si>
   <si>
+    <t>Supper Clubs</t>
+  </si>
+  <si>
     <t>Scannicchio's</t>
   </si>
   <si>
@@ -638,6 +1078,9 @@
     <t>https://www.yelp.com/biz/stina-philadelphia-3</t>
   </si>
   <si>
+    <t>Greek</t>
+  </si>
+  <si>
     <t>stinapizzeria@gmail.com</t>
   </si>
   <si>
@@ -656,6 +1099,9 @@
     <t>https://www.yelp.com/biz/tamalex-restaurant-bar-and-griil-philadelphia</t>
   </si>
   <si>
+    <t>New Mexican Cuisine</t>
+  </si>
+  <si>
     <t>Thai Square Restaurant</t>
   </si>
   <si>
@@ -773,6 +1219,9 @@
     <t>https://www.yelp.com/biz/cucina-maria-philadelphia</t>
   </si>
   <si>
+    <t>Italian, Seafood</t>
+  </si>
+  <si>
     <t>Figs</t>
   </si>
   <si>
@@ -788,6 +1237,9 @@
     <t>https://www.yelp.com/biz/figs-philadelphia</t>
   </si>
   <si>
+    <t>Moroccan</t>
+  </si>
+  <si>
     <t>Gnocchi Restaurant</t>
   </si>
   <si>
@@ -824,6 +1276,9 @@
     <t>https://www.yelp.com/biz/golden-gates-philadelphia</t>
   </si>
   <si>
+    <t>Russian, Dance Clubs</t>
+  </si>
+  <si>
     <t>Hardena</t>
   </si>
   <si>
@@ -836,6 +1291,9 @@
     <t>https://www.yelp.com/biz/hardena-waroeng-surabaya-restaurant-philadelphia</t>
   </si>
   <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
     <t>Heavy Metal Sausage</t>
   </si>
   <si>
@@ -860,6 +1318,9 @@
     <t>https://www.yelp.com/biz/kanella-philadelphia-4</t>
   </si>
   <si>
+    <t>Middle Eastern</t>
+  </si>
+  <si>
     <t>info@kanellarestaurant.com</t>
   </si>
   <si>
@@ -881,6 +1342,9 @@
     <t>https://www.yelp.com/biz/la-canasta-mexican-food-philadelphia-3</t>
   </si>
   <si>
+    <t>Mexican</t>
+  </si>
+  <si>
     <t>La Fontana Della Citta</t>
   </si>
   <si>
@@ -911,6 +1375,9 @@
     <t>https://www.yelp.com/biz/la-sera-italiana-philadelphia</t>
   </si>
   <si>
+    <t>Salad, Burgers</t>
+  </si>
+  <si>
     <t>La Trattoria</t>
   </si>
   <si>
@@ -1034,6 +1501,9 @@
     <t>https://www.yelp.com/biz/tabachoy-philadelphia</t>
   </si>
   <si>
+    <t>Filipino</t>
+  </si>
+  <si>
     <t>chance@tabachoyphilly.com</t>
   </si>
   <si>
@@ -1070,6 +1540,9 @@
     <t>https://www.yelp.com/biz/tonalli-philadelphia</t>
   </si>
   <si>
+    <t>Pizza, Tacos</t>
+  </si>
+  <si>
     <t>Umai Umai</t>
   </si>
   <si>
@@ -1100,6 +1573,9 @@
     <t>https://www.yelp.com/biz/winkel-philadelphia-4</t>
   </si>
   <si>
+    <t>Breakfast &amp; Brunch, Coffee &amp; Tea, Sandwiches</t>
+  </si>
+  <si>
     <t>Chateau Rouge</t>
   </si>
   <si>
@@ -1115,6 +1591,15 @@
     <t>https://www.yelp.com/biz/chateau-rouge-philadelphia</t>
   </si>
   <si>
+    <t>French, other</t>
+  </si>
+  <si>
+    <t>African</t>
+  </si>
+  <si>
+    <t>$10 per table</t>
+  </si>
+  <si>
     <t>hello@chateaurougephilly.com</t>
   </si>
   <si>
@@ -1148,6 +1633,9 @@
     <t>https://www.yelp.com/biz/yuhiro-omakase-sushi-and-handroll-bar-philadelphia</t>
   </si>
   <si>
+    <t>Sushi Bars, Wine Bars</t>
+  </si>
+  <si>
     <t>yuhirosushi@gmail.com</t>
   </si>
   <si>
@@ -1166,494 +1654,13 @@
     <t>https://www.yelp.com/biz/mabu-kitchen-philadelphia</t>
   </si>
   <si>
+    <t>Breakfast &amp; Brunch, Comfort Food</t>
+  </si>
+  <si>
     <t>mabukitchenmanager@outlook.com</t>
   </si>
   <si>
-    <t>Santucci's Original Square Pizza</t>
-  </si>
-  <si>
-    <t>901 S 10th St Philadelphia, PA 19147</t>
-  </si>
-  <si>
-    <t>(215) 825-5304</t>
-  </si>
-  <si>
-    <t>https://santuccispizza.com/santuccis-roxborough/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/santuccis-original-square-pizza-philadelphia-2</t>
-  </si>
-  <si>
-    <t>Alyan’s Middle Eastern &amp; Mediterranean Restaurant</t>
-  </si>
-  <si>
-    <t>603 S 4th St, Philadelphia, PA 19147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 922-3553  </t>
-  </si>
-  <si>
-    <t>Apricot Stone</t>
-  </si>
-  <si>
-    <t>428 W Girard Ave, Philadelphia, PA 19123 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(267) 606-6596  </t>
-  </si>
-  <si>
-    <t>http://www.apricotstonephilly.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/apricot-stone-philadelphia-4</t>
-  </si>
-  <si>
-    <t>info@apricotstonephilly.com</t>
-  </si>
-  <si>
-    <t>Casablanca Mediterranean Grill</t>
-  </si>
-  <si>
-    <t>947 Federal St, Philadelphia, PA 19147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(267) 324-5165  </t>
-  </si>
-  <si>
-    <t>http://www.casablanca-grill.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/casablanca-mediterranean-grill-philadelphia</t>
-  </si>
-  <si>
-    <t>casablancamg947@gmail.com</t>
-  </si>
-  <si>
-    <t>Chabba Thai bistro</t>
-  </si>
-  <si>
-    <t>4343 Main St, Philadelphia, PA 19127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 483-1979  </t>
-  </si>
-  <si>
-    <t>https://chabaathai.com/</t>
-  </si>
-  <si>
-    <t>Fiorino</t>
-  </si>
-  <si>
-    <t>3572 Indian Queen Ln, Philadelphia, PA 19129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 843-1500  </t>
-  </si>
-  <si>
-    <t>https://www.fiorino.us/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/fiorino-philadelphia-2</t>
-  </si>
-  <si>
-    <t>Han dynasty (manayunk)</t>
-  </si>
-  <si>
-    <t>4356 Main St, Philadelphia, PA 19127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 508-2066  </t>
-  </si>
-  <si>
-    <t>http://www.handynasty.net/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/the-towpath-philadelphia</t>
-  </si>
-  <si>
-    <t>June BYOB</t>
-  </si>
-  <si>
-    <t> 690 Haddon Ave, Collingswood, NJ 08108 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(856) 240-7041  </t>
-  </si>
-  <si>
-    <t>http://www.junebyob.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/june-byob-collingswood</t>
-  </si>
-  <si>
-    <t>info@junebyob.com</t>
-  </si>
-  <si>
-    <t>Kung Fu Hot Pot</t>
-  </si>
-  <si>
-    <t>1008 Cherry St 3rd floor, Philadelphia, PA 19107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 606-1899  </t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/kungfu-hotpot-philadelphia</t>
-  </si>
-  <si>
-    <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
-  </si>
-  <si>
-    <t>Sakartvelo</t>
-  </si>
-  <si>
-    <t>705 Chestnut St, Philadelphia, PA 19106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(267) 319-1631  </t>
-  </si>
-  <si>
-    <t>https://sakartvelopa.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/sakartvelo-philadelphia</t>
-  </si>
-  <si>
-    <t>test@email.com</t>
-  </si>
-  <si>
-    <t>Scampi</t>
-  </si>
-  <si>
-    <t> 617 S 3rd St, Philadelphia, PA 19147 </t>
-  </si>
-  <si>
-    <t>https://www.scampiphilly.com/menu</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/scampi-philadelphia</t>
-  </si>
-  <si>
-    <t>Vientiane Bistro</t>
-  </si>
-  <si>
-    <t>2537 Kensington Ave, Philadelphia, PA 19125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(267) 703-8199  </t>
-  </si>
-  <si>
-    <t>https://www.vientianebistro.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/vientiane-bistro-philadelphia</t>
-  </si>
-  <si>
-    <t>astigma@astigmatic.com</t>
-  </si>
-  <si>
-    <t>White yak</t>
-  </si>
-  <si>
-    <t> 6118 Ridge Ave, Philadelphia, PA 19128 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 483-0764  </t>
-  </si>
-  <si>
-    <t>https://whiteyakrestaurant.com/?utm_source=google</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/white-yak-philadelphia</t>
-  </si>
-  <si>
-    <t>Yamitsuki</t>
-  </si>
-  <si>
-    <t>1028 Arch St , Philadelphia, PA 19107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 629-3888  </t>
-  </si>
-  <si>
-    <t>https://yamitsuki1028.wixsite.com/yamitsukiramen</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/yamitsuki-ramen-philadelphia</t>
-  </si>
-  <si>
-    <t>yamitsuki1028@gmail.com</t>
-  </si>
-  <si>
-    <t>Yanako restaurant</t>
-  </si>
-  <si>
-    <t>4345 Main St, Philadelphia, PA 19127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(267) 297-8151  </t>
-  </si>
-  <si>
-    <t>https://theyanako.com/</t>
-  </si>
-  <si>
-    <t>Zeppoli</t>
-  </si>
-  <si>
-    <t>618 Collings Ave, Collingswood NJ 08107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(856) 854-2670  </t>
-  </si>
-  <si>
-    <t>http://www.zeppolirestaurant.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/zeppoli-collingswood</t>
-  </si>
-  <si>
-    <t>philly_restaurant_type</t>
-  </si>
-  <si>
-    <t>philly_restaurant_type_other_note</t>
-  </si>
-  <si>
-    <t>philly_corkage_fee</t>
-  </si>
-  <si>
-    <t>corkage_fee_amount</t>
-  </si>
-  <si>
-    <t>other_corkage_policy</t>
-  </si>
-  <si>
-    <t>wine_service_equipment</t>
-  </si>
-  <si>
-    <t>philly_equipment_other_note</t>
-  </si>
-  <si>
-    <t>byob_service_level</t>
-  </si>
-  <si>
-    <t>Italian</t>
-  </si>
-  <si>
-    <t>free</t>
-  </si>
-  <si>
-    <t>wine glasses, opener/corkscrew, Ice bucket</t>
-  </si>
-  <si>
-    <t>self_service</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Tibetan</t>
-  </si>
-  <si>
-    <t>: -- 請選擇 --</t>
-  </si>
-  <si>
-    <t>basic_service</t>
-  </si>
-  <si>
-    <t>Thai, other</t>
-  </si>
-  <si>
-    <t>Laotian</t>
-  </si>
-  <si>
-    <t>wine glasses</t>
-  </si>
-  <si>
-    <t>Asian, other</t>
-  </si>
-  <si>
-    <t>Ramen</t>
-  </si>
-  <si>
-    <t>Idk</t>
-  </si>
-  <si>
-    <t>Idk I just walked in here with beers</t>
-  </si>
-  <si>
-    <t>no_service</t>
-  </si>
-  <si>
-    <t>Georgian</t>
-  </si>
-  <si>
-    <t>Mediterranean, other</t>
-  </si>
-  <si>
-    <t>Armenian/Syrian</t>
-  </si>
-  <si>
-    <t>Thai</t>
-  </si>
-  <si>
-    <t>corkage_fee</t>
-  </si>
-  <si>
-    <t>wine glasses, opener/corkscrew</t>
-  </si>
-  <si>
-    <t>Japanese, other</t>
-  </si>
-  <si>
-    <t>Sushi Bars</t>
-  </si>
-  <si>
-    <t>Italian, other</t>
-  </si>
-  <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>Asian</t>
-  </si>
-  <si>
-    <t>Mediterranean</t>
-  </si>
-  <si>
-    <t>wine glasses, shot glasses, opener/corkscrew, Ice bucket</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>Italian, Mediterranean</t>
-  </si>
-  <si>
-    <t>French, Fine dining</t>
-  </si>
-  <si>
-    <t>wine glasses, opener/corkscrew, wine storage locker service</t>
-  </si>
-  <si>
-    <t>full_service</t>
-  </si>
-  <si>
-    <t>Chinese</t>
-  </si>
-  <si>
-    <t>I think you just need to bring a bottle opener</t>
-  </si>
-  <si>
-    <t>Sandwiches</t>
-  </si>
-  <si>
-    <t>Breakfast &amp; Brunch</t>
-  </si>
-  <si>
-    <t>Italian, Mediterranean, Seafood</t>
-  </si>
-  <si>
-    <t>Italian, Seafood, other</t>
-  </si>
-  <si>
-    <t>Pasta Shops</t>
-  </si>
-  <si>
-    <t>Pizza, Desserts</t>
-  </si>
-  <si>
-    <t>Mexican, other</t>
-  </si>
-  <si>
-    <t>Sandwiches, Tacos</t>
-  </si>
-  <si>
-    <t>New American</t>
-  </si>
-  <si>
-    <t>Italian, American, Seafood</t>
-  </si>
-  <si>
-    <t>Seafood, Japanese, other</t>
-  </si>
-  <si>
-    <t>Seafood</t>
-  </si>
-  <si>
-    <t>Cambodian</t>
-  </si>
-  <si>
-    <t>Ramen, Sushi Bars</t>
-  </si>
-  <si>
-    <t>Tapas/Small Plates</t>
-  </si>
-  <si>
-    <t>Pop-Up Restaurants</t>
-  </si>
-  <si>
-    <t>Mediterranean, Seafood, other</t>
-  </si>
-  <si>
-    <t>Turkish</t>
-  </si>
-  <si>
-    <t>Supper Clubs</t>
-  </si>
-  <si>
-    <t>Greek</t>
-  </si>
-  <si>
-    <t>New Mexican Cuisine</t>
-  </si>
-  <si>
-    <t>Italian, Seafood</t>
-  </si>
-  <si>
-    <t>Moroccan</t>
-  </si>
-  <si>
-    <t>Russian, Dance Clubs</t>
-  </si>
-  <si>
-    <t>Indonesian</t>
-  </si>
-  <si>
-    <t>Middle Eastern</t>
-  </si>
-  <si>
-    <t>Mexican</t>
-  </si>
-  <si>
-    <t>Salad, Burgers</t>
-  </si>
-  <si>
-    <t>Filipino</t>
-  </si>
-  <si>
-    <t>Pizza, Tacos</t>
-  </si>
-  <si>
-    <t>Breakfast &amp; Brunch, Coffee &amp; Tea, Sandwiches</t>
-  </si>
-  <si>
-    <t>French, other</t>
-  </si>
-  <si>
-    <t>African</t>
-  </si>
-  <si>
-    <t>$10 per table</t>
-  </si>
-  <si>
-    <t>Sushi Bars, Wine Bars</t>
-  </si>
-  <si>
-    <t>Breakfast &amp; Brunch, Comfort Food</t>
-  </si>
-  <si>
     <t>The Choice</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>845 W Lancaster Ave Bryn Mawr, PA 19010</t>
@@ -1674,24 +1681,22 @@
     <t>Amma's South Indian Cuisine</t>
   </si>
   <si>
+    <t>103 S 39th St UNIT 3, PA 19104</t>
+  </si>
+  <si>
+    <t>(808) 762 6627</t>
+  </si>
+  <si>
+    <t>https://ammasrestaurants.com/university-city/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/amma-s-south-indian-cuisine-philadelphia</t>
+  </si>
+  <si>
     <t>Indian</t>
   </si>
   <si>
-    <t>https://ammasrestaurants.com/university-city/</t>
-  </si>
-  <si>
-    <t>103 S 39th St UNIT 3, PA 19104</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(808) 762 6627</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/amma-s-south-indian-cuisine-philadelphia</t>
-  </si>
-  <si>
     <t>info@ammasusa.com</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Terakawa Ramen</t>
@@ -1700,21 +1705,21 @@
     <t>204 North 9th street, Philadelphia, PA 19107</t>
   </si>
   <si>
+    <t>(267) 687-1355</t>
+  </si>
+  <si>
+    <t>https://terakawaramen.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/terakawa-ramen-philadelphia</t>
+  </si>
+  <si>
     <t>125 South 40th Street, Philadelphia, PA 19104</t>
   </si>
   <si>
-    <t>(267) 687-1355</t>
-  </si>
-  <si>
     <t>(215) 516-6818</t>
   </si>
   <si>
-    <t>https://terakawaramen.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/terakawa-ramen-philadelphia</t>
-  </si>
-  <si>
     <t>https://www.yelp.com/biz/terakawa-ramen-philadelphia-2</t>
   </si>
   <si>
@@ -1775,22 +1780,22 @@
     <t>Radicchio Cafe</t>
   </si>
   <si>
+    <t>402 Wood St Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t>(215) 627-6850</t>
+  </si>
+  <si>
+    <t>https://www.radicchiocafe.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/radicchio-cafe-philadelphia</t>
+  </si>
+  <si>
+    <t>Italian, Cafes</t>
+  </si>
+  <si>
     <t>info@radicchiocafe.com</t>
-  </si>
-  <si>
-    <t>402 Wood St Philadelphia, PA 19106</t>
-  </si>
-  <si>
-    <t>(215) 627-6850</t>
-  </si>
-  <si>
-    <t>https://www.radicchiocafe.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/radicchio-cafe-philadelphia</t>
-  </si>
-  <si>
-    <t>Italian, Cafes</t>
   </si>
 </sst>
 </file>
@@ -1860,8 +1865,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2164,23 +2171,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:AA94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
-    <col min="10" max="10" width="13.875" customWidth="1"/>
-    <col min="11" max="11" width="13.375" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="15" max="15" width="12.875" customWidth="1"/>
-    <col min="16" max="16" width="13.25" customWidth="1"/>
-    <col min="17" max="17" width="15.875" customWidth="1"/>
-    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="17" max="17" width="10.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2200,78 +2197,99 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>459</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>460</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>462</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>463</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>464</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>466</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1374</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" t="s">
+      <c r="N2" t="s">
         <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>467</v>
-      </c>
-      <c r="I2" t="s">
-        <v>468</v>
-      </c>
-      <c r="L2" t="s">
-        <v>469</v>
-      </c>
-      <c r="N2" t="s">
-        <v>470</v>
       </c>
       <c r="O2">
         <v>39.933934299999997</v>
@@ -2279,46 +2297,46 @@
       <c r="P2">
         <v>-75.165249199999991</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="3">
         <v>45969</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1376</v>
       </c>
       <c r="B3" t="s">
-        <v>439</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>442</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>443</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>472</v>
+        <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O3">
         <v>40.033780200000002</v>
@@ -2326,37 +2344,37 @@
       <c r="P3">
         <v>-75.21579659999999</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1377</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O4">
         <v>39.941107500000001</v>
@@ -2364,43 +2382,43 @@
       <c r="P4">
         <v>-75.146249400000002</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="3">
         <v>45969</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1383</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>434</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>435</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>436</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>437</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>475</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>476</v>
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>477</v>
+        <v>59</v>
       </c>
       <c r="N5" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
       <c r="O5">
         <v>39.988109899999998</v>
@@ -2408,52 +2426,52 @@
       <c r="P5">
         <v>-75.1282341</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="3">
         <v>45987</v>
       </c>
       <c r="R5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1387</v>
       </c>
       <c r="B6" t="s">
-        <v>444</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>445</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>447</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>448</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>479</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>480</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>481</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>482</v>
+        <v>70</v>
       </c>
       <c r="O6">
         <v>39.953542300000002</v>
@@ -2461,46 +2479,46 @@
       <c r="P6">
         <v>-75.157455200000001</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="3">
         <v>45987</v>
       </c>
       <c r="R6" t="s">
-        <v>422</v>
+        <v>71</v>
       </c>
       <c r="S6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1388</v>
       </c>
       <c r="B7" t="s">
-        <v>423</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>424</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>425</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>426</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N7" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O7">
         <v>39.949672</v>
@@ -2508,43 +2526,43 @@
       <c r="P7">
         <v>-75.152562000000017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="3">
         <v>45987</v>
       </c>
       <c r="R7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1389</v>
       </c>
       <c r="B8" t="s">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
-        <v>485</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O8">
         <v>39.969888599999997</v>
@@ -2552,40 +2570,40 @@
       <c r="P8">
         <v>-75.144038499999994</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="3">
         <v>45987</v>
       </c>
       <c r="R8" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1398</v>
       </c>
       <c r="B9" t="s">
-        <v>398</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>399</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>401</v>
+        <v>91</v>
       </c>
       <c r="G9" t="s">
-        <v>486</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>487</v>
+        <v>93</v>
       </c>
       <c r="L9" t="s">
-        <v>488</v>
+        <v>94</v>
       </c>
       <c r="N9" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O9">
         <v>40.025693400000002</v>
@@ -2593,40 +2611,40 @@
       <c r="P9">
         <v>-75.2233971</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1399</v>
       </c>
       <c r="B10" t="s">
-        <v>450</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>451</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>452</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>487</v>
+        <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>488</v>
+        <v>94</v>
       </c>
       <c r="N10" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O10">
         <v>40.025600900000001</v>
@@ -2634,40 +2652,40 @@
       <c r="P10">
         <v>-75.2234981</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1401</v>
       </c>
       <c r="B11" t="s">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>403</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>405</v>
+        <v>104</v>
       </c>
       <c r="F11" t="s">
-        <v>406</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
-        <v>477</v>
+        <v>59</v>
       </c>
       <c r="N11" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O11">
         <v>40.009791999999997</v>
@@ -2675,43 +2693,43 @@
       <c r="P11">
         <v>-75.190426099999996</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1402</v>
       </c>
       <c r="B12" t="s">
-        <v>378</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>379</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>381</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>382</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O12">
         <v>39.939035199999999</v>
@@ -2719,40 +2737,40 @@
       <c r="P12">
         <v>-75.159225399999997</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="3">
         <v>45985</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1404</v>
       </c>
       <c r="B13" t="s">
-        <v>407</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>408</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>409</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>410</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>411</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>493</v>
+        <v>118</v>
       </c>
       <c r="I13" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>477</v>
+        <v>59</v>
       </c>
       <c r="N13" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O13">
         <v>40.025373700000003</v>
@@ -2760,40 +2778,40 @@
       <c r="P13">
         <v>-75.223862799999992</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1407</v>
       </c>
       <c r="B14" t="s">
-        <v>392</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>393</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>396</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
-        <v>494</v>
+        <v>124</v>
       </c>
       <c r="I14" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>495</v>
+        <v>125</v>
       </c>
       <c r="N14" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
       <c r="O14">
         <v>39.9346672</v>
@@ -2801,37 +2819,37 @@
       <c r="P14">
         <v>-75.160286099999993</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="3">
         <v>45987</v>
       </c>
       <c r="R14" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1408</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>385</v>
+        <v>129</v>
       </c>
       <c r="G15" t="s">
-        <v>494</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
-        <v>496</v>
+        <v>130</v>
       </c>
       <c r="N15" t="s">
-        <v>482</v>
+        <v>70</v>
       </c>
       <c r="O15">
         <v>39.941414799999997</v>
@@ -2839,40 +2857,40 @@
       <c r="P15">
         <v>-75.149054199999995</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="3">
         <v>45987</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1409</v>
       </c>
       <c r="B16" t="s">
-        <v>454</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>455</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>456</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>457</v>
+        <v>134</v>
       </c>
       <c r="F16" t="s">
-        <v>458</v>
+        <v>135</v>
       </c>
       <c r="G16" t="s">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="I16" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="N16" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O16">
         <v>39.910713899999998</v>
@@ -2880,7 +2898,7 @@
       <c r="P16">
         <v>-75.084474200000002</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="3">
         <v>45987</v>
       </c>
     </row>
@@ -2889,31 +2907,31 @@
         <v>1410</v>
       </c>
       <c r="B17" t="s">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>414</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>415</v>
+        <v>140</v>
       </c>
       <c r="F17" t="s">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="G17" t="s">
-        <v>498</v>
+        <v>142</v>
       </c>
       <c r="I17" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="N17" t="s">
-        <v>474</v>
+        <v>51</v>
       </c>
       <c r="O17">
         <v>39.916215800000003</v>
@@ -2921,11 +2939,11 @@
       <c r="P17">
         <v>-75.069438599999998</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="3">
         <v>45987</v>
       </c>
       <c r="R17" t="s">
-        <v>417</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -2933,28 +2951,28 @@
         <v>1412</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>430</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>431</v>
+        <v>146</v>
       </c>
       <c r="F18" t="s">
-        <v>432</v>
+        <v>147</v>
       </c>
       <c r="G18" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>499</v>
+        <v>148</v>
       </c>
       <c r="N18" t="s">
-        <v>500</v>
+        <v>149</v>
       </c>
       <c r="O18">
         <v>39.940898199999999</v>
@@ -2962,7 +2980,7 @@
       <c r="P18">
         <v>-75.147503599999993</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="3">
         <v>45987</v>
       </c>
     </row>
@@ -2971,34 +2989,34 @@
         <v>1417</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>420</v>
+        <v>152</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>153</v>
       </c>
       <c r="G19" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>501</v>
+        <v>154</v>
       </c>
       <c r="I19" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="K19" t="s">
-        <v>502</v>
+        <v>155</v>
       </c>
       <c r="L19" t="s">
-        <v>496</v>
+        <v>130</v>
       </c>
       <c r="N19" t="s">
-        <v>470</v>
+        <v>35</v>
       </c>
       <c r="O19">
         <v>39.954462199999988</v>
@@ -3006,7 +3024,7 @@
       <c r="P19">
         <v>-75.156541500000003</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="3">
         <v>45987</v>
       </c>
     </row>
@@ -3015,28 +3033,28 @@
         <v>1555</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="G20" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O20">
         <v>39.967158499999996</v>
@@ -3044,11 +3062,11 @@
       <c r="P20">
         <v>-75.1753073</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="3">
         <v>45969</v>
       </c>
       <c r="R20" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -3056,31 +3074,31 @@
         <v>1556</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="G21" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>503</v>
+        <v>167</v>
       </c>
       <c r="I21" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O21">
         <v>39.938799099999997</v>
@@ -3088,7 +3106,7 @@
       <c r="P21">
         <v>-75.152359599999997</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3097,31 +3115,31 @@
         <v>1557</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="G22" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H22" t="s">
-        <v>504</v>
+        <v>173</v>
       </c>
       <c r="I22" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O22">
         <v>39.950006500000001</v>
@@ -3129,7 +3147,7 @@
       <c r="P22">
         <v>-75.179640800000001</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3138,25 +3156,25 @@
         <v>1558</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="G23" t="s">
-        <v>505</v>
+        <v>178</v>
       </c>
       <c r="I23" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O23">
         <v>39.945162000000003</v>
@@ -3164,11 +3182,11 @@
       <c r="P23">
         <v>-75.170259099999996</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="3">
         <v>45969</v>
       </c>
       <c r="R23" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -3176,31 +3194,31 @@
         <v>1559</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G24" t="s">
-        <v>506</v>
+        <v>185</v>
       </c>
       <c r="H24" t="s">
-        <v>507</v>
+        <v>186</v>
       </c>
       <c r="I24" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O24">
         <v>39.937890799999998</v>
@@ -3208,11 +3226,11 @@
       <c r="P24">
         <v>-75.144517199999996</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="3">
         <v>45969</v>
       </c>
       <c r="R24" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -3220,31 +3238,31 @@
         <v>1560</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
+        <v>192</v>
       </c>
       <c r="G25" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H25" t="s">
-        <v>508</v>
+        <v>193</v>
       </c>
       <c r="I25" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O25">
         <v>39.972437200000002</v>
@@ -3252,14 +3270,14 @@
       <c r="P25">
         <v>-75.141018599999995</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="3">
         <v>45969</v>
       </c>
       <c r="R25" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="S25" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -3267,28 +3285,28 @@
         <v>1561</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="G26" t="s">
-        <v>509</v>
+        <v>200</v>
       </c>
       <c r="H26" t="s">
-        <v>510</v>
+        <v>201</v>
       </c>
       <c r="I26" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O26">
         <v>39.930126299999998</v>
@@ -3296,11 +3314,11 @@
       <c r="P26">
         <v>-75.161606300000003</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="3">
         <v>45969</v>
       </c>
       <c r="R26" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -3308,25 +3326,25 @@
         <v>1562</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="G27" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I27" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N27" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O27">
         <v>39.970733099999997</v>
@@ -3334,11 +3352,11 @@
       <c r="P27">
         <v>-75.129705099999995</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
         <v>45969</v>
       </c>
       <c r="R27" t="s">
-        <v>62</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -3346,31 +3364,31 @@
         <v>1563</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>208</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="G28" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H28" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I28" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N28" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O28">
         <v>39.945286199999998</v>
@@ -3378,7 +3396,7 @@
       <c r="P28">
         <v>-75.164066699999992</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3387,31 +3405,31 @@
         <v>1564</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>214</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="G29" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I29" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N29" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O29">
         <v>39.945343899999997</v>
@@ -3419,7 +3437,7 @@
       <c r="P29">
         <v>-75.164232699999999</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3428,31 +3446,31 @@
         <v>1565</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="F30" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="G30" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H30" t="s">
-        <v>511</v>
+        <v>222</v>
       </c>
       <c r="I30" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N30" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O30">
         <v>39.971564299999997</v>
@@ -3460,7 +3478,7 @@
       <c r="P30">
         <v>-75.144519399999993</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3469,31 +3487,31 @@
         <v>1566</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="G31" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H31" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I31" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N31" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O31">
         <v>39.967347200000013</v>
@@ -3501,11 +3519,11 @@
       <c r="P31">
         <v>-75.140985200000003</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="3">
         <v>45969</v>
       </c>
       <c r="R31" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -3513,28 +3531,28 @@
         <v>1567</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="G32" t="s">
-        <v>512</v>
+        <v>233</v>
       </c>
       <c r="I32" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>469</v>
+        <v>34</v>
       </c>
       <c r="N32" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O32">
         <v>39.944823399999997</v>
@@ -3542,11 +3560,11 @@
       <c r="P32">
         <v>-75.180016899999998</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="3">
         <v>45969</v>
       </c>
       <c r="R32" t="s">
-        <v>87</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -3554,31 +3572,31 @@
         <v>1568</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>235</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>236</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>237</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="G33" t="s">
-        <v>513</v>
+        <v>240</v>
       </c>
       <c r="H33" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N33" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O33">
         <v>39.944419500000002</v>
@@ -3586,7 +3604,7 @@
       <c r="P33">
         <v>-75.170737899999992</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3595,28 +3613,28 @@
         <v>1569</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>242</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>243</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="G34" t="s">
-        <v>513</v>
+        <v>240</v>
       </c>
       <c r="H34" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I34" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O34">
         <v>39.949910799999998</v>
@@ -3624,7 +3642,7 @@
       <c r="P34">
         <v>-75.160454999999999</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3633,31 +3651,31 @@
         <v>1570</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>246</v>
       </c>
       <c r="D35" t="s">
+        <v>247</v>
+      </c>
+      <c r="E35" t="s">
+        <v>248</v>
+      </c>
+      <c r="F35" t="s">
+        <v>249</v>
+      </c>
+      <c r="G35" t="s">
         <v>99</v>
       </c>
-      <c r="E35" t="s">
+      <c r="H35" t="s">
         <v>100</v>
       </c>
-      <c r="F35" t="s">
-        <v>101</v>
-      </c>
-      <c r="G35" t="s">
-        <v>489</v>
-      </c>
-      <c r="H35" t="s">
-        <v>490</v>
-      </c>
       <c r="I35" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N35" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O35">
         <v>39.947785699999997</v>
@@ -3665,7 +3683,7 @@
       <c r="P35">
         <v>-75.160108000000008</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3674,28 +3692,28 @@
         <v>1571</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>253</v>
       </c>
       <c r="G36" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H36" t="s">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O36">
         <v>39.9681268</v>
@@ -3703,7 +3721,7 @@
       <c r="P36">
         <v>-75.134557399999991</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3712,28 +3730,28 @@
         <v>1573</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="E37" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="G37" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I37" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O37">
         <v>39.947794299999998</v>
@@ -3741,7 +3759,7 @@
       <c r="P37">
         <v>-75.167785299999991</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3750,25 +3768,25 @@
         <v>1574</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="F38" t="s">
-        <v>119</v>
+        <v>262</v>
       </c>
       <c r="G38" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O38">
         <v>39.919627800000001</v>
@@ -3776,7 +3794,7 @@
       <c r="P38">
         <v>-75.171386099999992</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3785,28 +3803,28 @@
         <v>1575</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>266</v>
       </c>
       <c r="F39" t="s">
-        <v>124</v>
+        <v>267</v>
       </c>
       <c r="G39" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I39" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N39" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O39">
         <v>39.939477599999996</v>
@@ -3814,7 +3832,7 @@
       <c r="P39">
         <v>-75.171194099999994</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3823,25 +3841,25 @@
         <v>1576</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>269</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>271</v>
       </c>
       <c r="G40" t="s">
-        <v>514</v>
+        <v>272</v>
       </c>
       <c r="I40" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N40" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O40">
         <v>39.939990700000003</v>
@@ -3849,11 +3867,11 @@
       <c r="P40">
         <v>-75.152963700000001</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="3">
         <v>45969</v>
       </c>
       <c r="R40" t="s">
-        <v>129</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -3861,28 +3879,28 @@
         <v>1577</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>276</v>
       </c>
       <c r="E41" t="s">
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="F41" t="s">
-        <v>134</v>
+        <v>278</v>
       </c>
       <c r="G41" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I41" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O41">
         <v>39.949691500000007</v>
@@ -3890,14 +3908,14 @@
       <c r="P41">
         <v>-75.173786499999991</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="3">
         <v>45969</v>
       </c>
       <c r="R41" t="s">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="S41" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -3905,28 +3923,28 @@
         <v>1578</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>282</v>
       </c>
       <c r="E42" t="s">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="F42" t="s">
-        <v>140</v>
+        <v>284</v>
       </c>
       <c r="G42" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H42" t="s">
-        <v>515</v>
+        <v>285</v>
       </c>
       <c r="I42" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N42" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O42">
         <v>39.9399765</v>
@@ -3934,7 +3952,7 @@
       <c r="P42">
         <v>-75.157853799999998</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -3943,28 +3961,28 @@
         <v>1579</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>286</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>287</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="G43" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I43" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N43" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O43">
         <v>39.951250900000012</v>
@@ -3972,11 +3990,11 @@
       <c r="P43">
         <v>-75.174123500000007</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="3">
         <v>45969</v>
       </c>
       <c r="R43" t="s">
-        <v>146</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -3984,28 +4002,28 @@
         <v>1580</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>293</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>294</v>
       </c>
       <c r="E44" t="s">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="F44" t="s">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="G44" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I44" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N44" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O44">
         <v>39.946499199999998</v>
@@ -4013,14 +4031,14 @@
       <c r="P44">
         <v>-75.161768199999997</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="3">
         <v>45969</v>
       </c>
       <c r="R44" t="s">
-        <v>152</v>
+        <v>297</v>
       </c>
       <c r="S44" t="s">
-        <v>153</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -4028,31 +4046,31 @@
         <v>1581</v>
       </c>
       <c r="B45" t="s">
-        <v>154</v>
+        <v>299</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>301</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>302</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>303</v>
       </c>
       <c r="G45" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H45" t="s">
-        <v>516</v>
+        <v>304</v>
       </c>
       <c r="I45" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N45" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O45">
         <v>39.953597799999997</v>
@@ -4060,7 +4078,7 @@
       <c r="P45">
         <v>-75.160984799999994</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4069,31 +4087,31 @@
         <v>1582</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>305</v>
       </c>
       <c r="C46" t="s">
-        <v>160</v>
+        <v>306</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="E46" t="s">
-        <v>162</v>
+        <v>308</v>
       </c>
       <c r="F46" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="G46" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H46" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I46" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O46">
         <v>39.944041200000001</v>
@@ -4101,7 +4119,7 @@
       <c r="P46">
         <v>-75.170019699999997</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4110,31 +4128,31 @@
         <v>1583</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
-        <v>166</v>
+        <v>312</v>
       </c>
       <c r="E47" t="s">
-        <v>167</v>
+        <v>313</v>
       </c>
       <c r="F47" t="s">
-        <v>168</v>
+        <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>517</v>
+        <v>315</v>
       </c>
       <c r="I47" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O47">
         <v>39.951949399999997</v>
@@ -4142,11 +4160,11 @@
       <c r="P47">
         <v>-75.144386900000001</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47" s="3">
         <v>45969</v>
       </c>
       <c r="R47" t="s">
-        <v>169</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -4154,31 +4172,31 @@
         <v>1584</v>
       </c>
       <c r="B48" t="s">
-        <v>170</v>
+        <v>317</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>318</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>319</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>320</v>
       </c>
       <c r="F48" t="s">
-        <v>174</v>
+        <v>321</v>
       </c>
       <c r="G48" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H48" t="s">
-        <v>518</v>
+        <v>322</v>
       </c>
       <c r="I48" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O48">
         <v>39.936869300000012</v>
@@ -4186,11 +4204,11 @@
       <c r="P48">
         <v>-75.156515900000002</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48" s="3">
         <v>45969</v>
       </c>
       <c r="R48" t="s">
-        <v>175</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -4198,31 +4216,31 @@
         <v>1585</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>324</v>
       </c>
       <c r="C49" t="s">
-        <v>177</v>
+        <v>325</v>
       </c>
       <c r="D49" t="s">
-        <v>178</v>
+        <v>326</v>
       </c>
       <c r="E49" t="s">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="F49" t="s">
-        <v>180</v>
+        <v>328</v>
       </c>
       <c r="G49" t="s">
-        <v>519</v>
+        <v>329</v>
       </c>
       <c r="H49" t="s">
-        <v>520</v>
+        <v>330</v>
       </c>
       <c r="I49" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O49">
         <v>39.965340099999999</v>
@@ -4230,11 +4248,11 @@
       <c r="P49">
         <v>-75.140709299999997</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49" s="3">
         <v>45969</v>
       </c>
       <c r="R49" t="s">
-        <v>181</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -4242,25 +4260,25 @@
         <v>1586</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="C50" t="s">
-        <v>183</v>
+        <v>333</v>
       </c>
       <c r="D50" t="s">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="F50" t="s">
-        <v>185</v>
+        <v>335</v>
       </c>
       <c r="G50" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I50" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N50" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O50">
         <v>39.951353500000003</v>
@@ -4268,7 +4286,7 @@
       <c r="P50">
         <v>-75.175115599999998</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4277,31 +4295,31 @@
         <v>1587</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>336</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>337</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>338</v>
       </c>
       <c r="E51" t="s">
-        <v>189</v>
+        <v>339</v>
       </c>
       <c r="F51" t="s">
-        <v>190</v>
+        <v>340</v>
       </c>
       <c r="G51" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="H51" t="s">
-        <v>521</v>
+        <v>341</v>
       </c>
       <c r="I51" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O51">
         <v>39.926275500000003</v>
@@ -4309,7 +4327,7 @@
       <c r="P51">
         <v>-75.167463699999999</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4318,28 +4336,28 @@
         <v>1588</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>342</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>343</v>
       </c>
       <c r="D52" t="s">
-        <v>193</v>
+        <v>344</v>
       </c>
       <c r="E52" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="F52" t="s">
-        <v>195</v>
+        <v>346</v>
       </c>
       <c r="G52" t="s">
-        <v>505</v>
+        <v>178</v>
       </c>
       <c r="I52" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N52" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O52">
         <v>39.919344799999998</v>
@@ -4347,7 +4365,7 @@
       <c r="P52">
         <v>-75.171119699999991</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4356,31 +4374,31 @@
         <v>1589</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>347</v>
       </c>
       <c r="C53" t="s">
-        <v>197</v>
+        <v>348</v>
       </c>
       <c r="D53" t="s">
-        <v>198</v>
+        <v>349</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>350</v>
       </c>
       <c r="F53" t="s">
-        <v>200</v>
+        <v>351</v>
       </c>
       <c r="G53" t="s">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
-        <v>522</v>
+        <v>352</v>
       </c>
       <c r="I53" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N53" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O53">
         <v>39.925220400000001</v>
@@ -4388,11 +4406,11 @@
       <c r="P53">
         <v>-75.174716699999991</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53" s="3">
         <v>45969</v>
       </c>
       <c r="R53" t="s">
-        <v>201</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -4400,31 +4418,31 @@
         <v>1590</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>354</v>
       </c>
       <c r="C54" t="s">
-        <v>203</v>
+        <v>355</v>
       </c>
       <c r="D54" t="s">
-        <v>204</v>
+        <v>356</v>
       </c>
       <c r="E54" t="s">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="F54" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="G54" t="s">
-        <v>509</v>
+        <v>200</v>
       </c>
       <c r="H54" t="s">
-        <v>523</v>
+        <v>359</v>
       </c>
       <c r="I54" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N54" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O54">
         <v>39.9339212</v>
@@ -4432,7 +4450,7 @@
       <c r="P54">
         <v>-75.155556500000003</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4441,28 +4459,28 @@
         <v>1591</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
+        <v>360</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
+        <v>361</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>362</v>
       </c>
       <c r="E55" t="s">
-        <v>210</v>
+        <v>363</v>
       </c>
       <c r="F55" t="s">
-        <v>211</v>
+        <v>364</v>
       </c>
       <c r="G55" t="s">
-        <v>486</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O55">
         <v>39.942576899999999</v>
@@ -4470,11 +4488,11 @@
       <c r="P55">
         <v>-75.185306799999992</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55" s="3">
         <v>45969</v>
       </c>
       <c r="R55" t="s">
-        <v>212</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
@@ -4482,28 +4500,28 @@
         <v>1592</v>
       </c>
       <c r="B56" t="s">
-        <v>213</v>
+        <v>366</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>367</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>368</v>
       </c>
       <c r="E56" t="s">
-        <v>216</v>
+        <v>369</v>
       </c>
       <c r="F56" t="s">
-        <v>217</v>
+        <v>370</v>
       </c>
       <c r="G56" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N56" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O56">
         <v>39.948765399999999</v>
@@ -4511,11 +4529,11 @@
       <c r="P56">
         <v>-75.177968399999997</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56" s="3">
         <v>45969</v>
       </c>
       <c r="R56" t="s">
-        <v>218</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
@@ -4523,31 +4541,31 @@
         <v>1593</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>372</v>
       </c>
       <c r="C57" t="s">
-        <v>220</v>
+        <v>373</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>374</v>
       </c>
       <c r="E57" t="s">
-        <v>222</v>
+        <v>375</v>
       </c>
       <c r="F57" t="s">
-        <v>223</v>
+        <v>376</v>
       </c>
       <c r="G57" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H57" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I57" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N57" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O57">
         <v>39.9515782</v>
@@ -4555,7 +4573,7 @@
       <c r="P57">
         <v>-75.174830900000003</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4564,31 +4582,31 @@
         <v>1594</v>
       </c>
       <c r="B58" t="s">
-        <v>224</v>
+        <v>377</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>378</v>
       </c>
       <c r="D58" t="s">
-        <v>226</v>
+        <v>379</v>
       </c>
       <c r="E58" t="s">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="F58" t="s">
-        <v>228</v>
+        <v>381</v>
       </c>
       <c r="G58" t="s">
-        <v>475</v>
+        <v>57</v>
       </c>
       <c r="H58" t="s">
-        <v>476</v>
+        <v>58</v>
       </c>
       <c r="I58" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N58" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O58">
         <v>39.948388199999997</v>
@@ -4596,7 +4614,7 @@
       <c r="P58">
         <v>-75.217944799999998</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58" s="3">
         <v>45969</v>
       </c>
     </row>
@@ -4605,28 +4623,28 @@
         <v>1726</v>
       </c>
       <c r="B59" t="s">
-        <v>229</v>
+        <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="D59" t="s">
-        <v>231</v>
+        <v>384</v>
       </c>
       <c r="E59" t="s">
-        <v>232</v>
+        <v>385</v>
       </c>
       <c r="F59" t="s">
-        <v>233</v>
+        <v>386</v>
       </c>
       <c r="G59" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O59">
         <v>39.931907000000002</v>
@@ -4634,7 +4652,7 @@
       <c r="P59">
         <v>-75.149544399999996</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4643,28 +4661,28 @@
         <v>1727</v>
       </c>
       <c r="B60" t="s">
-        <v>234</v>
+        <v>387</v>
       </c>
       <c r="C60" t="s">
-        <v>235</v>
+        <v>388</v>
       </c>
       <c r="D60" t="s">
-        <v>236</v>
+        <v>389</v>
       </c>
       <c r="F60" t="s">
-        <v>237</v>
+        <v>390</v>
       </c>
       <c r="G60" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H60" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I60" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O60">
         <v>39.910426600000001</v>
@@ -4672,7 +4690,7 @@
       <c r="P60">
         <v>-75.050069499999992</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4681,25 +4699,25 @@
         <v>1729</v>
       </c>
       <c r="B61" t="s">
-        <v>238</v>
+        <v>391</v>
       </c>
       <c r="C61" t="s">
-        <v>239</v>
+        <v>392</v>
       </c>
       <c r="D61" t="s">
-        <v>240</v>
+        <v>393</v>
       </c>
       <c r="F61" t="s">
-        <v>241</v>
+        <v>394</v>
       </c>
       <c r="G61" t="s">
-        <v>494</v>
+        <v>124</v>
       </c>
       <c r="I61" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N61" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O61">
         <v>39.941114900000002</v>
@@ -4707,7 +4725,7 @@
       <c r="P61">
         <v>-75.149088399999997</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4716,25 +4734,25 @@
         <v>1730</v>
       </c>
       <c r="B62" t="s">
-        <v>242</v>
+        <v>395</v>
       </c>
       <c r="C62" t="s">
-        <v>243</v>
+        <v>396</v>
       </c>
       <c r="D62" t="s">
-        <v>244</v>
+        <v>397</v>
       </c>
       <c r="F62" t="s">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="G62" t="s">
-        <v>524</v>
+        <v>399</v>
       </c>
       <c r="I62" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O62">
         <v>39.939704499999998</v>
@@ -4742,7 +4760,7 @@
       <c r="P62">
         <v>-75.156259599999998</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4751,31 +4769,31 @@
         <v>1731</v>
       </c>
       <c r="B63" t="s">
-        <v>246</v>
+        <v>400</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>401</v>
       </c>
       <c r="D63" t="s">
-        <v>248</v>
+        <v>402</v>
       </c>
       <c r="E63" t="s">
-        <v>249</v>
+        <v>403</v>
       </c>
       <c r="F63" t="s">
-        <v>250</v>
+        <v>404</v>
       </c>
       <c r="G63" t="s">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s">
-        <v>525</v>
+        <v>405</v>
       </c>
       <c r="I63" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N63" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O63">
         <v>39.968518099999997</v>
@@ -4783,7 +4801,7 @@
       <c r="P63">
         <v>-75.178519699999995</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4792,28 +4810,28 @@
         <v>1732</v>
       </c>
       <c r="B64" t="s">
-        <v>251</v>
+        <v>406</v>
       </c>
       <c r="C64" t="s">
-        <v>252</v>
+        <v>407</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="E64" t="s">
-        <v>254</v>
+        <v>409</v>
       </c>
       <c r="F64" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="G64" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O64">
         <v>39.9413883</v>
@@ -4821,14 +4839,14 @@
       <c r="P64">
         <v>-75.150354600000014</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64" s="3">
         <v>45977</v>
       </c>
       <c r="R64" t="s">
-        <v>256</v>
+        <v>411</v>
       </c>
       <c r="S64" t="s">
-        <v>257</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
@@ -4836,31 +4854,31 @@
         <v>1733</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>413</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>414</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>415</v>
       </c>
       <c r="E65" t="s">
-        <v>261</v>
+        <v>416</v>
       </c>
       <c r="F65" t="s">
-        <v>262</v>
+        <v>417</v>
       </c>
       <c r="G65" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H65" t="s">
-        <v>526</v>
+        <v>418</v>
       </c>
       <c r="I65" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N65" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O65">
         <v>40.1219337</v>
@@ -4868,7 +4886,7 @@
       <c r="P65">
         <v>-75.034327399999995</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4877,28 +4895,28 @@
         <v>1734</v>
       </c>
       <c r="B66" t="s">
-        <v>263</v>
+        <v>419</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="D66" t="s">
-        <v>265</v>
+        <v>421</v>
       </c>
       <c r="F66" t="s">
-        <v>266</v>
+        <v>422</v>
       </c>
       <c r="G66" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="H66" t="s">
-        <v>527</v>
+        <v>423</v>
       </c>
       <c r="I66" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N66" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O66">
         <v>39.928446399999999</v>
@@ -4906,7 +4924,7 @@
       <c r="P66">
         <v>-75.171258600000002</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4915,25 +4933,25 @@
         <v>1735</v>
       </c>
       <c r="B67" t="s">
-        <v>267</v>
+        <v>424</v>
       </c>
       <c r="C67" t="s">
-        <v>268</v>
+        <v>425</v>
       </c>
       <c r="F67" t="s">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="G67" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H67" t="s">
-        <v>503</v>
+        <v>167</v>
       </c>
       <c r="I67" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N67" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O67">
         <v>39.919901199999998</v>
@@ -4941,7 +4959,7 @@
       <c r="P67">
         <v>-75.173383200000004</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -4950,31 +4968,31 @@
         <v>1736</v>
       </c>
       <c r="B68" t="s">
-        <v>270</v>
+        <v>427</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>428</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>429</v>
       </c>
       <c r="E68" t="s">
-        <v>273</v>
+        <v>430</v>
       </c>
       <c r="F68" t="s">
-        <v>274</v>
+        <v>431</v>
       </c>
       <c r="G68" t="s">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s">
-        <v>528</v>
+        <v>432</v>
       </c>
       <c r="I68" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O68">
         <v>39.9463188</v>
@@ -4982,14 +5000,14 @@
       <c r="P68">
         <v>-75.157960899999992</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68" s="3">
         <v>45977</v>
       </c>
       <c r="R68" t="s">
-        <v>275</v>
+        <v>433</v>
       </c>
       <c r="S68" t="s">
-        <v>276</v>
+        <v>434</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
@@ -4997,28 +5015,28 @@
         <v>1737</v>
       </c>
       <c r="B69" t="s">
-        <v>277</v>
+        <v>435</v>
       </c>
       <c r="C69" t="s">
-        <v>278</v>
+        <v>436</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>437</v>
       </c>
       <c r="E69" t="s">
-        <v>280</v>
+        <v>438</v>
       </c>
       <c r="F69" t="s">
-        <v>281</v>
+        <v>439</v>
       </c>
       <c r="G69" t="s">
-        <v>529</v>
+        <v>440</v>
       </c>
       <c r="I69" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O69">
         <v>39.918631400000002</v>
@@ -5026,7 +5044,7 @@
       <c r="P69">
         <v>-75.153989299999992</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5035,28 +5053,28 @@
         <v>1738</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>441</v>
       </c>
       <c r="C70" t="s">
-        <v>283</v>
+        <v>442</v>
       </c>
       <c r="D70" t="s">
-        <v>284</v>
+        <v>443</v>
       </c>
       <c r="E70" t="s">
-        <v>285</v>
+        <v>444</v>
       </c>
       <c r="F70" t="s">
-        <v>286</v>
+        <v>445</v>
       </c>
       <c r="G70" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I70" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N70" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O70">
         <v>39.947769000000001</v>
@@ -5064,11 +5082,11 @@
       <c r="P70">
         <v>-75.16970049999999</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="3">
         <v>45977</v>
       </c>
       <c r="R70" t="s">
-        <v>287</v>
+        <v>446</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.3">
@@ -5076,28 +5094,28 @@
         <v>1739</v>
       </c>
       <c r="B71" t="s">
-        <v>288</v>
+        <v>447</v>
       </c>
       <c r="C71" t="s">
-        <v>289</v>
+        <v>448</v>
       </c>
       <c r="D71" t="s">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="F71" t="s">
-        <v>291</v>
+        <v>450</v>
       </c>
       <c r="G71" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H71" t="s">
-        <v>530</v>
+        <v>451</v>
       </c>
       <c r="I71" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N71" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O71">
         <v>39.943967499999999</v>
@@ -5105,7 +5123,7 @@
       <c r="P71">
         <v>-75.169153299999991</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5114,28 +5132,28 @@
         <v>1740</v>
       </c>
       <c r="B72" t="s">
-        <v>292</v>
+        <v>452</v>
       </c>
       <c r="C72" t="s">
-        <v>293</v>
+        <v>453</v>
       </c>
       <c r="D72" t="s">
-        <v>294</v>
+        <v>454</v>
       </c>
       <c r="E72" t="s">
-        <v>295</v>
+        <v>455</v>
       </c>
       <c r="F72" t="s">
-        <v>296</v>
+        <v>456</v>
       </c>
       <c r="G72" t="s">
-        <v>467</v>
+        <v>32</v>
       </c>
       <c r="I72" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N72" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O72">
         <v>40.059318500000003</v>
@@ -5143,17 +5161,17 @@
       <c r="P72">
         <v>-75.190036300000003</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72" s="3">
         <v>45977</v>
       </c>
       <c r="R72" t="s">
-        <v>297</v>
+        <v>457</v>
       </c>
       <c r="S72" t="s">
-        <v>298</v>
+        <v>458</v>
       </c>
       <c r="T72" t="s">
-        <v>299</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.3">
@@ -5161,28 +5179,28 @@
         <v>1741</v>
       </c>
       <c r="B73" t="s">
-        <v>300</v>
+        <v>460</v>
       </c>
       <c r="C73" t="s">
-        <v>301</v>
+        <v>461</v>
       </c>
       <c r="D73" t="s">
-        <v>302</v>
+        <v>462</v>
       </c>
       <c r="E73" t="s">
-        <v>303</v>
+        <v>463</v>
       </c>
       <c r="F73" t="s">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="G73" t="s">
-        <v>529</v>
+        <v>440</v>
       </c>
       <c r="I73" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N73" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O73">
         <v>39.921155900000002</v>
@@ -5190,11 +5208,11 @@
       <c r="P73">
         <v>-75.163266499999992</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73" s="3">
         <v>45977</v>
       </c>
       <c r="R73" t="s">
-        <v>305</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
@@ -5202,28 +5220,28 @@
         <v>1742</v>
       </c>
       <c r="B74" t="s">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="C74" t="s">
-        <v>307</v>
+        <v>467</v>
       </c>
       <c r="D74" t="s">
-        <v>308</v>
+        <v>468</v>
       </c>
       <c r="E74" t="s">
-        <v>309</v>
+        <v>469</v>
       </c>
       <c r="F74" t="s">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="G74" t="s">
-        <v>529</v>
+        <v>440</v>
       </c>
       <c r="I74" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O74">
         <v>39.926405699999997</v>
@@ -5231,7 +5249,7 @@
       <c r="P74">
         <v>-75.157535600000003</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5240,31 +5258,31 @@
         <v>1743</v>
       </c>
       <c r="B75" t="s">
-        <v>311</v>
+        <v>471</v>
       </c>
       <c r="C75" t="s">
-        <v>312</v>
+        <v>472</v>
       </c>
       <c r="D75" t="s">
-        <v>313</v>
+        <v>473</v>
       </c>
       <c r="E75" t="s">
-        <v>314</v>
+        <v>474</v>
       </c>
       <c r="F75" t="s">
-        <v>315</v>
+        <v>475</v>
       </c>
       <c r="G75" t="s">
-        <v>506</v>
+        <v>185</v>
       </c>
       <c r="H75" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I75" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N75" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O75">
         <v>39.952112100000001</v>
@@ -5272,11 +5290,11 @@
       <c r="P75">
         <v>-75.172149099999999</v>
       </c>
-      <c r="Q75" s="2">
+      <c r="Q75" s="3">
         <v>45977</v>
       </c>
       <c r="R75" t="s">
-        <v>316</v>
+        <v>476</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
@@ -5284,31 +5302,31 @@
         <v>1744</v>
       </c>
       <c r="B76" t="s">
-        <v>317</v>
+        <v>477</v>
       </c>
       <c r="C76" t="s">
-        <v>318</v>
+        <v>478</v>
       </c>
       <c r="D76" t="s">
-        <v>319</v>
+        <v>479</v>
       </c>
       <c r="E76" t="s">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="F76" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="G76" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H76" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I76" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N76" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O76">
         <v>39.982485199999999</v>
@@ -5316,11 +5334,11 @@
       <c r="P76">
         <v>-75.102839599999996</v>
       </c>
-      <c r="Q76" s="2">
+      <c r="Q76" s="3">
         <v>45977</v>
       </c>
       <c r="R76" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
@@ -5328,31 +5346,31 @@
         <v>1745</v>
       </c>
       <c r="B77" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="C77" t="s">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="D77" t="s">
-        <v>325</v>
+        <v>485</v>
       </c>
       <c r="E77" t="s">
-        <v>326</v>
+        <v>486</v>
       </c>
       <c r="F77" t="s">
-        <v>327</v>
+        <v>487</v>
       </c>
       <c r="G77" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H77" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I77" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N77" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O77">
         <v>39.940707699999997</v>
@@ -5360,7 +5378,7 @@
       <c r="P77">
         <v>-75.146044199999992</v>
       </c>
-      <c r="Q77" s="2">
+      <c r="Q77" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5369,31 +5387,31 @@
         <v>1746</v>
       </c>
       <c r="B78" t="s">
-        <v>328</v>
+        <v>488</v>
       </c>
       <c r="C78" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="D78" t="s">
-        <v>330</v>
+        <v>490</v>
       </c>
       <c r="E78" t="s">
-        <v>331</v>
+        <v>491</v>
       </c>
       <c r="F78" t="s">
-        <v>332</v>
+        <v>492</v>
       </c>
       <c r="G78" t="s">
-        <v>478</v>
+        <v>66</v>
       </c>
       <c r="H78" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="I78" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N78" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O78">
         <v>39.938333399999998</v>
@@ -5401,14 +5419,14 @@
       <c r="P78">
         <v>-75.159783899999994</v>
       </c>
-      <c r="Q78" s="2">
+      <c r="Q78" s="3">
         <v>45977</v>
       </c>
       <c r="R78" t="s">
-        <v>333</v>
+        <v>494</v>
       </c>
       <c r="S78" t="s">
-        <v>334</v>
+        <v>495</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
@@ -5416,31 +5434,31 @@
         <v>1747</v>
       </c>
       <c r="B79" t="s">
-        <v>335</v>
+        <v>496</v>
       </c>
       <c r="C79" t="s">
-        <v>336</v>
+        <v>497</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>498</v>
       </c>
       <c r="E79" t="s">
-        <v>338</v>
+        <v>499</v>
       </c>
       <c r="F79" t="s">
-        <v>339</v>
+        <v>500</v>
       </c>
       <c r="G79" t="s">
-        <v>491</v>
+        <v>111</v>
       </c>
       <c r="H79" t="s">
-        <v>492</v>
+        <v>112</v>
       </c>
       <c r="I79" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N79" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O79">
         <v>39.9803949</v>
@@ -5448,7 +5466,7 @@
       <c r="P79">
         <v>-75.113133699999992</v>
       </c>
-      <c r="Q79" s="2">
+      <c r="Q79" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5457,31 +5475,31 @@
         <v>1748</v>
       </c>
       <c r="B80" t="s">
-        <v>340</v>
+        <v>501</v>
       </c>
       <c r="C80" t="s">
-        <v>341</v>
+        <v>502</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>503</v>
       </c>
       <c r="E80" t="s">
-        <v>343</v>
+        <v>504</v>
       </c>
       <c r="F80" t="s">
-        <v>344</v>
+        <v>505</v>
       </c>
       <c r="G80" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H80" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="I80" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N80" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O80">
         <v>39.926336599999999</v>
@@ -5489,7 +5507,7 @@
       <c r="P80">
         <v>-75.147412399999993</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5498,31 +5516,31 @@
         <v>1749</v>
       </c>
       <c r="B81" t="s">
-        <v>345</v>
+        <v>507</v>
       </c>
       <c r="C81" t="s">
-        <v>346</v>
+        <v>508</v>
       </c>
       <c r="D81" t="s">
-        <v>347</v>
+        <v>509</v>
       </c>
       <c r="E81" t="s">
-        <v>348</v>
+        <v>510</v>
       </c>
       <c r="F81" t="s">
-        <v>349</v>
+        <v>511</v>
       </c>
       <c r="G81" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H81" t="s">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="I81" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O81">
         <v>39.964689399999997</v>
@@ -5530,7 +5548,7 @@
       <c r="P81">
         <v>-75.174111199999999</v>
       </c>
-      <c r="Q81" s="2">
+      <c r="Q81" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5539,31 +5557,31 @@
         <v>1750</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>512</v>
       </c>
       <c r="C82" t="s">
-        <v>351</v>
+        <v>513</v>
       </c>
       <c r="D82" t="s">
-        <v>352</v>
+        <v>514</v>
       </c>
       <c r="E82" t="s">
-        <v>353</v>
+        <v>515</v>
       </c>
       <c r="F82" t="s">
-        <v>354</v>
+        <v>516</v>
       </c>
       <c r="G82" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H82" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="I82" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N82" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O82">
         <v>39.947806000000007</v>
@@ -5571,7 +5589,7 @@
       <c r="P82">
         <v>-75.160342099999994</v>
       </c>
-      <c r="Q82" s="2">
+      <c r="Q82" s="3">
         <v>45977</v>
       </c>
     </row>
@@ -5580,34 +5598,34 @@
         <v>1754</v>
       </c>
       <c r="B83" t="s">
-        <v>355</v>
+        <v>518</v>
       </c>
       <c r="C83" t="s">
-        <v>356</v>
+        <v>519</v>
       </c>
       <c r="D83" t="s">
-        <v>357</v>
+        <v>520</v>
       </c>
       <c r="E83" t="s">
-        <v>358</v>
+        <v>521</v>
       </c>
       <c r="F83" t="s">
-        <v>359</v>
+        <v>522</v>
       </c>
       <c r="G83" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="H83" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="I83" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="K83" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="N83" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O83">
         <v>39.944972700000001</v>
@@ -5615,11 +5633,11 @@
       <c r="P83">
         <v>-75.177395099999998</v>
       </c>
-      <c r="Q83" s="2">
+      <c r="Q83" s="3">
         <v>45978</v>
       </c>
       <c r="R83" t="s">
-        <v>360</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -5627,28 +5645,28 @@
         <v>1755</v>
       </c>
       <c r="B84" t="s">
-        <v>361</v>
+        <v>527</v>
       </c>
       <c r="C84" t="s">
-        <v>362</v>
+        <v>528</v>
       </c>
       <c r="E84" t="s">
-        <v>363</v>
+        <v>529</v>
       </c>
       <c r="F84" t="s">
-        <v>364</v>
+        <v>530</v>
       </c>
       <c r="G84" t="s">
-        <v>471</v>
+        <v>43</v>
       </c>
       <c r="H84" t="s">
-        <v>518</v>
+        <v>322</v>
       </c>
       <c r="I84" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N84" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O84">
         <v>39.974236699999999</v>
@@ -5656,11 +5674,11 @@
       <c r="P84">
         <v>-75.182546800000011</v>
       </c>
-      <c r="Q84" s="2">
+      <c r="Q84" s="3">
         <v>45978</v>
       </c>
       <c r="R84" t="s">
-        <v>365</v>
+        <v>531</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -5668,31 +5686,31 @@
         <v>1756</v>
       </c>
       <c r="B85" t="s">
-        <v>366</v>
+        <v>532</v>
       </c>
       <c r="C85" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
       <c r="D85" t="s">
-        <v>368</v>
+        <v>534</v>
       </c>
       <c r="E85" t="s">
-        <v>369</v>
+        <v>535</v>
       </c>
       <c r="F85" t="s">
-        <v>370</v>
+        <v>536</v>
       </c>
       <c r="G85" t="s">
-        <v>489</v>
+        <v>99</v>
       </c>
       <c r="H85" t="s">
         <v>537</v>
       </c>
       <c r="I85" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N85" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O85">
         <v>39.9798258</v>
@@ -5700,11 +5718,11 @@
       <c r="P85">
         <v>-75.129835499999999</v>
       </c>
-      <c r="Q85" s="2">
+      <c r="Q85" s="3">
         <v>45978</v>
       </c>
       <c r="R85" t="s">
-        <v>371</v>
+        <v>538</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
@@ -5712,31 +5730,31 @@
         <v>1757</v>
       </c>
       <c r="B86" t="s">
-        <v>372</v>
+        <v>539</v>
       </c>
       <c r="C86" t="s">
-        <v>373</v>
+        <v>540</v>
       </c>
       <c r="D86" t="s">
-        <v>374</v>
+        <v>541</v>
       </c>
       <c r="E86" t="s">
-        <v>375</v>
+        <v>542</v>
       </c>
       <c r="F86" t="s">
-        <v>376</v>
+        <v>543</v>
       </c>
       <c r="G86" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="H86" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="I86" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N86" t="s">
-        <v>473</v>
+        <v>45</v>
       </c>
       <c r="O86">
         <v>39.944876200000003</v>
@@ -5744,258 +5762,327 @@
       <c r="P86">
         <v>-75.160762800000001</v>
       </c>
-      <c r="Q86" s="2">
+      <c r="Q86" s="3">
         <v>45979</v>
       </c>
       <c r="R86" t="s">
-        <v>377</v>
+        <v>545</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1786</v>
+      </c>
       <c r="B87" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C87" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D87" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="E87" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F87" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G87" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="I87" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N87" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q87" s="2">
+        <v>45</v>
+      </c>
+      <c r="O87">
+        <v>40.022318299999988</v>
+      </c>
+      <c r="P87">
+        <v>-75.319580799999997</v>
+      </c>
+      <c r="Q87" s="3">
         <v>45997</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1787</v>
+      </c>
       <c r="B88" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="C88" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D88" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E88" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="F88" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G88" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="I88" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q88" s="2">
+        <v>45</v>
+      </c>
+      <c r="O88">
+        <v>39.954628999999997</v>
+      </c>
+      <c r="P88">
+        <v>-75.199683899999997</v>
+      </c>
+      <c r="Q88" s="3">
         <v>45997</v>
       </c>
-      <c r="R88" s="3" t="s">
-        <v>551</v>
+      <c r="R88" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1788</v>
+      </c>
       <c r="B89" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C89" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D89" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E89" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F89" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="G89" t="s">
-        <v>479</v>
+        <v>67</v>
       </c>
       <c r="I89" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N89" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q89" s="2">
+        <v>45</v>
+      </c>
+      <c r="O89">
+        <v>39.955408599999998</v>
+      </c>
+      <c r="P89">
+        <v>-75.1544861</v>
+      </c>
+      <c r="Q89" s="3">
         <v>45997</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1789</v>
+      </c>
       <c r="B90" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C90" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="D90" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E90" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F90" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="G90" t="s">
-        <v>479</v>
+        <v>67</v>
       </c>
       <c r="I90" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q90" s="2">
+        <v>45</v>
+      </c>
+      <c r="O90">
+        <v>39.954715299999997</v>
+      </c>
+      <c r="P90">
+        <v>-75.202095200000002</v>
+      </c>
+      <c r="Q90" s="3">
         <v>45997</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1790</v>
+      </c>
       <c r="B91" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="C91" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D91" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="F91" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G91" t="s">
-        <v>501</v>
+        <v>154</v>
       </c>
       <c r="I91" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N91" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q91" s="2">
+        <v>45</v>
+      </c>
+      <c r="O91">
+        <v>39.953813599999997</v>
+      </c>
+      <c r="P91">
+        <v>-75.1558378</v>
+      </c>
+      <c r="Q91" s="3">
         <v>45997</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1791</v>
+      </c>
       <c r="B92" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C92" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D92" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="E92" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F92" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="G92" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="I92" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N92" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q92" s="2">
+        <v>45</v>
+      </c>
+      <c r="O92">
+        <v>39.967475999999998</v>
+      </c>
+      <c r="P92">
+        <v>-75.1694289</v>
+      </c>
+      <c r="Q92" s="3">
         <v>45997</v>
       </c>
       <c r="R92" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1792</v>
+      </c>
       <c r="B93" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C93" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="D93" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E93" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="F93" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="G93" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="I93" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N93" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q93" s="2">
+        <v>45</v>
+      </c>
+      <c r="O93">
+        <v>39.966393500000002</v>
+      </c>
+      <c r="P93">
+        <v>-75.134263699999991</v>
+      </c>
+      <c r="Q93" s="3">
         <v>45997</v>
       </c>
       <c r="R93" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1793</v>
+      </c>
       <c r="B94" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C94" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="D94" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E94" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="F94" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="G94" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="I94" t="s">
-        <v>468</v>
+        <v>33</v>
       </c>
       <c r="N94" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q94" s="2">
+        <v>45</v>
+      </c>
+      <c r="O94">
+        <v>39.956620099999988</v>
+      </c>
+      <c r="P94">
+        <v>-75.146333400000003</v>
+      </c>
+      <c r="Q94" s="3">
         <v>45997</v>
       </c>
       <c r="R94" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T86">
-    <sortCondition ref="A2:A86"/>
-  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BB5322-6432-4257-9EC9-AC71D11A9850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5F3359-F541-40EF-9598-E1077B2E0949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="598">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -1796,6 +1796,25 @@
   </si>
   <si>
     <t>info@radicchiocafe.com</t>
+  </si>
+  <si>
+    <t>Bucatini Caffè</t>
+  </si>
+  <si>
+    <t>1824 S 13th St, Philadelphia, PA 19148</t>
+  </si>
+  <si>
+    <t>(215) 990-2821</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bucatinicaffe.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/bucatini-caffe-philadelphia</t>
+  </si>
+  <si>
+    <t>Italian, Pasta Shops</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA94"/>
+  <dimension ref="A1:AA95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="10.75" style="3" customWidth="1"/>
@@ -6082,6 +6101,35 @@
         <v>591</v>
       </c>
     </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>592</v>
+      </c>
+      <c r="C95" t="s">
+        <v>593</v>
+      </c>
+      <c r="D95" t="s">
+        <v>594</v>
+      </c>
+      <c r="E95" t="s">
+        <v>595</v>
+      </c>
+      <c r="F95" t="s">
+        <v>596</v>
+      </c>
+      <c r="G95" t="s">
+        <v>597</v>
+      </c>
+      <c r="I95" t="s">
+        <v>33</v>
+      </c>
+      <c r="N95" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q95" s="3">
+        <v>45997</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5F3359-F541-40EF-9598-E1077B2E0949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C738C8BB-7814-4A29-9F94-0B16D77B3BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="601">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -1750,9 +1750,6 @@
     <t>https://www.yelp.com/biz/tiffin-fairmount-philadelphia</t>
   </si>
   <si>
-    <t>Desserts, Vegan, Indian</t>
-  </si>
-  <si>
     <t>catering@tiffin.com</t>
   </si>
   <si>
@@ -1792,9 +1789,6 @@
     <t>https://www.yelp.com/biz/radicchio-cafe-philadelphia</t>
   </si>
   <si>
-    <t>Italian, Cafes</t>
-  </si>
-  <si>
     <t>info@radicchiocafe.com</t>
   </si>
   <si>
@@ -1805,16 +1799,36 @@
   </si>
   <si>
     <t>(215) 990-2821</t>
+  </si>
+  <si>
+    <t>https://bucatinicaffe.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/bucatini-caffe-philadelphia</t>
+  </si>
+  <si>
+    <t>Italian, other</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://bucatinicaffe.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/bucatini-caffe-philadelphia</t>
-  </si>
-  <si>
-    <t>Italian, Pasta Shops</t>
+    <t>Cafes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>American</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desserts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vegan, Indian, other</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>other</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1879,12 +1893,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2193,7 +2204,7 @@
   <dimension ref="A1:AA95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="17" max="17" width="10.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
@@ -2245,7 +2256,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -2316,7 +2327,7 @@
       <c r="P2">
         <v>-75.165249199999991</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>45969</v>
       </c>
       <c r="R2" t="s">
@@ -2363,7 +2374,7 @@
       <c r="P3">
         <v>-75.21579659999999</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2401,7 +2412,7 @@
       <c r="P4">
         <v>-75.146249400000002</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -2445,7 +2456,7 @@
       <c r="P5">
         <v>-75.1282341</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>45987</v>
       </c>
       <c r="R5" t="s">
@@ -2498,7 +2509,7 @@
       <c r="P6">
         <v>-75.157455200000001</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>45987</v>
       </c>
       <c r="R6" t="s">
@@ -2545,7 +2556,7 @@
       <c r="P7">
         <v>-75.152562000000017</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>45987</v>
       </c>
       <c r="R7" t="s">
@@ -2589,7 +2600,7 @@
       <c r="P8">
         <v>-75.144038499999994</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>45987</v>
       </c>
       <c r="R8" t="s">
@@ -2630,7 +2641,7 @@
       <c r="P9">
         <v>-75.2233971</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2671,7 +2682,7 @@
       <c r="P10">
         <v>-75.2234981</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2712,7 +2723,7 @@
       <c r="P11">
         <v>-75.190426099999996</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2756,7 +2767,7 @@
       <c r="P12">
         <v>-75.159225399999997</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="2">
         <v>45985</v>
       </c>
     </row>
@@ -2797,7 +2808,7 @@
       <c r="P13">
         <v>-75.223862799999992</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2838,7 +2849,7 @@
       <c r="P14">
         <v>-75.160286099999993</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="2">
         <v>45987</v>
       </c>
       <c r="R14" t="s">
@@ -2876,7 +2887,7 @@
       <c r="P15">
         <v>-75.149054199999995</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2917,7 +2928,7 @@
       <c r="P16">
         <v>-75.084474200000002</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -2958,7 +2969,7 @@
       <c r="P17">
         <v>-75.069438599999998</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="2">
         <v>45987</v>
       </c>
       <c r="R17" t="s">
@@ -2999,7 +3010,7 @@
       <c r="P18">
         <v>-75.147503599999993</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -3043,7 +3054,7 @@
       <c r="P19">
         <v>-75.156541500000003</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="2">
         <v>45987</v>
       </c>
     </row>
@@ -3081,7 +3092,7 @@
       <c r="P20">
         <v>-75.1753073</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="2">
         <v>45969</v>
       </c>
       <c r="R20" t="s">
@@ -3125,7 +3136,7 @@
       <c r="P21">
         <v>-75.152359599999997</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3166,7 +3177,7 @@
       <c r="P22">
         <v>-75.179640800000001</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3201,7 +3212,7 @@
       <c r="P23">
         <v>-75.170259099999996</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="2">
         <v>45969</v>
       </c>
       <c r="R23" t="s">
@@ -3245,7 +3256,7 @@
       <c r="P24">
         <v>-75.144517199999996</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="2">
         <v>45969</v>
       </c>
       <c r="R24" t="s">
@@ -3289,7 +3300,7 @@
       <c r="P25">
         <v>-75.141018599999995</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="Q25" s="2">
         <v>45969</v>
       </c>
       <c r="R25" t="s">
@@ -3333,7 +3344,7 @@
       <c r="P26">
         <v>-75.161606300000003</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="2">
         <v>45969</v>
       </c>
       <c r="R26" t="s">
@@ -3371,7 +3382,7 @@
       <c r="P27">
         <v>-75.129705099999995</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="2">
         <v>45969</v>
       </c>
       <c r="R27" t="s">
@@ -3415,7 +3426,7 @@
       <c r="P28">
         <v>-75.164066699999992</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="Q28" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3456,7 +3467,7 @@
       <c r="P29">
         <v>-75.164232699999999</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3497,7 +3508,7 @@
       <c r="P30">
         <v>-75.144519399999993</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3538,7 +3549,7 @@
       <c r="P31">
         <v>-75.140985200000003</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="Q31" s="2">
         <v>45969</v>
       </c>
       <c r="R31" t="s">
@@ -3579,7 +3590,7 @@
       <c r="P32">
         <v>-75.180016899999998</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="2">
         <v>45969</v>
       </c>
       <c r="R32" t="s">
@@ -3623,7 +3634,7 @@
       <c r="P33">
         <v>-75.170737899999992</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3661,7 +3672,7 @@
       <c r="P34">
         <v>-75.160454999999999</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3702,7 +3713,7 @@
       <c r="P35">
         <v>-75.160108000000008</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3740,7 +3751,7 @@
       <c r="P36">
         <v>-75.134557399999991</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q36" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3778,7 +3789,7 @@
       <c r="P37">
         <v>-75.167785299999991</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q37" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3813,7 +3824,7 @@
       <c r="P38">
         <v>-75.171386099999992</v>
       </c>
-      <c r="Q38" s="3">
+      <c r="Q38" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3851,7 +3862,7 @@
       <c r="P39">
         <v>-75.171194099999994</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -3886,7 +3897,7 @@
       <c r="P40">
         <v>-75.152963700000001</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="2">
         <v>45969</v>
       </c>
       <c r="R40" t="s">
@@ -3927,7 +3938,7 @@
       <c r="P41">
         <v>-75.173786499999991</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="2">
         <v>45969</v>
       </c>
       <c r="R41" t="s">
@@ -3971,7 +3982,7 @@
       <c r="P42">
         <v>-75.157853799999998</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4009,7 +4020,7 @@
       <c r="P43">
         <v>-75.174123500000007</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="2">
         <v>45969</v>
       </c>
       <c r="R43" t="s">
@@ -4050,7 +4061,7 @@
       <c r="P44">
         <v>-75.161768199999997</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="2">
         <v>45969</v>
       </c>
       <c r="R44" t="s">
@@ -4097,7 +4108,7 @@
       <c r="P45">
         <v>-75.160984799999994</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4138,7 +4149,7 @@
       <c r="P46">
         <v>-75.170019699999997</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4179,7 +4190,7 @@
       <c r="P47">
         <v>-75.144386900000001</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="2">
         <v>45969</v>
       </c>
       <c r="R47" t="s">
@@ -4223,7 +4234,7 @@
       <c r="P48">
         <v>-75.156515900000002</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="2">
         <v>45969</v>
       </c>
       <c r="R48" t="s">
@@ -4267,7 +4278,7 @@
       <c r="P49">
         <v>-75.140709299999997</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="2">
         <v>45969</v>
       </c>
       <c r="R49" t="s">
@@ -4305,7 +4316,7 @@
       <c r="P50">
         <v>-75.175115599999998</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4346,7 +4357,7 @@
       <c r="P51">
         <v>-75.167463699999999</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4384,7 +4395,7 @@
       <c r="P52">
         <v>-75.171119699999991</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4425,7 +4436,7 @@
       <c r="P53">
         <v>-75.174716699999991</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53" s="2">
         <v>45969</v>
       </c>
       <c r="R53" t="s">
@@ -4469,7 +4480,7 @@
       <c r="P54">
         <v>-75.155556500000003</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4507,7 +4518,7 @@
       <c r="P55">
         <v>-75.185306799999992</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55" s="2">
         <v>45969</v>
       </c>
       <c r="R55" t="s">
@@ -4548,7 +4559,7 @@
       <c r="P56">
         <v>-75.177968399999997</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="2">
         <v>45969</v>
       </c>
       <c r="R56" t="s">
@@ -4592,7 +4603,7 @@
       <c r="P57">
         <v>-75.174830900000003</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4633,7 +4644,7 @@
       <c r="P58">
         <v>-75.217944799999998</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="2">
         <v>45969</v>
       </c>
     </row>
@@ -4671,7 +4682,7 @@
       <c r="P59">
         <v>-75.149544399999996</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4709,7 +4720,7 @@
       <c r="P60">
         <v>-75.050069499999992</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4744,7 +4755,7 @@
       <c r="P61">
         <v>-75.149088399999997</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="Q61" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4779,7 +4790,7 @@
       <c r="P62">
         <v>-75.156259599999998</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4820,7 +4831,7 @@
       <c r="P63">
         <v>-75.178519699999995</v>
       </c>
-      <c r="Q63" s="3">
+      <c r="Q63" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4858,7 +4869,7 @@
       <c r="P64">
         <v>-75.150354600000014</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="Q64" s="2">
         <v>45977</v>
       </c>
       <c r="R64" t="s">
@@ -4905,7 +4916,7 @@
       <c r="P65">
         <v>-75.034327399999995</v>
       </c>
-      <c r="Q65" s="3">
+      <c r="Q65" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4943,7 +4954,7 @@
       <c r="P66">
         <v>-75.171258600000002</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -4978,7 +4989,7 @@
       <c r="P67">
         <v>-75.173383200000004</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="Q67" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5019,7 +5030,7 @@
       <c r="P68">
         <v>-75.157960899999992</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="Q68" s="2">
         <v>45977</v>
       </c>
       <c r="R68" t="s">
@@ -5063,7 +5074,7 @@
       <c r="P69">
         <v>-75.153989299999992</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="Q69" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5101,7 +5112,7 @@
       <c r="P70">
         <v>-75.16970049999999</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q70" s="2">
         <v>45977</v>
       </c>
       <c r="R70" t="s">
@@ -5142,7 +5153,7 @@
       <c r="P71">
         <v>-75.169153299999991</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="Q71" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5180,7 +5191,7 @@
       <c r="P72">
         <v>-75.190036300000003</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="2">
         <v>45977</v>
       </c>
       <c r="R72" t="s">
@@ -5227,7 +5238,7 @@
       <c r="P73">
         <v>-75.163266499999992</v>
       </c>
-      <c r="Q73" s="3">
+      <c r="Q73" s="2">
         <v>45977</v>
       </c>
       <c r="R73" t="s">
@@ -5268,7 +5279,7 @@
       <c r="P74">
         <v>-75.157535600000003</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="Q74" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5309,7 +5320,7 @@
       <c r="P75">
         <v>-75.172149099999999</v>
       </c>
-      <c r="Q75" s="3">
+      <c r="Q75" s="2">
         <v>45977</v>
       </c>
       <c r="R75" t="s">
@@ -5353,7 +5364,7 @@
       <c r="P76">
         <v>-75.102839599999996</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="2">
         <v>45977</v>
       </c>
       <c r="R76" t="s">
@@ -5397,7 +5408,7 @@
       <c r="P77">
         <v>-75.146044199999992</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="Q77" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5438,7 +5449,7 @@
       <c r="P78">
         <v>-75.159783899999994</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="Q78" s="2">
         <v>45977</v>
       </c>
       <c r="R78" t="s">
@@ -5485,7 +5496,7 @@
       <c r="P79">
         <v>-75.113133699999992</v>
       </c>
-      <c r="Q79" s="3">
+      <c r="Q79" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5526,7 +5537,7 @@
       <c r="P80">
         <v>-75.147412399999993</v>
       </c>
-      <c r="Q80" s="3">
+      <c r="Q80" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5567,7 +5578,7 @@
       <c r="P81">
         <v>-75.174111199999999</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5608,7 +5619,7 @@
       <c r="P82">
         <v>-75.160342099999994</v>
       </c>
-      <c r="Q82" s="3">
+      <c r="Q82" s="2">
         <v>45977</v>
       </c>
     </row>
@@ -5652,7 +5663,7 @@
       <c r="P83">
         <v>-75.177395099999998</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="2">
         <v>45978</v>
       </c>
       <c r="R83" t="s">
@@ -5693,7 +5704,7 @@
       <c r="P84">
         <v>-75.182546800000011</v>
       </c>
-      <c r="Q84" s="3">
+      <c r="Q84" s="2">
         <v>45978</v>
       </c>
       <c r="R84" t="s">
@@ -5737,7 +5748,7 @@
       <c r="P85">
         <v>-75.129835499999999</v>
       </c>
-      <c r="Q85" s="3">
+      <c r="Q85" s="2">
         <v>45978</v>
       </c>
       <c r="R85" t="s">
@@ -5781,7 +5792,7 @@
       <c r="P86">
         <v>-75.160762800000001</v>
       </c>
-      <c r="Q86" s="3">
+      <c r="Q86" s="2">
         <v>45979</v>
       </c>
       <c r="R86" t="s">
@@ -5808,6 +5819,9 @@
         <v>550</v>
       </c>
       <c r="G87" t="s">
+        <v>600</v>
+      </c>
+      <c r="H87" t="s">
         <v>551</v>
       </c>
       <c r="I87" t="s">
@@ -5822,7 +5836,7 @@
       <c r="P87">
         <v>-75.319580799999997</v>
       </c>
-      <c r="Q87" s="3">
+      <c r="Q87" s="2">
         <v>45997</v>
       </c>
     </row>
@@ -5860,7 +5874,7 @@
       <c r="P88">
         <v>-75.199683899999997</v>
       </c>
-      <c r="Q88" s="3">
+      <c r="Q88" s="2">
         <v>45997</v>
       </c>
       <c r="R88" t="s">
@@ -5887,6 +5901,9 @@
         <v>563</v>
       </c>
       <c r="G89" t="s">
+        <v>600</v>
+      </c>
+      <c r="H89" t="s">
         <v>67</v>
       </c>
       <c r="I89" t="s">
@@ -5901,7 +5918,7 @@
       <c r="P89">
         <v>-75.1544861</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="2">
         <v>45997</v>
       </c>
     </row>
@@ -5925,6 +5942,9 @@
         <v>566</v>
       </c>
       <c r="G90" t="s">
+        <v>600</v>
+      </c>
+      <c r="H90" t="s">
         <v>67</v>
       </c>
       <c r="I90" t="s">
@@ -5939,7 +5959,7 @@
       <c r="P90">
         <v>-75.202095200000002</v>
       </c>
-      <c r="Q90" s="3">
+      <c r="Q90" s="2">
         <v>45997</v>
       </c>
     </row>
@@ -5974,7 +5994,7 @@
       <c r="P91">
         <v>-75.1558378</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="2">
         <v>45997</v>
       </c>
     </row>
@@ -5998,7 +6018,10 @@
         <v>575</v>
       </c>
       <c r="G92" t="s">
-        <v>576</v>
+        <v>599</v>
+      </c>
+      <c r="H92" t="s">
+        <v>598</v>
       </c>
       <c r="I92" t="s">
         <v>33</v>
@@ -6012,11 +6035,11 @@
       <c r="P92">
         <v>-75.1694289</v>
       </c>
-      <c r="Q92" s="3">
+      <c r="Q92" s="2">
         <v>45997</v>
       </c>
       <c r="R92" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
@@ -6024,22 +6047,25 @@
         <v>1792</v>
       </c>
       <c r="B93" t="s">
+        <v>577</v>
+      </c>
+      <c r="C93" t="s">
         <v>578</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>579</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>580</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>581</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>597</v>
+      </c>
+      <c r="H93" t="s">
         <v>582</v>
-      </c>
-      <c r="G93" t="s">
-        <v>583</v>
       </c>
       <c r="I93" t="s">
         <v>33</v>
@@ -6053,11 +6079,11 @@
       <c r="P93">
         <v>-75.134263699999991</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="Q93" s="2">
         <v>45997</v>
       </c>
       <c r="R93" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
@@ -6065,22 +6091,25 @@
         <v>1793</v>
       </c>
       <c r="B94" t="s">
+        <v>584</v>
+      </c>
+      <c r="C94" t="s">
         <v>585</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>586</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>587</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>588</v>
       </c>
-      <c r="F94" t="s">
-        <v>589</v>
-      </c>
       <c r="G94" t="s">
-        <v>590</v>
+        <v>595</v>
+      </c>
+      <c r="H94" t="s">
+        <v>596</v>
       </c>
       <c r="I94" t="s">
         <v>33</v>
@@ -6094,31 +6123,37 @@
       <c r="P94">
         <v>-75.146333400000003</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="2">
         <v>45997</v>
       </c>
       <c r="R94" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1794</v>
+      </c>
+      <c r="B95" t="s">
+        <v>590</v>
+      </c>
+      <c r="C95" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
+      <c r="D95" t="s">
         <v>592</v>
       </c>
-      <c r="C95" t="s">
+      <c r="E95" t="s">
         <v>593</v>
       </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
         <v>594</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>595</v>
       </c>
-      <c r="F95" t="s">
-        <v>596</v>
-      </c>
-      <c r="G95" t="s">
-        <v>597</v>
+      <c r="H95" t="s">
+        <v>186</v>
       </c>
       <c r="I95" t="s">
         <v>33</v>
@@ -6126,8 +6161,14 @@
       <c r="N95" t="s">
         <v>45</v>
       </c>
-      <c r="Q95" s="3">
-        <v>45997</v>
+      <c r="O95">
+        <v>39.927078799999997</v>
+      </c>
+      <c r="P95">
+        <v>-75.16715219999999</v>
+      </c>
+      <c r="Q95" s="2">
+        <v>45998</v>
       </c>
     </row>
   </sheetData>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C738C8BB-7814-4A29-9F94-0B16D77B3BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39A709D-C0B1-439F-9171-B8E0B7B36FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="594">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -80,27 +80,6 @@
   </si>
   <si>
     <t>Email_3</t>
-  </si>
-  <si>
-    <t>Email_4</t>
-  </si>
-  <si>
-    <t>Email_5</t>
-  </si>
-  <si>
-    <t>Email_6</t>
-  </si>
-  <si>
-    <t>Email_7</t>
-  </si>
-  <si>
-    <t>Email_8</t>
-  </si>
-  <si>
-    <t>Email_9</t>
-  </si>
-  <si>
-    <t>Email_10</t>
   </si>
   <si>
     <t>Burrata</t>
@@ -2201,13 +2180,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA95"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,58 +2247,37 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1374</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
       </c>
       <c r="O2">
         <v>39.933934299999997</v>
@@ -2331,42 +2289,42 @@
         <v>45969</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1376</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O3">
         <v>40.033780200000002</v>
@@ -2378,33 +2336,33 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1377</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O4">
         <v>39.941107500000001</v>
@@ -2416,39 +2374,39 @@
         <v>45969</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1383</v>
       </c>
       <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
         <v>52</v>
       </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" t="s">
-        <v>59</v>
-      </c>
       <c r="N5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O5">
         <v>39.988109899999998</v>
@@ -2460,48 +2418,48 @@
         <v>45987</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1387</v>
       </c>
       <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
         <v>61</v>
       </c>
-      <c r="C6" t="s">
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
         <v>62</v>
       </c>
-      <c r="D6" t="s">
+      <c r="N6" t="s">
         <v>63</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" t="s">
-        <v>70</v>
       </c>
       <c r="O6">
         <v>39.953542300000002</v>
@@ -2513,42 +2471,42 @@
         <v>45987</v>
       </c>
       <c r="R6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="S6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1388</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O7">
         <v>39.949672</v>
@@ -2560,39 +2518,39 @@
         <v>45987</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1389</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O8">
         <v>39.969888599999997</v>
@@ -2604,36 +2562,36 @@
         <v>45987</v>
       </c>
       <c r="R8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1398</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O9">
         <v>40.025693400000002</v>
@@ -2645,36 +2603,36 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1399</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="N10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O10">
         <v>40.025600900000001</v>
@@ -2686,36 +2644,36 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1401</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O11">
         <v>40.009791999999997</v>
@@ -2727,39 +2685,39 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1402</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O12">
         <v>39.939035199999999</v>
@@ -2771,36 +2729,36 @@
         <v>45985</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1404</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O13">
         <v>40.025373700000003</v>
@@ -2812,36 +2770,36 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1407</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F14" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="N14" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O14">
         <v>39.9346672</v>
@@ -2853,33 +2811,33 @@
         <v>45987</v>
       </c>
       <c r="R14" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1408</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G15" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N15" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="O15">
         <v>39.941414799999997</v>
@@ -2891,36 +2849,36 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1409</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O16">
         <v>39.910713899999998</v>
@@ -2937,31 +2895,31 @@
         <v>1410</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G17" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O17">
         <v>39.916215800000003</v>
@@ -2973,7 +2931,7 @@
         <v>45987</v>
       </c>
       <c r="R17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -2981,28 +2939,28 @@
         <v>1412</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="N18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="O18">
         <v>39.940898199999999</v>
@@ -3019,34 +2977,34 @@
         <v>1417</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K19" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O19">
         <v>39.954462199999988</v>
@@ -3063,28 +3021,28 @@
         <v>1555</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O20">
         <v>39.967158499999996</v>
@@ -3096,7 +3054,7 @@
         <v>45969</v>
       </c>
       <c r="R20" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -3104,31 +3062,31 @@
         <v>1556</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F21" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O21">
         <v>39.938799099999997</v>
@@ -3145,31 +3103,31 @@
         <v>1557</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C22" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F22" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H22" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O22">
         <v>39.950006500000001</v>
@@ -3186,25 +3144,25 @@
         <v>1558</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E23" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O23">
         <v>39.945162000000003</v>
@@ -3216,7 +3174,7 @@
         <v>45969</v>
       </c>
       <c r="R23" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -3224,31 +3182,31 @@
         <v>1559</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F24" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O24">
         <v>39.937890799999998</v>
@@ -3260,7 +3218,7 @@
         <v>45969</v>
       </c>
       <c r="R24" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -3268,31 +3226,31 @@
         <v>1560</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D25" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F25" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O25">
         <v>39.972437200000002</v>
@@ -3304,10 +3262,10 @@
         <v>45969</v>
       </c>
       <c r="R25" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="S25" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -3315,28 +3273,28 @@
         <v>1561</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G26" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O26">
         <v>39.930126299999998</v>
@@ -3348,7 +3306,7 @@
         <v>45969</v>
       </c>
       <c r="R26" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -3356,25 +3314,25 @@
         <v>1562</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E27" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F27" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O27">
         <v>39.970733099999997</v>
@@ -3386,7 +3344,7 @@
         <v>45969</v>
       </c>
       <c r="R27" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -3394,31 +3352,31 @@
         <v>1563</v>
       </c>
       <c r="B28" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D28" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E28" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G28" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O28">
         <v>39.945286199999998</v>
@@ -3435,31 +3393,31 @@
         <v>1564</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D29" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E29" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F29" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O29">
         <v>39.945343899999997</v>
@@ -3476,31 +3434,31 @@
         <v>1565</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E30" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F30" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O30">
         <v>39.971564299999997</v>
@@ -3517,31 +3475,31 @@
         <v>1566</v>
       </c>
       <c r="B31" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D31" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E31" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F31" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O31">
         <v>39.967347200000013</v>
@@ -3553,7 +3511,7 @@
         <v>45969</v>
       </c>
       <c r="R31" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -3561,28 +3519,28 @@
         <v>1567</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E32" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F32" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G32" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N32" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O32">
         <v>39.944823399999997</v>
@@ -3594,7 +3552,7 @@
         <v>45969</v>
       </c>
       <c r="R32" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -3602,31 +3560,31 @@
         <v>1568</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C33" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D33" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E33" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F33" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G33" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H33" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O33">
         <v>39.944419500000002</v>
@@ -3643,28 +3601,28 @@
         <v>1569</v>
       </c>
       <c r="B34" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C34" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D34" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F34" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G34" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H34" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O34">
         <v>39.949910799999998</v>
@@ -3681,31 +3639,31 @@
         <v>1570</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D35" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E35" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F35" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O35">
         <v>39.947785699999997</v>
@@ -3722,28 +3680,28 @@
         <v>1571</v>
       </c>
       <c r="B36" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C36" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E36" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O36">
         <v>39.9681268</v>
@@ -3760,28 +3718,28 @@
         <v>1573</v>
       </c>
       <c r="B37" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D37" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E37" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F37" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O37">
         <v>39.947794299999998</v>
@@ -3798,25 +3756,25 @@
         <v>1574</v>
       </c>
       <c r="B38" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C38" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D38" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F38" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O38">
         <v>39.919627800000001</v>
@@ -3833,28 +3791,28 @@
         <v>1575</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D39" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E39" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F39" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O39">
         <v>39.939477599999996</v>
@@ -3871,25 +3829,25 @@
         <v>1576</v>
       </c>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D40" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E40" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G40" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O40">
         <v>39.939990700000003</v>
@@ -3901,7 +3859,7 @@
         <v>45969</v>
       </c>
       <c r="R40" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -3909,28 +3867,28 @@
         <v>1577</v>
       </c>
       <c r="B41" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E41" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F41" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O41">
         <v>39.949691500000007</v>
@@ -3942,10 +3900,10 @@
         <v>45969</v>
       </c>
       <c r="R41" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="S41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -3953,28 +3911,28 @@
         <v>1578</v>
       </c>
       <c r="B42" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C42" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E42" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F42" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="G42" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H42" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O42">
         <v>39.9399765</v>
@@ -3991,28 +3949,28 @@
         <v>1579</v>
       </c>
       <c r="B43" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C43" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E43" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F43" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O43">
         <v>39.951250900000012</v>
@@ -4024,7 +3982,7 @@
         <v>45969</v>
       </c>
       <c r="R43" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -4032,28 +3990,28 @@
         <v>1580</v>
       </c>
       <c r="B44" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C44" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F44" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O44">
         <v>39.946499199999998</v>
@@ -4065,10 +4023,10 @@
         <v>45969</v>
       </c>
       <c r="R44" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="S44" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -4076,31 +4034,31 @@
         <v>1581</v>
       </c>
       <c r="B45" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D45" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="E45" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F45" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G45" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H45" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O45">
         <v>39.953597799999997</v>
@@ -4117,31 +4075,31 @@
         <v>1582</v>
       </c>
       <c r="B46" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C46" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="G46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O46">
         <v>39.944041200000001</v>
@@ -4158,31 +4116,31 @@
         <v>1583</v>
       </c>
       <c r="B47" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C47" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E47" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F47" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O47">
         <v>39.951949399999997</v>
@@ -4194,7 +4152,7 @@
         <v>45969</v>
       </c>
       <c r="R47" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -4202,31 +4160,31 @@
         <v>1584</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C48" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D48" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E48" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F48" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="G48" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H48" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O48">
         <v>39.936869300000012</v>
@@ -4238,7 +4196,7 @@
         <v>45969</v>
       </c>
       <c r="R48" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -4246,31 +4204,31 @@
         <v>1585</v>
       </c>
       <c r="B49" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C49" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D49" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E49" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F49" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G49" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H49" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N49" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O49">
         <v>39.965340099999999</v>
@@ -4282,7 +4240,7 @@
         <v>45969</v>
       </c>
       <c r="R49" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -4290,25 +4248,25 @@
         <v>1586</v>
       </c>
       <c r="B50" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C50" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D50" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F50" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N50" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O50">
         <v>39.951353500000003</v>
@@ -4325,31 +4283,31 @@
         <v>1587</v>
       </c>
       <c r="B51" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C51" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D51" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E51" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F51" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G51" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H51" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O51">
         <v>39.926275500000003</v>
@@ -4366,28 +4324,28 @@
         <v>1588</v>
       </c>
       <c r="B52" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C52" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D52" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E52" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F52" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I52" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O52">
         <v>39.919344799999998</v>
@@ -4404,31 +4362,31 @@
         <v>1589</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C53" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D53" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E53" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="F53" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="G53" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O53">
         <v>39.925220400000001</v>
@@ -4440,7 +4398,7 @@
         <v>45969</v>
       </c>
       <c r="R53" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -4448,31 +4406,31 @@
         <v>1590</v>
       </c>
       <c r="B54" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C54" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D54" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E54" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F54" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G54" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H54" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="I54" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O54">
         <v>39.9339212</v>
@@ -4489,28 +4447,28 @@
         <v>1591</v>
       </c>
       <c r="B55" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C55" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D55" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E55" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F55" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="G55" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N55" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O55">
         <v>39.942576899999999</v>
@@ -4522,7 +4480,7 @@
         <v>45969</v>
       </c>
       <c r="R55" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
@@ -4530,28 +4488,28 @@
         <v>1592</v>
       </c>
       <c r="B56" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C56" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D56" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E56" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F56" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N56" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O56">
         <v>39.948765399999999</v>
@@ -4563,7 +4521,7 @@
         <v>45969</v>
       </c>
       <c r="R56" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
@@ -4571,31 +4529,31 @@
         <v>1593</v>
       </c>
       <c r="B57" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C57" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D57" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E57" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="F57" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G57" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N57" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O57">
         <v>39.9515782</v>
@@ -4612,31 +4570,31 @@
         <v>1594</v>
       </c>
       <c r="B58" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C58" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D58" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E58" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="F58" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G58" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N58" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O58">
         <v>39.948388199999997</v>
@@ -4653,28 +4611,28 @@
         <v>1726</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C59" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D59" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="E59" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F59" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G59" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I59" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N59" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O59">
         <v>39.931907000000002</v>
@@ -4691,28 +4649,28 @@
         <v>1727</v>
       </c>
       <c r="B60" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C60" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D60" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="F60" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H60" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I60" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O60">
         <v>39.910426600000001</v>
@@ -4729,25 +4687,25 @@
         <v>1729</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D61" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F61" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G61" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I61" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O61">
         <v>39.941114900000002</v>
@@ -4764,25 +4722,25 @@
         <v>1730</v>
       </c>
       <c r="B62" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C62" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D62" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F62" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G62" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I62" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N62" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O62">
         <v>39.939704499999998</v>
@@ -4799,31 +4757,31 @@
         <v>1731</v>
       </c>
       <c r="B63" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C63" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D63" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E63" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="F63" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="G63" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="I63" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O63">
         <v>39.968518099999997</v>
@@ -4840,28 +4798,28 @@
         <v>1732</v>
       </c>
       <c r="B64" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C64" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D64" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E64" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F64" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="G64" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I64" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N64" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O64">
         <v>39.9413883</v>
@@ -4873,10 +4831,10 @@
         <v>45977</v>
       </c>
       <c r="R64" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="S64" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.3">
@@ -4884,31 +4842,31 @@
         <v>1733</v>
       </c>
       <c r="B65" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C65" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D65" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E65" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="F65" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G65" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I65" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N65" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O65">
         <v>40.1219337</v>
@@ -4925,28 +4883,28 @@
         <v>1734</v>
       </c>
       <c r="B66" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C66" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D66" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F66" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="G66" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H66" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N66" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O66">
         <v>39.928446399999999</v>
@@ -4963,25 +4921,25 @@
         <v>1735</v>
       </c>
       <c r="B67" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C67" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F67" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="G67" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H67" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I67" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N67" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O67">
         <v>39.919901199999998</v>
@@ -4998,31 +4956,31 @@
         <v>1736</v>
       </c>
       <c r="B68" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C68" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D68" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E68" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F68" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="I68" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O68">
         <v>39.9463188</v>
@@ -5034,10 +4992,10 @@
         <v>45977</v>
       </c>
       <c r="R68" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="S68" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
@@ -5045,28 +5003,28 @@
         <v>1737</v>
       </c>
       <c r="B69" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C69" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D69" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E69" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F69" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G69" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="I69" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O69">
         <v>39.918631400000002</v>
@@ -5083,28 +5041,28 @@
         <v>1738</v>
       </c>
       <c r="B70" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C70" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D70" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="E70" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F70" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I70" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O70">
         <v>39.947769000000001</v>
@@ -5116,7 +5074,7 @@
         <v>45977</v>
       </c>
       <c r="R70" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.3">
@@ -5124,28 +5082,28 @@
         <v>1739</v>
       </c>
       <c r="B71" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C71" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D71" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F71" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="G71" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H71" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I71" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N71" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O71">
         <v>39.943967499999999</v>
@@ -5162,28 +5120,28 @@
         <v>1740</v>
       </c>
       <c r="B72" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C72" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D72" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="E72" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F72" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G72" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I72" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N72" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O72">
         <v>40.059318500000003</v>
@@ -5195,13 +5153,13 @@
         <v>45977</v>
       </c>
       <c r="R72" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="S72" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="T72" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.3">
@@ -5209,28 +5167,28 @@
         <v>1741</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="C73" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="D73" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E73" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="F73" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G73" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="I73" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N73" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O73">
         <v>39.921155900000002</v>
@@ -5242,7 +5200,7 @@
         <v>45977</v>
       </c>
       <c r="R73" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.3">
@@ -5250,28 +5208,28 @@
         <v>1742</v>
       </c>
       <c r="B74" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C74" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D74" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E74" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F74" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G74" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="I74" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N74" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O74">
         <v>39.926405699999997</v>
@@ -5288,31 +5246,31 @@
         <v>1743</v>
       </c>
       <c r="B75" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C75" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D75" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="E75" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F75" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G75" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H75" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I75" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N75" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O75">
         <v>39.952112100000001</v>
@@ -5324,7 +5282,7 @@
         <v>45977</v>
       </c>
       <c r="R75" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
@@ -5332,31 +5290,31 @@
         <v>1744</v>
       </c>
       <c r="B76" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C76" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D76" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E76" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F76" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="G76" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H76" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I76" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N76" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O76">
         <v>39.982485199999999</v>
@@ -5368,7 +5326,7 @@
         <v>45977</v>
       </c>
       <c r="R76" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
@@ -5376,31 +5334,31 @@
         <v>1745</v>
       </c>
       <c r="B77" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C77" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D77" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E77" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F77" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G77" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H77" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I77" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N77" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O77">
         <v>39.940707699999997</v>
@@ -5417,31 +5375,31 @@
         <v>1746</v>
       </c>
       <c r="B78" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C78" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="D78" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="E78" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="F78" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="G78" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H78" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="I78" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N78" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O78">
         <v>39.938333399999998</v>
@@ -5453,10 +5411,10 @@
         <v>45977</v>
       </c>
       <c r="R78" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="S78" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
@@ -5464,31 +5422,31 @@
         <v>1747</v>
       </c>
       <c r="B79" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C79" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D79" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="E79" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F79" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G79" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H79" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I79" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O79">
         <v>39.9803949</v>
@@ -5505,31 +5463,31 @@
         <v>1748</v>
       </c>
       <c r="B80" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C80" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D80" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E80" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F80" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G80" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H80" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="I80" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N80" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O80">
         <v>39.926336599999999</v>
@@ -5546,31 +5504,31 @@
         <v>1749</v>
       </c>
       <c r="B81" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C81" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D81" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E81" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F81" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="G81" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H81" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I81" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N81" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O81">
         <v>39.964689399999997</v>
@@ -5587,31 +5545,31 @@
         <v>1750</v>
       </c>
       <c r="B82" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C82" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="D82" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="E82" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="F82" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="G82" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H82" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="I82" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N82" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O82">
         <v>39.947806000000007</v>
@@ -5628,34 +5586,34 @@
         <v>1754</v>
       </c>
       <c r="B83" t="s">
+        <v>511</v>
+      </c>
+      <c r="C83" t="s">
+        <v>512</v>
+      </c>
+      <c r="D83" t="s">
+        <v>513</v>
+      </c>
+      <c r="E83" t="s">
+        <v>514</v>
+      </c>
+      <c r="F83" t="s">
+        <v>515</v>
+      </c>
+      <c r="G83" t="s">
+        <v>516</v>
+      </c>
+      <c r="H83" t="s">
+        <v>517</v>
+      </c>
+      <c r="I83" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83" t="s">
         <v>518</v>
       </c>
-      <c r="C83" t="s">
-        <v>519</v>
-      </c>
-      <c r="D83" t="s">
-        <v>520</v>
-      </c>
-      <c r="E83" t="s">
-        <v>521</v>
-      </c>
-      <c r="F83" t="s">
-        <v>522</v>
-      </c>
-      <c r="G83" t="s">
-        <v>523</v>
-      </c>
-      <c r="H83" t="s">
-        <v>524</v>
-      </c>
-      <c r="I83" t="s">
-        <v>43</v>
-      </c>
-      <c r="K83" t="s">
-        <v>525</v>
-      </c>
       <c r="N83" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O83">
         <v>39.944972700000001</v>
@@ -5667,7 +5625,7 @@
         <v>45978</v>
       </c>
       <c r="R83" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
@@ -5675,28 +5633,28 @@
         <v>1755</v>
       </c>
       <c r="B84" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C84" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E84" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="F84" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="G84" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="I84" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N84" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O84">
         <v>39.974236699999999</v>
@@ -5708,7 +5666,7 @@
         <v>45978</v>
       </c>
       <c r="R84" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
@@ -5716,31 +5674,31 @@
         <v>1756</v>
       </c>
       <c r="B85" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C85" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D85" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E85" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="F85" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="G85" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H85" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="I85" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O85">
         <v>39.9798258</v>
@@ -5752,7 +5710,7 @@
         <v>45978</v>
       </c>
       <c r="R85" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
@@ -5760,31 +5718,31 @@
         <v>1757</v>
       </c>
       <c r="B86" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="C86" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D86" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="E86" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F86" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G86" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="H86" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I86" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N86" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O86">
         <v>39.944876200000003</v>
@@ -5796,7 +5754,7 @@
         <v>45979</v>
       </c>
       <c r="R86" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
@@ -5804,31 +5762,31 @@
         <v>1786</v>
       </c>
       <c r="B87" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="C87" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="D87" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E87" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="F87" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G87" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H87" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="I87" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N87" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O87">
         <v>40.022318299999988</v>
@@ -5845,28 +5803,28 @@
         <v>1787</v>
       </c>
       <c r="B88" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C88" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D88" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E88" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="F88" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="G88" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="I88" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N88" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O88">
         <v>39.954628999999997</v>
@@ -5878,7 +5836,7 @@
         <v>45997</v>
       </c>
       <c r="R88" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
@@ -5886,31 +5844,31 @@
         <v>1788</v>
       </c>
       <c r="B89" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C89" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="D89" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="E89" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="G89" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H89" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I89" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N89" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O89">
         <v>39.955408599999998</v>
@@ -5927,31 +5885,31 @@
         <v>1789</v>
       </c>
       <c r="B90" t="s">
+        <v>552</v>
+      </c>
+      <c r="C90" t="s">
+        <v>557</v>
+      </c>
+      <c r="D90" t="s">
+        <v>558</v>
+      </c>
+      <c r="E90" t="s">
+        <v>555</v>
+      </c>
+      <c r="F90" t="s">
         <v>559</v>
       </c>
-      <c r="C90" t="s">
-        <v>564</v>
-      </c>
-      <c r="D90" t="s">
-        <v>565</v>
-      </c>
-      <c r="E90" t="s">
-        <v>562</v>
-      </c>
-      <c r="F90" t="s">
-        <v>566</v>
-      </c>
       <c r="G90" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H90" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I90" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O90">
         <v>39.954715299999997</v>
@@ -5968,25 +5926,25 @@
         <v>1790</v>
       </c>
       <c r="B91" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C91" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D91" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="F91" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="G91" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I91" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N91" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O91">
         <v>39.953813599999997</v>
@@ -6003,31 +5961,31 @@
         <v>1791</v>
       </c>
       <c r="B92" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C92" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="D92" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="E92" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="F92" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="G92" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="H92" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="I92" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N92" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O92">
         <v>39.967475999999998</v>
@@ -6039,7 +5997,7 @@
         <v>45997</v>
       </c>
       <c r="R92" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
@@ -6047,31 +6005,31 @@
         <v>1792</v>
       </c>
       <c r="B93" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="C93" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="D93" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="E93" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="F93" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="G93" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="H93" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="I93" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N93" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O93">
         <v>39.966393500000002</v>
@@ -6083,7 +6041,7 @@
         <v>45997</v>
       </c>
       <c r="R93" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
@@ -6091,31 +6049,31 @@
         <v>1793</v>
       </c>
       <c r="B94" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C94" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="D94" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E94" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="F94" t="s">
+        <v>581</v>
+      </c>
+      <c r="G94" t="s">
         <v>588</v>
       </c>
-      <c r="G94" t="s">
-        <v>595</v>
-      </c>
       <c r="H94" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="I94" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N94" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O94">
         <v>39.956620099999988</v>
@@ -6127,7 +6085,7 @@
         <v>45997</v>
       </c>
       <c r="R94" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
@@ -6135,31 +6093,31 @@
         <v>1794</v>
       </c>
       <c r="B95" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C95" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="D95" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="E95" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="F95" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G95" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="H95" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="I95" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N95" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O95">
         <v>39.927078799999997</v>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39A709D-C0B1-439F-9171-B8E0B7B36FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24138D43-E156-43CE-8F23-A4ACD57D954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="618">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>Tibetan</t>
-  </si>
-  <si>
-    <t>: -- 請選擇 --</t>
   </si>
   <si>
     <t>La Nonna</t>
@@ -1808,6 +1805,81 @@
   <si>
     <t>other</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cover_image_url</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-3.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_georgian_byob_khachapuri-1.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-1.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_thai_byob_assorteddishes.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_chinese_byob_hotpot.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_georgian_byob_khachapuri-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_fishplate.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-chef-preparing-sushi-logo.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-carbonara-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-japanese-ramen-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_meze.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_french_byob_finedining-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/italian-restaurant-logo-placeholder-3.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-1.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_japanese_byob_sushibar-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_seafood_byob-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-official-logo-coming-soon.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-2.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_japanese_byob_sushibar-1.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-indian-curry-naan-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
+    <t>https://example.com/placeholder/vegan-1.webp</t>
+  </si>
+  <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/byob-steak-medium-rare.webp</t>
   </si>
 </sst>
 </file>
@@ -1872,12 +1944,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2180,13 +2255,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="18" max="18" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2194,3938 +2270,3983 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1374</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>39.933934299999997</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>-75.165249199999991</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="R2" s="2">
         <v>45969</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>29</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1376</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3">
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3">
         <v>40.033780200000002</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>-75.21579659999999</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1377</v>
       </c>
       <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>41</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
         <v>43</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4">
+      <c r="P4">
         <v>39.941107500000001</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>-75.146249400000002</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1383</v>
       </c>
       <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>49</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>50</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>51</v>
       </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5">
+        <v>39.988109899999998</v>
+      </c>
+      <c r="Q5">
+        <v>-75.1282341</v>
+      </c>
+      <c r="R5" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S5" t="s">
         <v>52</v>
       </c>
-      <c r="N5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5">
-        <v>39.988109899999998</v>
-      </c>
-      <c r="P5">
-        <v>-75.1282341</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1387</v>
       </c>
       <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D6" t="s">
         <v>54</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>55</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>56</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>57</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>58</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>59</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
         <v>60</v>
       </c>
-      <c r="I6" t="s">
+      <c r="M6" t="s">
         <v>36</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>61</v>
       </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>62</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6">
+        <v>39.953542300000002</v>
+      </c>
+      <c r="Q6">
+        <v>-75.157455200000001</v>
+      </c>
+      <c r="R6" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S6" t="s">
         <v>63</v>
       </c>
-      <c r="O6">
-        <v>39.953542300000002</v>
-      </c>
-      <c r="P6">
-        <v>-75.157455200000001</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="T6" t="s">
         <v>64</v>
       </c>
-      <c r="S6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1388</v>
       </c>
       <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D7" t="s">
         <v>66</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>69</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
         <v>70</v>
       </c>
-      <c r="G7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7">
+        <v>39.949672</v>
+      </c>
+      <c r="Q7">
+        <v>-75.152562000000017</v>
+      </c>
+      <c r="R7" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S7" t="s">
         <v>71</v>
       </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7">
-        <v>39.949672</v>
-      </c>
-      <c r="P7">
-        <v>-75.152562000000017</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1389</v>
       </c>
       <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D8" t="s">
         <v>73</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>75</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>77</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>78</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8">
+        <v>39.969888599999997</v>
+      </c>
+      <c r="Q8">
+        <v>-75.144038499999994</v>
+      </c>
+      <c r="R8" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S8" t="s">
         <v>79</v>
       </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8">
-        <v>39.969888599999997</v>
-      </c>
-      <c r="P8">
-        <v>-75.144038499999994</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1398</v>
       </c>
       <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D9" t="s">
         <v>81</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>83</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>84</v>
       </c>
-      <c r="G9" t="s">
+      <c r="J9" t="s">
         <v>85</v>
       </c>
-      <c r="I9" t="s">
+      <c r="M9" t="s">
         <v>86</v>
       </c>
-      <c r="L9" t="s">
-        <v>87</v>
-      </c>
-      <c r="N9" t="s">
-        <v>44</v>
-      </c>
-      <c r="O9">
+      <c r="O9" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9">
         <v>40.025693400000002</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>-75.2233971</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1399</v>
       </c>
       <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D10" t="s">
         <v>88</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>89</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>90</v>
       </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>91</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>92</v>
       </c>
-      <c r="H10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M10" t="s">
         <v>86</v>
       </c>
-      <c r="L10" t="s">
-        <v>87</v>
-      </c>
-      <c r="N10" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10">
+      <c r="O10" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10">
         <v>40.025600900000001</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>-75.2234981</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1401</v>
       </c>
       <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" t="s">
         <v>94</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>95</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>96</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>97</v>
       </c>
-      <c r="F11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>25</v>
       </c>
-      <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11" t="s">
-        <v>44</v>
-      </c>
-      <c r="O11">
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11">
         <v>40.009791999999997</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>-75.190426099999996</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1402</v>
       </c>
       <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D12" t="s">
         <v>99</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>100</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>101</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>102</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>103</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>104</v>
       </c>
-      <c r="H12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12">
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12">
+      <c r="P12">
         <v>39.939035199999999</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>-75.159225399999997</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <v>45985</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1404</v>
       </c>
       <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D13" t="s">
         <v>106</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>107</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>108</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>109</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>110</v>
       </c>
-      <c r="G13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" t="s">
-        <v>52</v>
-      </c>
-      <c r="N13" t="s">
-        <v>44</v>
-      </c>
-      <c r="O13">
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13">
         <v>40.025373700000003</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>-75.223862799999992</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1407</v>
       </c>
       <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D14" t="s">
         <v>112</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>113</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>114</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>115</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>116</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
         <v>117</v>
       </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="O14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14">
+        <v>39.9346672</v>
+      </c>
+      <c r="Q14">
+        <v>-75.160286099999993</v>
+      </c>
+      <c r="R14" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S14" t="s">
         <v>118</v>
       </c>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14">
-        <v>39.9346672</v>
-      </c>
-      <c r="P14">
-        <v>-75.160286099999993</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1408</v>
       </c>
       <c r="B15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D15" t="s">
         <v>120</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>121</v>
       </c>
-      <c r="D15" t="s">
+      <c r="H15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
         <v>122</v>
       </c>
-      <c r="G15" t="s">
-        <v>117</v>
-      </c>
-      <c r="I15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>123</v>
-      </c>
-      <c r="N15" t="s">
-        <v>63</v>
-      </c>
-      <c r="O15">
+      <c r="O15" t="s">
+        <v>62</v>
+      </c>
+      <c r="P15">
         <v>39.941414799999997</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>-75.149054199999995</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1409</v>
       </c>
       <c r="B16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D16" t="s">
         <v>124</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>125</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>126</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>127</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>128</v>
       </c>
-      <c r="G16" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
         <v>27</v>
       </c>
-      <c r="N16" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16">
+      <c r="O16" t="s">
+        <v>43</v>
+      </c>
+      <c r="P16">
         <v>39.910713899999998</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>-75.084474200000002</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1410</v>
       </c>
       <c r="B17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D17" t="s">
         <v>130</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>131</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>132</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>133</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>134</v>
       </c>
-      <c r="G17" t="s">
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17">
+        <v>39.916215800000003</v>
+      </c>
+      <c r="Q17">
+        <v>-75.069438599999998</v>
+      </c>
+      <c r="R17" s="2">
+        <v>45987</v>
+      </c>
+      <c r="S17" t="s">
         <v>135</v>
       </c>
-      <c r="I17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" t="s">
-        <v>44</v>
-      </c>
-      <c r="O17">
-        <v>39.916215800000003</v>
-      </c>
-      <c r="P17">
-        <v>-75.069438599999998</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>45987</v>
-      </c>
-      <c r="R17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1412</v>
       </c>
       <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D18" t="s">
         <v>137</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>138</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>139</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
         <v>140</v>
       </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="O18" t="s">
         <v>141</v>
       </c>
-      <c r="N18" t="s">
-        <v>142</v>
-      </c>
-      <c r="O18">
+      <c r="P18">
         <v>39.940898199999999</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>-75.147503599999993</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1417</v>
       </c>
       <c r="B19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D19" t="s">
         <v>143</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>144</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>145</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" t="s">
         <v>146</v>
       </c>
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" t="s">
         <v>147</v>
       </c>
-      <c r="I19" t="s">
-        <v>36</v>
-      </c>
-      <c r="K19" t="s">
-        <v>148</v>
-      </c>
-      <c r="L19" t="s">
-        <v>123</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="M19" t="s">
+        <v>122</v>
+      </c>
+      <c r="O19" t="s">
         <v>28</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>39.954462199999988</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>-75.156541500000003</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1555</v>
       </c>
       <c r="B20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D20" t="s">
         <v>149</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>150</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>151</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>152</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20">
+        <v>39.967158499999996</v>
+      </c>
+      <c r="Q20">
+        <v>-75.1753073</v>
+      </c>
+      <c r="R20" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S20" t="s">
         <v>153</v>
       </c>
-      <c r="G20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" t="s">
-        <v>38</v>
-      </c>
-      <c r="O20">
-        <v>39.967158499999996</v>
-      </c>
-      <c r="P20">
-        <v>-75.1753073</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R20" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1556</v>
       </c>
       <c r="B21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D21" t="s">
         <v>155</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>156</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>157</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>158</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" t="s">
         <v>159</v>
       </c>
-      <c r="G21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21">
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21">
         <v>39.938799099999997</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>-75.152359599999997</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1557</v>
       </c>
       <c r="B22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D22" t="s">
         <v>161</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>162</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>163</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>164</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" t="s">
         <v>165</v>
       </c>
-      <c r="G22" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>38</v>
-      </c>
-      <c r="O22">
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22">
         <v>39.950006500000001</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>-75.179640800000001</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="R22" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1558</v>
       </c>
       <c r="B23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" t="s">
         <v>167</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>168</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>169</v>
       </c>
-      <c r="E23" t="s">
+      <c r="H23" t="s">
         <v>170</v>
       </c>
-      <c r="G23" t="s">
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23">
+        <v>39.945162000000003</v>
+      </c>
+      <c r="Q23">
+        <v>-75.170259099999996</v>
+      </c>
+      <c r="R23" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S23" t="s">
         <v>171</v>
       </c>
-      <c r="I23" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" t="s">
-        <v>38</v>
-      </c>
-      <c r="O23">
-        <v>39.945162000000003</v>
-      </c>
-      <c r="P23">
-        <v>-75.170259099999996</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1559</v>
       </c>
       <c r="B24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D24" t="s">
         <v>173</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>174</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>175</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>176</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>177</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>178</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24">
+        <v>39.937890799999998</v>
+      </c>
+      <c r="Q24">
+        <v>-75.144517199999996</v>
+      </c>
+      <c r="R24" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S24" t="s">
         <v>179</v>
       </c>
-      <c r="I24" t="s">
-        <v>26</v>
-      </c>
-      <c r="N24" t="s">
-        <v>38</v>
-      </c>
-      <c r="O24">
-        <v>39.937890799999998</v>
-      </c>
-      <c r="P24">
-        <v>-75.144517199999996</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1560</v>
       </c>
       <c r="B25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D25" t="s">
         <v>181</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>182</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>183</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>184</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" t="s">
         <v>185</v>
       </c>
-      <c r="G25" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25">
+        <v>39.972437200000002</v>
+      </c>
+      <c r="Q25">
+        <v>-75.141018599999995</v>
+      </c>
+      <c r="R25" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S25" t="s">
         <v>186</v>
       </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" t="s">
-        <v>38</v>
-      </c>
-      <c r="O25">
-        <v>39.972437200000002</v>
-      </c>
-      <c r="P25">
-        <v>-75.141018599999995</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R25" t="s">
+      <c r="T25" t="s">
         <v>187</v>
       </c>
-      <c r="S25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1561</v>
       </c>
       <c r="B26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D26" t="s">
         <v>189</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>190</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>191</v>
       </c>
-      <c r="E26" t="s">
+      <c r="H26" t="s">
         <v>192</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>193</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26">
+        <v>39.930126299999998</v>
+      </c>
+      <c r="Q26">
+        <v>-75.161606300000003</v>
+      </c>
+      <c r="R26" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S26" t="s">
         <v>194</v>
       </c>
-      <c r="I26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" t="s">
-        <v>38</v>
-      </c>
-      <c r="O26">
-        <v>39.930126299999998</v>
-      </c>
-      <c r="P26">
-        <v>-75.161606300000003</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1562</v>
       </c>
       <c r="B27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D27" t="s">
         <v>196</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
         <v>197</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>198</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27">
+        <v>39.970733099999997</v>
+      </c>
+      <c r="Q27">
+        <v>-75.129705099999995</v>
+      </c>
+      <c r="R27" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S27" t="s">
         <v>199</v>
       </c>
-      <c r="G27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>38</v>
-      </c>
-      <c r="O27">
-        <v>39.970733099999997</v>
-      </c>
-      <c r="P27">
-        <v>-75.129705099999995</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R27" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1563</v>
       </c>
       <c r="B28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D28" t="s">
         <v>201</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>202</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>203</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>204</v>
       </c>
-      <c r="F28" t="s">
-        <v>205</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" t="s">
         <v>104</v>
       </c>
-      <c r="H28" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" t="s">
-        <v>38</v>
-      </c>
-      <c r="O28">
+      <c r="J28" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28">
         <v>39.945286199999998</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>-75.164066699999992</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="R28" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1564</v>
       </c>
       <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D29" t="s">
         <v>206</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>207</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>208</v>
       </c>
-      <c r="E29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F29" t="s">
-        <v>205</v>
-      </c>
       <c r="G29" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" t="s">
         <v>104</v>
       </c>
-      <c r="H29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>38</v>
-      </c>
-      <c r="O29">
+      <c r="J29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29">
         <v>39.945343899999997</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>-75.164232699999999</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="R29" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1565</v>
       </c>
       <c r="B30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D30" t="s">
         <v>210</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E30" t="s">
         <v>211</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>212</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>213</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
         <v>214</v>
       </c>
-      <c r="G30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" t="s">
-        <v>215</v>
-      </c>
-      <c r="I30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>38</v>
-      </c>
-      <c r="O30">
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30">
         <v>39.971564299999997</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>-75.144519399999993</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="R30" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1566</v>
       </c>
       <c r="B31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D31" t="s">
         <v>216</v>
       </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>217</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>218</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>219</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31">
+        <v>39.967347200000013</v>
+      </c>
+      <c r="Q31">
+        <v>-75.140985200000003</v>
+      </c>
+      <c r="R31" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S31" t="s">
         <v>220</v>
       </c>
-      <c r="G31" t="s">
-        <v>92</v>
-      </c>
-      <c r="H31" t="s">
-        <v>93</v>
-      </c>
-      <c r="I31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>38</v>
-      </c>
-      <c r="O31">
-        <v>39.967347200000013</v>
-      </c>
-      <c r="P31">
-        <v>-75.140985200000003</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1567</v>
       </c>
       <c r="B32" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D32" t="s">
         <v>222</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>223</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>224</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>225</v>
       </c>
-      <c r="G32" t="s">
+      <c r="J32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32">
+        <v>39.944823399999997</v>
+      </c>
+      <c r="Q32">
+        <v>-75.180016899999998</v>
+      </c>
+      <c r="R32" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S32" t="s">
         <v>226</v>
       </c>
-      <c r="I32" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" t="s">
-        <v>38</v>
-      </c>
-      <c r="O32">
-        <v>39.944823399999997</v>
-      </c>
-      <c r="P32">
-        <v>-75.180016899999998</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1568</v>
       </c>
       <c r="B33" t="s">
+        <v>227</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D33" t="s">
         <v>228</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>229</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>230</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>231</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>232</v>
       </c>
-      <c r="G33" t="s">
-        <v>233</v>
-      </c>
-      <c r="H33" t="s">
-        <v>93</v>
-      </c>
       <c r="I33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>38</v>
-      </c>
-      <c r="O33">
+        <v>92</v>
+      </c>
+      <c r="J33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33">
         <v>39.944419500000002</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>-75.170737899999992</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1569</v>
       </c>
       <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D34" t="s">
         <v>234</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>235</v>
       </c>
-      <c r="D34" t="s">
+      <c r="G34" t="s">
         <v>236</v>
       </c>
-      <c r="F34" t="s">
-        <v>237</v>
-      </c>
-      <c r="G34" t="s">
-        <v>233</v>
-      </c>
       <c r="H34" t="s">
-        <v>93</v>
+        <v>232</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" t="s">
-        <v>38</v>
-      </c>
-      <c r="O34">
+        <v>92</v>
+      </c>
+      <c r="J34" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34">
         <v>39.949910799999998</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>-75.160454999999999</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="R34" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1570</v>
       </c>
       <c r="B35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D35" t="s">
         <v>238</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
         <v>239</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>240</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>241</v>
       </c>
-      <c r="F35" t="s">
-        <v>242</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" t="s">
         <v>92</v>
       </c>
-      <c r="H35" t="s">
-        <v>93</v>
-      </c>
-      <c r="I35" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" t="s">
-        <v>38</v>
-      </c>
-      <c r="O35">
+      <c r="J35" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35">
         <v>39.947785699999997</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>-75.160108000000008</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1571</v>
       </c>
       <c r="B36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D36" t="s">
         <v>243</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>244</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>245</v>
       </c>
-      <c r="E36" t="s">
-        <v>246</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>36</v>
       </c>
-      <c r="H36" t="s">
-        <v>71</v>
-      </c>
       <c r="I36" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" t="s">
-        <v>38</v>
-      </c>
-      <c r="O36">
+        <v>70</v>
+      </c>
+      <c r="J36" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36">
         <v>39.9681268</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>-75.134557399999991</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="R36" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1573</v>
       </c>
       <c r="B37" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D37" t="s">
         <v>247</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
         <v>248</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>249</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>250</v>
       </c>
-      <c r="F37" t="s">
-        <v>251</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>25</v>
       </c>
-      <c r="I37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37">
+      <c r="J37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37">
         <v>39.947794299999998</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>-75.167785299999991</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="R37" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1574</v>
       </c>
       <c r="B38" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D38" t="s">
         <v>252</v>
       </c>
-      <c r="C38" t="s">
+      <c r="E38" t="s">
         <v>253</v>
       </c>
-      <c r="D38" t="s">
+      <c r="G38" t="s">
         <v>254</v>
       </c>
-      <c r="F38" t="s">
-        <v>255</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>25</v>
       </c>
-      <c r="I38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>38</v>
-      </c>
-      <c r="O38">
+      <c r="J38" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38">
         <v>39.919627800000001</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>-75.171386099999992</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1575</v>
       </c>
       <c r="B39" t="s">
+        <v>255</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D39" t="s">
         <v>256</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E39" t="s">
         <v>257</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>258</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>259</v>
       </c>
-      <c r="F39" t="s">
-        <v>260</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>25</v>
       </c>
-      <c r="I39" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39">
+      <c r="J39" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39">
         <v>39.939477599999996</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>-75.171194099999994</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1576</v>
       </c>
       <c r="B40" t="s">
+        <v>260</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D40" t="s">
         <v>261</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
         <v>262</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>263</v>
       </c>
-      <c r="E40" t="s">
+      <c r="H40" t="s">
         <v>264</v>
       </c>
-      <c r="G40" t="s">
+      <c r="J40" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40">
+        <v>39.939990700000003</v>
+      </c>
+      <c r="Q40">
+        <v>-75.152963700000001</v>
+      </c>
+      <c r="R40" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S40" t="s">
         <v>265</v>
       </c>
-      <c r="I40" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" t="s">
-        <v>38</v>
-      </c>
-      <c r="O40">
-        <v>39.939990700000003</v>
-      </c>
-      <c r="P40">
-        <v>-75.152963700000001</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R40" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1577</v>
       </c>
       <c r="B41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D41" t="s">
         <v>267</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>268</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>269</v>
       </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>270</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41">
+        <v>39.949691500000007</v>
+      </c>
+      <c r="Q41">
+        <v>-75.173786499999991</v>
+      </c>
+      <c r="R41" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S41" t="s">
         <v>271</v>
       </c>
-      <c r="G41" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" t="s">
-        <v>38</v>
-      </c>
-      <c r="O41">
-        <v>39.949691500000007</v>
-      </c>
-      <c r="P41">
-        <v>-75.173786499999991</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R41" t="s">
+      <c r="T41" t="s">
         <v>272</v>
       </c>
-      <c r="S41" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1578</v>
       </c>
       <c r="B42" t="s">
+        <v>273</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D42" t="s">
         <v>274</v>
       </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>275</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>276</v>
       </c>
-      <c r="F42" t="s">
+      <c r="H42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" t="s">
         <v>277</v>
       </c>
-      <c r="G42" t="s">
-        <v>36</v>
-      </c>
-      <c r="H42" t="s">
-        <v>278</v>
-      </c>
-      <c r="I42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42">
+      <c r="J42" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42">
         <v>39.9399765</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>-75.157853799999998</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="R42" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1579</v>
       </c>
       <c r="B43" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D43" t="s">
         <v>279</v>
       </c>
-      <c r="C43" t="s">
+      <c r="E43" t="s">
         <v>280</v>
       </c>
-      <c r="D43" t="s">
+      <c r="F43" t="s">
         <v>281</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>282</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43">
+        <v>39.951250900000012</v>
+      </c>
+      <c r="Q43">
+        <v>-75.174123500000007</v>
+      </c>
+      <c r="R43" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S43" t="s">
         <v>283</v>
       </c>
-      <c r="G43" t="s">
-        <v>25</v>
-      </c>
-      <c r="I43" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" t="s">
-        <v>38</v>
-      </c>
-      <c r="O43">
-        <v>39.951250900000012</v>
-      </c>
-      <c r="P43">
-        <v>-75.174123500000007</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R43" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1580</v>
       </c>
       <c r="B44" t="s">
+        <v>284</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D44" t="s">
         <v>285</v>
       </c>
-      <c r="C44" t="s">
+      <c r="E44" t="s">
         <v>286</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>287</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>288</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44">
+        <v>39.946499199999998</v>
+      </c>
+      <c r="Q44">
+        <v>-75.161768199999997</v>
+      </c>
+      <c r="R44" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S44" t="s">
         <v>289</v>
       </c>
-      <c r="G44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I44" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" t="s">
-        <v>38</v>
-      </c>
-      <c r="O44">
-        <v>39.946499199999998</v>
-      </c>
-      <c r="P44">
-        <v>-75.161768199999997</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R44" t="s">
+      <c r="T44" t="s">
         <v>290</v>
       </c>
-      <c r="S44" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1581</v>
       </c>
       <c r="B45" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D45" t="s">
         <v>292</v>
       </c>
-      <c r="C45" t="s">
+      <c r="E45" t="s">
         <v>293</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>294</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>295</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" t="s">
         <v>296</v>
       </c>
-      <c r="G45" t="s">
-        <v>36</v>
-      </c>
-      <c r="H45" t="s">
-        <v>297</v>
-      </c>
-      <c r="I45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>38</v>
-      </c>
-      <c r="O45">
+      <c r="J45" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45">
         <v>39.953597799999997</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>-75.160984799999994</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="R45" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1582</v>
       </c>
       <c r="B46" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D46" t="s">
         <v>298</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E46" t="s">
         <v>299</v>
       </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
         <v>300</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>301</v>
       </c>
-      <c r="F46" t="s">
-        <v>302</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
+        <v>91</v>
+      </c>
+      <c r="I46" t="s">
         <v>92</v>
       </c>
-      <c r="H46" t="s">
-        <v>93</v>
-      </c>
-      <c r="I46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>38</v>
-      </c>
-      <c r="O46">
+      <c r="J46" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46">
         <v>39.944041200000001</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>-75.170019699999997</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="R46" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1583</v>
       </c>
       <c r="B47" t="s">
+        <v>302</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D47" t="s">
         <v>303</v>
       </c>
-      <c r="C47" t="s">
+      <c r="E47" t="s">
         <v>304</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>305</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>306</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s">
         <v>307</v>
       </c>
-      <c r="G47" t="s">
-        <v>78</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47">
+        <v>39.951949399999997</v>
+      </c>
+      <c r="Q47">
+        <v>-75.144386900000001</v>
+      </c>
+      <c r="R47" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S47" t="s">
         <v>308</v>
       </c>
-      <c r="I47" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" t="s">
-        <v>38</v>
-      </c>
-      <c r="O47">
-        <v>39.951949399999997</v>
-      </c>
-      <c r="P47">
-        <v>-75.144386900000001</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R47" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1584</v>
       </c>
       <c r="B48" t="s">
+        <v>309</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D48" t="s">
         <v>310</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E48" t="s">
         <v>311</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
         <v>312</v>
       </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
         <v>313</v>
       </c>
-      <c r="F48" t="s">
+      <c r="H48" t="s">
+        <v>103</v>
+      </c>
+      <c r="I48" t="s">
         <v>314</v>
       </c>
-      <c r="G48" t="s">
-        <v>104</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48">
+        <v>39.936869300000012</v>
+      </c>
+      <c r="Q48">
+        <v>-75.156515900000002</v>
+      </c>
+      <c r="R48" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S48" t="s">
         <v>315</v>
       </c>
-      <c r="I48" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" t="s">
-        <v>38</v>
-      </c>
-      <c r="O48">
-        <v>39.936869300000012</v>
-      </c>
-      <c r="P48">
-        <v>-75.156515900000002</v>
-      </c>
-      <c r="Q48" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R48" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1585</v>
       </c>
       <c r="B49" t="s">
+        <v>316</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D49" t="s">
         <v>317</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>318</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
         <v>319</v>
       </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
         <v>320</v>
       </c>
-      <c r="F49" t="s">
+      <c r="H49" t="s">
         <v>321</v>
       </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
         <v>322</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
+        <v>26</v>
+      </c>
+      <c r="P49">
+        <v>39.965340099999999</v>
+      </c>
+      <c r="Q49">
+        <v>-75.140709299999997</v>
+      </c>
+      <c r="R49" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S49" t="s">
         <v>323</v>
       </c>
-      <c r="I49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>38</v>
-      </c>
-      <c r="O49">
-        <v>39.965340099999999</v>
-      </c>
-      <c r="P49">
-        <v>-75.140709299999997</v>
-      </c>
-      <c r="Q49" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R49" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1586</v>
       </c>
       <c r="B50" t="s">
+        <v>324</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D50" t="s">
         <v>325</v>
       </c>
-      <c r="C50" t="s">
+      <c r="E50" t="s">
         <v>326</v>
       </c>
-      <c r="D50" t="s">
+      <c r="G50" t="s">
         <v>327</v>
       </c>
-      <c r="F50" t="s">
-        <v>328</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>25</v>
       </c>
-      <c r="I50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>38</v>
-      </c>
-      <c r="O50">
+      <c r="J50" t="s">
+        <v>26</v>
+      </c>
+      <c r="P50">
         <v>39.951353500000003</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>-75.175115599999998</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="R50" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1587</v>
       </c>
       <c r="B51" t="s">
+        <v>328</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D51" t="s">
         <v>329</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>330</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>331</v>
       </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>332</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" t="s">
+        <v>58</v>
+      </c>
+      <c r="I51" t="s">
         <v>333</v>
       </c>
-      <c r="G51" t="s">
-        <v>59</v>
-      </c>
-      <c r="H51" t="s">
-        <v>334</v>
-      </c>
-      <c r="I51" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" t="s">
-        <v>38</v>
-      </c>
-      <c r="O51">
+      <c r="J51" t="s">
+        <v>26</v>
+      </c>
+      <c r="P51">
         <v>39.926275500000003</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>-75.167463699999999</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="R51" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1588</v>
       </c>
       <c r="B52" t="s">
+        <v>334</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D52" t="s">
         <v>335</v>
       </c>
-      <c r="C52" t="s">
+      <c r="E52" t="s">
         <v>336</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>337</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>338</v>
       </c>
-      <c r="F52" t="s">
-        <v>339</v>
-      </c>
-      <c r="G52" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" t="s">
-        <v>38</v>
-      </c>
-      <c r="O52">
+      <c r="H52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J52" t="s">
+        <v>26</v>
+      </c>
+      <c r="P52">
         <v>39.919344799999998</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>-75.171119699999991</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="R52" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1589</v>
       </c>
       <c r="B53" t="s">
+        <v>339</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D53" t="s">
         <v>340</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" t="s">
         <v>341</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
         <v>342</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>343</v>
       </c>
-      <c r="F53" t="s">
+      <c r="H53" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s">
         <v>344</v>
       </c>
-      <c r="G53" t="s">
-        <v>78</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="J53" t="s">
+        <v>26</v>
+      </c>
+      <c r="P53">
+        <v>39.925220400000001</v>
+      </c>
+      <c r="Q53">
+        <v>-75.174716699999991</v>
+      </c>
+      <c r="R53" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S53" t="s">
         <v>345</v>
       </c>
-      <c r="I53" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" t="s">
-        <v>38</v>
-      </c>
-      <c r="O53">
-        <v>39.925220400000001</v>
-      </c>
-      <c r="P53">
-        <v>-75.174716699999991</v>
-      </c>
-      <c r="Q53" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R53" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1590</v>
       </c>
       <c r="B54" t="s">
+        <v>346</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D54" t="s">
         <v>347</v>
       </c>
-      <c r="C54" t="s">
+      <c r="E54" t="s">
         <v>348</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>349</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>350</v>
       </c>
-      <c r="F54" t="s">
+      <c r="H54" t="s">
+        <v>192</v>
+      </c>
+      <c r="I54" t="s">
         <v>351</v>
       </c>
-      <c r="G54" t="s">
-        <v>193</v>
-      </c>
-      <c r="H54" t="s">
-        <v>352</v>
-      </c>
-      <c r="I54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" t="s">
-        <v>38</v>
-      </c>
-      <c r="O54">
+      <c r="J54" t="s">
+        <v>26</v>
+      </c>
+      <c r="P54">
         <v>39.9339212</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>-75.155556500000003</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="R54" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1591</v>
       </c>
       <c r="B55" t="s">
+        <v>352</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D55" t="s">
         <v>353</v>
       </c>
-      <c r="C55" t="s">
+      <c r="E55" t="s">
         <v>354</v>
       </c>
-      <c r="D55" t="s">
+      <c r="F55" t="s">
         <v>355</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>356</v>
       </c>
-      <c r="F55" t="s">
+      <c r="H55" t="s">
+        <v>84</v>
+      </c>
+      <c r="J55" t="s">
+        <v>26</v>
+      </c>
+      <c r="P55">
+        <v>39.942576899999999</v>
+      </c>
+      <c r="Q55">
+        <v>-75.185306799999992</v>
+      </c>
+      <c r="R55" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S55" t="s">
         <v>357</v>
       </c>
-      <c r="G55" t="s">
-        <v>85</v>
-      </c>
-      <c r="I55" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" t="s">
-        <v>38</v>
-      </c>
-      <c r="O55">
-        <v>39.942576899999999</v>
-      </c>
-      <c r="P55">
-        <v>-75.185306799999992</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R55" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1592</v>
       </c>
       <c r="B56" t="s">
+        <v>358</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D56" t="s">
         <v>359</v>
       </c>
-      <c r="C56" t="s">
+      <c r="E56" t="s">
         <v>360</v>
       </c>
-      <c r="D56" t="s">
+      <c r="F56" t="s">
         <v>361</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>362</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56">
+        <v>39.948765399999999</v>
+      </c>
+      <c r="Q56">
+        <v>-75.177968399999997</v>
+      </c>
+      <c r="R56" s="2">
+        <v>45969</v>
+      </c>
+      <c r="S56" t="s">
         <v>363</v>
       </c>
-      <c r="G56" t="s">
-        <v>25</v>
-      </c>
-      <c r="I56" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" t="s">
-        <v>38</v>
-      </c>
-      <c r="O56">
-        <v>39.948765399999999</v>
-      </c>
-      <c r="P56">
-        <v>-75.177968399999997</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>45969</v>
-      </c>
-      <c r="R56" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1593</v>
       </c>
       <c r="B57" t="s">
+        <v>364</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D57" t="s">
         <v>365</v>
       </c>
-      <c r="C57" t="s">
+      <c r="E57" t="s">
         <v>366</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>367</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>368</v>
       </c>
-      <c r="F57" t="s">
-        <v>369</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
+        <v>91</v>
+      </c>
+      <c r="I57" t="s">
         <v>92</v>
       </c>
-      <c r="H57" t="s">
-        <v>93</v>
-      </c>
-      <c r="I57" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" t="s">
-        <v>38</v>
-      </c>
-      <c r="O57">
+      <c r="J57" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57">
         <v>39.9515782</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>-75.174830900000003</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="R57" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1594</v>
       </c>
       <c r="B58" t="s">
+        <v>369</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D58" t="s">
         <v>370</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
         <v>371</v>
       </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
         <v>372</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>373</v>
       </c>
-      <c r="F58" t="s">
-        <v>374</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
+        <v>49</v>
+      </c>
+      <c r="I58" t="s">
         <v>50</v>
       </c>
-      <c r="H58" t="s">
-        <v>51</v>
-      </c>
-      <c r="I58" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" t="s">
-        <v>38</v>
-      </c>
-      <c r="O58">
+      <c r="J58" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58">
         <v>39.948388199999997</v>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>-75.217944799999998</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="R58" s="2">
         <v>45969</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1726</v>
       </c>
       <c r="B59" t="s">
+        <v>374</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D59" t="s">
         <v>375</v>
       </c>
-      <c r="C59" t="s">
+      <c r="E59" t="s">
         <v>376</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>377</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>378</v>
       </c>
-      <c r="F59" t="s">
-        <v>379</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>25</v>
       </c>
-      <c r="I59" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" t="s">
-        <v>38</v>
-      </c>
-      <c r="O59">
+      <c r="J59" t="s">
+        <v>26</v>
+      </c>
+      <c r="P59">
         <v>39.931907000000002</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>-75.149544399999996</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="R59" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1727</v>
       </c>
       <c r="B60" t="s">
+        <v>379</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D60" t="s">
         <v>380</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>381</v>
       </c>
-      <c r="D60" t="s">
+      <c r="G60" t="s">
         <v>382</v>
       </c>
-      <c r="F60" t="s">
-        <v>383</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>36</v>
       </c>
-      <c r="H60" t="s">
-        <v>105</v>
-      </c>
       <c r="I60" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" t="s">
-        <v>38</v>
-      </c>
-      <c r="O60">
+        <v>104</v>
+      </c>
+      <c r="J60" t="s">
+        <v>26</v>
+      </c>
+      <c r="P60">
         <v>39.910426600000001</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>-75.050069499999992</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="R60" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1729</v>
       </c>
       <c r="B61" t="s">
+        <v>383</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D61" t="s">
         <v>384</v>
       </c>
-      <c r="C61" t="s">
+      <c r="E61" t="s">
         <v>385</v>
       </c>
-      <c r="D61" t="s">
+      <c r="G61" t="s">
         <v>386</v>
       </c>
-      <c r="F61" t="s">
-        <v>387</v>
-      </c>
-      <c r="G61" t="s">
-        <v>117</v>
-      </c>
-      <c r="I61" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" t="s">
-        <v>38</v>
-      </c>
-      <c r="O61">
+      <c r="H61" t="s">
+        <v>116</v>
+      </c>
+      <c r="J61" t="s">
+        <v>26</v>
+      </c>
+      <c r="P61">
         <v>39.941114900000002</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>-75.149088399999997</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="R61" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1730</v>
       </c>
       <c r="B62" t="s">
+        <v>387</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D62" t="s">
         <v>388</v>
       </c>
-      <c r="C62" t="s">
+      <c r="E62" t="s">
         <v>389</v>
       </c>
-      <c r="D62" t="s">
+      <c r="G62" t="s">
         <v>390</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" t="s">
         <v>391</v>
       </c>
-      <c r="G62" t="s">
-        <v>392</v>
-      </c>
-      <c r="I62" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" t="s">
-        <v>38</v>
-      </c>
-      <c r="O62">
+      <c r="J62" t="s">
+        <v>26</v>
+      </c>
+      <c r="P62">
         <v>39.939704499999998</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>-75.156259599999998</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="R62" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1731</v>
       </c>
       <c r="B63" t="s">
+        <v>392</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D63" t="s">
         <v>393</v>
       </c>
-      <c r="C63" t="s">
+      <c r="E63" t="s">
         <v>394</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>395</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>396</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s">
         <v>397</v>
       </c>
-      <c r="G63" t="s">
-        <v>78</v>
-      </c>
-      <c r="H63" t="s">
-        <v>398</v>
-      </c>
-      <c r="I63" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" t="s">
-        <v>38</v>
-      </c>
-      <c r="O63">
+      <c r="J63" t="s">
+        <v>26</v>
+      </c>
+      <c r="P63">
         <v>39.968518099999997</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>-75.178519699999995</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="R63" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1732</v>
       </c>
       <c r="B64" t="s">
+        <v>398</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D64" t="s">
         <v>399</v>
       </c>
-      <c r="C64" t="s">
+      <c r="E64" t="s">
         <v>400</v>
       </c>
-      <c r="D64" t="s">
+      <c r="F64" t="s">
         <v>401</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>402</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>26</v>
+      </c>
+      <c r="P64">
+        <v>39.9413883</v>
+      </c>
+      <c r="Q64">
+        <v>-75.150354600000014</v>
+      </c>
+      <c r="R64" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S64" t="s">
         <v>403</v>
       </c>
-      <c r="G64" t="s">
-        <v>25</v>
-      </c>
-      <c r="I64" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" t="s">
-        <v>38</v>
-      </c>
-      <c r="O64">
-        <v>39.9413883</v>
-      </c>
-      <c r="P64">
-        <v>-75.150354600000014</v>
-      </c>
-      <c r="Q64" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R64" t="s">
+      <c r="T64" t="s">
         <v>404</v>
       </c>
-      <c r="S64" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1733</v>
       </c>
       <c r="B65" t="s">
+        <v>405</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D65" t="s">
         <v>406</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
         <v>407</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>408</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>409</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
+        <v>36</v>
+      </c>
+      <c r="I65" t="s">
         <v>410</v>
       </c>
-      <c r="G65" t="s">
-        <v>36</v>
-      </c>
-      <c r="H65" t="s">
-        <v>411</v>
-      </c>
-      <c r="I65" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" t="s">
-        <v>38</v>
-      </c>
-      <c r="O65">
+      <c r="J65" t="s">
+        <v>26</v>
+      </c>
+      <c r="P65">
         <v>40.1219337</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>-75.034327399999995</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="R65" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1734</v>
       </c>
       <c r="B66" t="s">
+        <v>411</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D66" t="s">
         <v>412</v>
       </c>
-      <c r="C66" t="s">
+      <c r="E66" t="s">
         <v>413</v>
       </c>
-      <c r="D66" t="s">
+      <c r="G66" t="s">
         <v>414</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" t="s">
+        <v>58</v>
+      </c>
+      <c r="I66" t="s">
         <v>415</v>
       </c>
-      <c r="G66" t="s">
-        <v>59</v>
-      </c>
-      <c r="H66" t="s">
-        <v>416</v>
-      </c>
-      <c r="I66" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" t="s">
-        <v>38</v>
-      </c>
-      <c r="O66">
+      <c r="J66" t="s">
+        <v>26</v>
+      </c>
+      <c r="P66">
         <v>39.928446399999999</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>-75.171258600000002</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="R66" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1735</v>
       </c>
       <c r="B67" t="s">
+        <v>416</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D67" t="s">
         <v>417</v>
       </c>
-      <c r="C67" t="s">
+      <c r="G67" t="s">
         <v>418</v>
       </c>
-      <c r="F67" t="s">
-        <v>419</v>
-      </c>
-      <c r="G67" t="s">
-        <v>104</v>
-      </c>
       <c r="H67" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="I67" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" t="s">
-        <v>38</v>
-      </c>
-      <c r="O67">
+        <v>159</v>
+      </c>
+      <c r="J67" t="s">
+        <v>26</v>
+      </c>
+      <c r="P67">
         <v>39.919901199999998</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>-75.173383200000004</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="R67" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1736</v>
       </c>
       <c r="B68" t="s">
+        <v>419</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D68" t="s">
         <v>420</v>
       </c>
-      <c r="C68" t="s">
+      <c r="E68" t="s">
         <v>421</v>
       </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
         <v>422</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
         <v>423</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s">
         <v>424</v>
       </c>
-      <c r="G68" t="s">
-        <v>78</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
+        <v>26</v>
+      </c>
+      <c r="P68">
+        <v>39.9463188</v>
+      </c>
+      <c r="Q68">
+        <v>-75.157960899999992</v>
+      </c>
+      <c r="R68" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S68" t="s">
         <v>425</v>
       </c>
-      <c r="I68" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" t="s">
-        <v>38</v>
-      </c>
-      <c r="O68">
-        <v>39.9463188</v>
-      </c>
-      <c r="P68">
-        <v>-75.157960899999992</v>
-      </c>
-      <c r="Q68" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R68" t="s">
+      <c r="T68" t="s">
         <v>426</v>
       </c>
-      <c r="S68" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1737</v>
       </c>
       <c r="B69" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D69" t="s">
         <v>428</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" t="s">
         <v>429</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>430</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>431</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
         <v>432</v>
       </c>
-      <c r="G69" t="s">
-        <v>433</v>
-      </c>
-      <c r="I69" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" t="s">
-        <v>38</v>
-      </c>
-      <c r="O69">
+      <c r="J69" t="s">
+        <v>26</v>
+      </c>
+      <c r="P69">
         <v>39.918631400000002</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>-75.153989299999992</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="R69" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1738</v>
       </c>
       <c r="B70" t="s">
+        <v>433</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D70" t="s">
         <v>434</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" t="s">
         <v>435</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
         <v>436</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>437</v>
       </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" t="s">
+        <v>26</v>
+      </c>
+      <c r="P70">
+        <v>39.947769000000001</v>
+      </c>
+      <c r="Q70">
+        <v>-75.16970049999999</v>
+      </c>
+      <c r="R70" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S70" t="s">
         <v>438</v>
       </c>
-      <c r="G70" t="s">
-        <v>25</v>
-      </c>
-      <c r="I70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>38</v>
-      </c>
-      <c r="O70">
-        <v>39.947769000000001</v>
-      </c>
-      <c r="P70">
-        <v>-75.16970049999999</v>
-      </c>
-      <c r="Q70" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R70" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1739</v>
       </c>
       <c r="B71" t="s">
+        <v>439</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D71" t="s">
         <v>440</v>
       </c>
-      <c r="C71" t="s">
+      <c r="E71" t="s">
         <v>441</v>
       </c>
-      <c r="D71" t="s">
+      <c r="G71" t="s">
         <v>442</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
+        <v>103</v>
+      </c>
+      <c r="I71" t="s">
         <v>443</v>
       </c>
-      <c r="G71" t="s">
-        <v>104</v>
-      </c>
-      <c r="H71" t="s">
-        <v>444</v>
-      </c>
-      <c r="I71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" t="s">
-        <v>38</v>
-      </c>
-      <c r="O71">
+      <c r="J71" t="s">
+        <v>26</v>
+      </c>
+      <c r="P71">
         <v>39.943967499999999</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>-75.169153299999991</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="R71" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1740</v>
       </c>
       <c r="B72" t="s">
+        <v>444</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D72" t="s">
         <v>445</v>
       </c>
-      <c r="C72" t="s">
+      <c r="E72" t="s">
         <v>446</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F72" t="s">
         <v>447</v>
       </c>
-      <c r="E72" t="s">
+      <c r="G72" t="s">
         <v>448</v>
       </c>
-      <c r="F72" t="s">
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" t="s">
+        <v>26</v>
+      </c>
+      <c r="P72">
+        <v>40.059318500000003</v>
+      </c>
+      <c r="Q72">
+        <v>-75.190036300000003</v>
+      </c>
+      <c r="R72" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S72" t="s">
         <v>449</v>
       </c>
-      <c r="G72" t="s">
-        <v>25</v>
-      </c>
-      <c r="I72" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" t="s">
-        <v>38</v>
-      </c>
-      <c r="O72">
-        <v>40.059318500000003</v>
-      </c>
-      <c r="P72">
-        <v>-75.190036300000003</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R72" t="s">
+      <c r="T72" t="s">
         <v>450</v>
       </c>
-      <c r="S72" t="s">
+      <c r="U72" t="s">
         <v>451</v>
       </c>
-      <c r="T72" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1741</v>
       </c>
       <c r="B73" t="s">
+        <v>452</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D73" t="s">
         <v>453</v>
       </c>
-      <c r="C73" t="s">
+      <c r="E73" t="s">
         <v>454</v>
       </c>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
         <v>455</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>456</v>
       </c>
-      <c r="F73" t="s">
+      <c r="H73" t="s">
+        <v>432</v>
+      </c>
+      <c r="J73" t="s">
+        <v>26</v>
+      </c>
+      <c r="P73">
+        <v>39.921155900000002</v>
+      </c>
+      <c r="Q73">
+        <v>-75.163266499999992</v>
+      </c>
+      <c r="R73" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S73" t="s">
         <v>457</v>
       </c>
-      <c r="G73" t="s">
-        <v>433</v>
-      </c>
-      <c r="I73" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" t="s">
-        <v>38</v>
-      </c>
-      <c r="O73">
-        <v>39.921155900000002</v>
-      </c>
-      <c r="P73">
-        <v>-75.163266499999992</v>
-      </c>
-      <c r="Q73" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R73" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1742</v>
       </c>
       <c r="B74" t="s">
+        <v>458</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D74" t="s">
         <v>459</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" t="s">
         <v>460</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
         <v>461</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>462</v>
       </c>
-      <c r="F74" t="s">
-        <v>463</v>
-      </c>
-      <c r="G74" t="s">
-        <v>433</v>
-      </c>
-      <c r="I74" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" t="s">
-        <v>38</v>
-      </c>
-      <c r="O74">
+      <c r="H74" t="s">
+        <v>432</v>
+      </c>
+      <c r="J74" t="s">
+        <v>26</v>
+      </c>
+      <c r="P74">
         <v>39.926405699999997</v>
       </c>
-      <c r="P74">
+      <c r="Q74">
         <v>-75.157535600000003</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="R74" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1743</v>
       </c>
       <c r="B75" t="s">
+        <v>463</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D75" t="s">
         <v>464</v>
       </c>
-      <c r="C75" t="s">
+      <c r="E75" t="s">
         <v>465</v>
       </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
         <v>466</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>467</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" t="s">
+        <v>177</v>
+      </c>
+      <c r="I75" t="s">
+        <v>104</v>
+      </c>
+      <c r="J75" t="s">
+        <v>26</v>
+      </c>
+      <c r="P75">
+        <v>39.952112100000001</v>
+      </c>
+      <c r="Q75">
+        <v>-75.172149099999999</v>
+      </c>
+      <c r="R75" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S75" t="s">
         <v>468</v>
       </c>
-      <c r="G75" t="s">
-        <v>178</v>
-      </c>
-      <c r="H75" t="s">
-        <v>105</v>
-      </c>
-      <c r="I75" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" t="s">
-        <v>38</v>
-      </c>
-      <c r="O75">
-        <v>39.952112100000001</v>
-      </c>
-      <c r="P75">
-        <v>-75.172149099999999</v>
-      </c>
-      <c r="Q75" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R75" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1744</v>
       </c>
       <c r="B76" t="s">
+        <v>469</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D76" t="s">
         <v>470</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" t="s">
         <v>471</v>
       </c>
-      <c r="D76" t="s">
+      <c r="F76" t="s">
         <v>472</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>473</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" t="s">
+        <v>26</v>
+      </c>
+      <c r="P76">
+        <v>39.982485199999999</v>
+      </c>
+      <c r="Q76">
+        <v>-75.102839599999996</v>
+      </c>
+      <c r="R76" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S76" t="s">
         <v>474</v>
       </c>
-      <c r="G76" t="s">
-        <v>36</v>
-      </c>
-      <c r="H76" t="s">
-        <v>105</v>
-      </c>
-      <c r="I76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>38</v>
-      </c>
-      <c r="O76">
-        <v>39.982485199999999</v>
-      </c>
-      <c r="P76">
-        <v>-75.102839599999996</v>
-      </c>
-      <c r="Q76" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R76" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1745</v>
       </c>
       <c r="B77" t="s">
+        <v>475</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D77" t="s">
         <v>476</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" t="s">
         <v>477</v>
       </c>
-      <c r="D77" t="s">
+      <c r="F77" t="s">
         <v>478</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>479</v>
       </c>
-      <c r="F77" t="s">
-        <v>480</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
+        <v>91</v>
+      </c>
+      <c r="I77" t="s">
         <v>92</v>
       </c>
-      <c r="H77" t="s">
-        <v>93</v>
-      </c>
-      <c r="I77" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" t="s">
-        <v>38</v>
-      </c>
-      <c r="O77">
+      <c r="J77" t="s">
+        <v>26</v>
+      </c>
+      <c r="P77">
         <v>39.940707699999997</v>
       </c>
-      <c r="P77">
+      <c r="Q77">
         <v>-75.146044199999992</v>
       </c>
-      <c r="Q77" s="2">
+      <c r="R77" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1746</v>
       </c>
       <c r="B78" t="s">
+        <v>480</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D78" t="s">
         <v>481</v>
       </c>
-      <c r="C78" t="s">
+      <c r="E78" t="s">
         <v>482</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
         <v>483</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>484</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" t="s">
+        <v>58</v>
+      </c>
+      <c r="I78" t="s">
         <v>485</v>
       </c>
-      <c r="G78" t="s">
-        <v>59</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
+        <v>26</v>
+      </c>
+      <c r="P78">
+        <v>39.938333399999998</v>
+      </c>
+      <c r="Q78">
+        <v>-75.159783899999994</v>
+      </c>
+      <c r="R78" s="2">
+        <v>45977</v>
+      </c>
+      <c r="S78" t="s">
         <v>486</v>
       </c>
-      <c r="I78" t="s">
-        <v>26</v>
-      </c>
-      <c r="N78" t="s">
-        <v>38</v>
-      </c>
-      <c r="O78">
-        <v>39.938333399999998</v>
-      </c>
-      <c r="P78">
-        <v>-75.159783899999994</v>
-      </c>
-      <c r="Q78" s="2">
-        <v>45977</v>
-      </c>
-      <c r="R78" t="s">
+      <c r="T78" t="s">
         <v>487</v>
       </c>
-      <c r="S78" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1747</v>
       </c>
       <c r="B79" t="s">
+        <v>488</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D79" t="s">
         <v>489</v>
       </c>
-      <c r="C79" t="s">
+      <c r="E79" t="s">
         <v>490</v>
       </c>
-      <c r="D79" t="s">
+      <c r="F79" t="s">
         <v>491</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>492</v>
       </c>
-      <c r="F79" t="s">
-        <v>493</v>
-      </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
+        <v>103</v>
+      </c>
+      <c r="I79" t="s">
         <v>104</v>
       </c>
-      <c r="H79" t="s">
-        <v>105</v>
-      </c>
-      <c r="I79" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" t="s">
-        <v>38</v>
-      </c>
-      <c r="O79">
+      <c r="J79" t="s">
+        <v>26</v>
+      </c>
+      <c r="P79">
         <v>39.9803949</v>
       </c>
-      <c r="P79">
+      <c r="Q79">
         <v>-75.113133699999992</v>
       </c>
-      <c r="Q79" s="2">
+      <c r="R79" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1748</v>
       </c>
       <c r="B80" t="s">
+        <v>493</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D80" t="s">
         <v>494</v>
       </c>
-      <c r="C80" t="s">
+      <c r="E80" t="s">
         <v>495</v>
       </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
         <v>496</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>497</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" t="s">
         <v>498</v>
       </c>
-      <c r="G80" t="s">
-        <v>36</v>
-      </c>
-      <c r="H80" t="s">
-        <v>499</v>
-      </c>
-      <c r="I80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>38</v>
-      </c>
-      <c r="O80">
+      <c r="J80" t="s">
+        <v>26</v>
+      </c>
+      <c r="P80">
         <v>39.926336599999999</v>
       </c>
-      <c r="P80">
+      <c r="Q80">
         <v>-75.147412399999993</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1749</v>
       </c>
       <c r="B81" t="s">
+        <v>499</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D81" t="s">
         <v>500</v>
       </c>
-      <c r="C81" t="s">
+      <c r="E81" t="s">
         <v>501</v>
       </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
         <v>502</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>503</v>
       </c>
-      <c r="F81" t="s">
-        <v>504</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" t="s">
         <v>92</v>
       </c>
-      <c r="H81" t="s">
-        <v>93</v>
-      </c>
-      <c r="I81" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" t="s">
-        <v>38</v>
-      </c>
-      <c r="O81">
+      <c r="J81" t="s">
+        <v>26</v>
+      </c>
+      <c r="P81">
         <v>39.964689399999997</v>
       </c>
-      <c r="P81">
+      <c r="Q81">
         <v>-75.174111199999999</v>
       </c>
-      <c r="Q81" s="2">
+      <c r="R81" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1750</v>
       </c>
       <c r="B82" t="s">
+        <v>504</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D82" t="s">
         <v>505</v>
       </c>
-      <c r="C82" t="s">
+      <c r="E82" t="s">
         <v>506</v>
       </c>
-      <c r="D82" t="s">
+      <c r="F82" t="s">
         <v>507</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>508</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H82" t="s">
+        <v>36</v>
+      </c>
+      <c r="I82" t="s">
         <v>509</v>
       </c>
-      <c r="G82" t="s">
-        <v>36</v>
-      </c>
-      <c r="H82" t="s">
-        <v>510</v>
-      </c>
-      <c r="I82" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" t="s">
-        <v>38</v>
-      </c>
-      <c r="O82">
+      <c r="J82" t="s">
+        <v>26</v>
+      </c>
+      <c r="P82">
         <v>39.947806000000007</v>
       </c>
-      <c r="P82">
+      <c r="Q82">
         <v>-75.160342099999994</v>
       </c>
-      <c r="Q82" s="2">
+      <c r="R82" s="2">
         <v>45977</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1754</v>
       </c>
       <c r="B83" t="s">
+        <v>510</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D83" t="s">
         <v>511</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" t="s">
         <v>512</v>
       </c>
-      <c r="D83" t="s">
+      <c r="F83" t="s">
         <v>513</v>
       </c>
-      <c r="E83" t="s">
+      <c r="G83" t="s">
         <v>514</v>
       </c>
-      <c r="F83" t="s">
+      <c r="H83" t="s">
         <v>515</v>
       </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>516</v>
       </c>
-      <c r="H83" t="s">
+      <c r="J83" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" t="s">
         <v>517</v>
       </c>
-      <c r="I83" t="s">
-        <v>36</v>
-      </c>
-      <c r="K83" t="s">
+      <c r="P83">
+        <v>39.944972700000001</v>
+      </c>
+      <c r="Q83">
+        <v>-75.177395099999998</v>
+      </c>
+      <c r="R83" s="2">
+        <v>45978</v>
+      </c>
+      <c r="S83" t="s">
         <v>518</v>
       </c>
-      <c r="N83" t="s">
-        <v>38</v>
-      </c>
-      <c r="O83">
-        <v>39.944972700000001</v>
-      </c>
-      <c r="P83">
-        <v>-75.177395099999998</v>
-      </c>
-      <c r="Q83" s="2">
-        <v>45978</v>
-      </c>
-      <c r="R83" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1755</v>
       </c>
       <c r="B84" t="s">
+        <v>519</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D84" t="s">
         <v>520</v>
       </c>
-      <c r="C84" t="s">
+      <c r="F84" t="s">
         <v>521</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>522</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" t="s">
+        <v>36</v>
+      </c>
+      <c r="I84" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" t="s">
+        <v>26</v>
+      </c>
+      <c r="P84">
+        <v>39.974236699999999</v>
+      </c>
+      <c r="Q84">
+        <v>-75.182546800000011</v>
+      </c>
+      <c r="R84" s="2">
+        <v>45978</v>
+      </c>
+      <c r="S84" t="s">
         <v>523</v>
       </c>
-      <c r="G84" t="s">
-        <v>36</v>
-      </c>
-      <c r="H84" t="s">
-        <v>315</v>
-      </c>
-      <c r="I84" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" t="s">
-        <v>38</v>
-      </c>
-      <c r="O84">
-        <v>39.974236699999999</v>
-      </c>
-      <c r="P84">
-        <v>-75.182546800000011</v>
-      </c>
-      <c r="Q84" s="2">
-        <v>45978</v>
-      </c>
-      <c r="R84" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1756</v>
       </c>
       <c r="B85" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D85" t="s">
         <v>525</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E85" t="s">
         <v>526</v>
       </c>
-      <c r="D85" t="s">
+      <c r="F85" t="s">
         <v>527</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>528</v>
       </c>
-      <c r="F85" t="s">
+      <c r="H85" t="s">
+        <v>91</v>
+      </c>
+      <c r="I85" t="s">
         <v>529</v>
       </c>
-      <c r="G85" t="s">
-        <v>92</v>
-      </c>
-      <c r="H85" t="s">
+      <c r="J85" t="s">
+        <v>26</v>
+      </c>
+      <c r="P85">
+        <v>39.9798258</v>
+      </c>
+      <c r="Q85">
+        <v>-75.129835499999999</v>
+      </c>
+      <c r="R85" s="2">
+        <v>45978</v>
+      </c>
+      <c r="S85" t="s">
         <v>530</v>
       </c>
-      <c r="I85" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" t="s">
-        <v>38</v>
-      </c>
-      <c r="O85">
-        <v>39.9798258</v>
-      </c>
-      <c r="P85">
-        <v>-75.129835499999999</v>
-      </c>
-      <c r="Q85" s="2">
-        <v>45978</v>
-      </c>
-      <c r="R85" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1757</v>
       </c>
       <c r="B86" t="s">
+        <v>531</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D86" t="s">
         <v>532</v>
       </c>
-      <c r="C86" t="s">
+      <c r="E86" t="s">
         <v>533</v>
       </c>
-      <c r="D86" t="s">
+      <c r="F86" t="s">
         <v>534</v>
       </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>535</v>
       </c>
-      <c r="F86" t="s">
+      <c r="H86" t="s">
+        <v>515</v>
+      </c>
+      <c r="I86" t="s">
         <v>536</v>
       </c>
-      <c r="G86" t="s">
-        <v>516</v>
-      </c>
-      <c r="H86" t="s">
+      <c r="J86" t="s">
+        <v>26</v>
+      </c>
+      <c r="P86">
+        <v>39.944876200000003</v>
+      </c>
+      <c r="Q86">
+        <v>-75.160762800000001</v>
+      </c>
+      <c r="R86" s="2">
+        <v>45979</v>
+      </c>
+      <c r="S86" t="s">
         <v>537</v>
       </c>
-      <c r="I86" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" t="s">
-        <v>38</v>
-      </c>
-      <c r="O86">
-        <v>39.944876200000003</v>
-      </c>
-      <c r="P86">
-        <v>-75.160762800000001</v>
-      </c>
-      <c r="Q86" s="2">
-        <v>45979</v>
-      </c>
-      <c r="R86" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1786</v>
       </c>
       <c r="B87" t="s">
+        <v>538</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D87" t="s">
         <v>539</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
         <v>540</v>
       </c>
-      <c r="D87" t="s">
+      <c r="F87" t="s">
         <v>541</v>
       </c>
-      <c r="E87" t="s">
+      <c r="G87" t="s">
         <v>542</v>
       </c>
-      <c r="F87" t="s">
+      <c r="H87" t="s">
+        <v>592</v>
+      </c>
+      <c r="I87" t="s">
         <v>543</v>
       </c>
-      <c r="G87" t="s">
-        <v>593</v>
-      </c>
-      <c r="H87" t="s">
-        <v>544</v>
-      </c>
-      <c r="I87" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" t="s">
-        <v>38</v>
-      </c>
-      <c r="O87">
+      <c r="J87" t="s">
+        <v>26</v>
+      </c>
+      <c r="P87">
         <v>40.022318299999988</v>
       </c>
-      <c r="P87">
+      <c r="Q87">
         <v>-75.319580799999997</v>
       </c>
-      <c r="Q87" s="2">
+      <c r="R87" s="2">
         <v>45997</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1787</v>
       </c>
       <c r="B88" t="s">
+        <v>544</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D88" t="s">
         <v>545</v>
       </c>
-      <c r="C88" t="s">
+      <c r="E88" t="s">
         <v>546</v>
       </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
         <v>547</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>548</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" t="s">
         <v>549</v>
       </c>
-      <c r="G88" t="s">
+      <c r="J88" t="s">
+        <v>26</v>
+      </c>
+      <c r="P88">
+        <v>39.954628999999997</v>
+      </c>
+      <c r="Q88">
+        <v>-75.199683899999997</v>
+      </c>
+      <c r="R88" s="2">
+        <v>45997</v>
+      </c>
+      <c r="S88" t="s">
         <v>550</v>
       </c>
-      <c r="I88" t="s">
-        <v>26</v>
-      </c>
-      <c r="N88" t="s">
-        <v>38</v>
-      </c>
-      <c r="O88">
-        <v>39.954628999999997</v>
-      </c>
-      <c r="P88">
-        <v>-75.199683899999997</v>
-      </c>
-      <c r="Q88" s="2">
-        <v>45997</v>
-      </c>
-      <c r="R88" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1788</v>
       </c>
       <c r="B89" t="s">
+        <v>551</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D89" t="s">
         <v>552</v>
       </c>
-      <c r="C89" t="s">
+      <c r="E89" t="s">
         <v>553</v>
       </c>
-      <c r="D89" t="s">
+      <c r="F89" t="s">
         <v>554</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>555</v>
       </c>
-      <c r="F89" t="s">
-        <v>556</v>
-      </c>
-      <c r="G89" t="s">
-        <v>593</v>
-      </c>
       <c r="H89" t="s">
-        <v>60</v>
+        <v>592</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" t="s">
-        <v>38</v>
-      </c>
-      <c r="O89">
+        <v>59</v>
+      </c>
+      <c r="J89" t="s">
+        <v>26</v>
+      </c>
+      <c r="P89">
         <v>39.955408599999998</v>
       </c>
-      <c r="P89">
+      <c r="Q89">
         <v>-75.1544861</v>
       </c>
-      <c r="Q89" s="2">
+      <c r="R89" s="2">
         <v>45997</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1789</v>
       </c>
       <c r="B90" t="s">
-        <v>552</v>
-      </c>
-      <c r="C90" t="s">
+        <v>551</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D90" t="s">
+        <v>556</v>
+      </c>
+      <c r="E90" t="s">
         <v>557</v>
       </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
+        <v>554</v>
+      </c>
+      <c r="G90" t="s">
         <v>558</v>
       </c>
-      <c r="E90" t="s">
-        <v>555</v>
-      </c>
-      <c r="F90" t="s">
-        <v>559</v>
-      </c>
-      <c r="G90" t="s">
-        <v>593</v>
-      </c>
       <c r="H90" t="s">
-        <v>60</v>
+        <v>592</v>
       </c>
       <c r="I90" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" t="s">
-        <v>38</v>
-      </c>
-      <c r="O90">
+        <v>59</v>
+      </c>
+      <c r="J90" t="s">
+        <v>26</v>
+      </c>
+      <c r="P90">
         <v>39.954715299999997</v>
       </c>
-      <c r="P90">
+      <c r="Q90">
         <v>-75.202095200000002</v>
       </c>
-      <c r="Q90" s="2">
+      <c r="R90" s="2">
         <v>45997</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1790</v>
       </c>
       <c r="B91" t="s">
+        <v>559</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D91" t="s">
         <v>560</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" t="s">
         <v>561</v>
       </c>
-      <c r="D91" t="s">
+      <c r="G91" t="s">
         <v>562</v>
       </c>
-      <c r="F91" t="s">
-        <v>563</v>
-      </c>
-      <c r="G91" t="s">
-        <v>147</v>
-      </c>
-      <c r="I91" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" t="s">
-        <v>38</v>
-      </c>
-      <c r="O91">
+      <c r="H91" t="s">
+        <v>146</v>
+      </c>
+      <c r="J91" t="s">
+        <v>26</v>
+      </c>
+      <c r="P91">
         <v>39.953813599999997</v>
       </c>
-      <c r="P91">
+      <c r="Q91">
         <v>-75.1558378</v>
       </c>
-      <c r="Q91" s="2">
+      <c r="R91" s="2">
         <v>45997</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1791</v>
       </c>
       <c r="B92" t="s">
+        <v>563</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D92" t="s">
         <v>564</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92" t="s">
         <v>565</v>
       </c>
-      <c r="D92" t="s">
+      <c r="F92" t="s">
         <v>566</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>567</v>
-      </c>
-      <c r="F92" t="s">
-        <v>568</v>
-      </c>
-      <c r="G92" t="s">
-        <v>592</v>
       </c>
       <c r="H92" t="s">
         <v>591</v>
       </c>
       <c r="I92" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" t="s">
-        <v>38</v>
-      </c>
-      <c r="O92">
+        <v>590</v>
+      </c>
+      <c r="J92" t="s">
+        <v>26</v>
+      </c>
+      <c r="P92">
         <v>39.967475999999998</v>
       </c>
-      <c r="P92">
+      <c r="Q92">
         <v>-75.1694289</v>
       </c>
-      <c r="Q92" s="2">
+      <c r="R92" s="2">
         <v>45997</v>
       </c>
-      <c r="R92" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S92" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1792</v>
       </c>
       <c r="B93" t="s">
+        <v>569</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D93" t="s">
         <v>570</v>
       </c>
-      <c r="C93" t="s">
+      <c r="E93" t="s">
         <v>571</v>
       </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
         <v>572</v>
       </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>573</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" t="s">
+        <v>589</v>
+      </c>
+      <c r="I93" t="s">
         <v>574</v>
       </c>
-      <c r="G93" t="s">
-        <v>590</v>
-      </c>
-      <c r="H93" t="s">
+      <c r="J93" t="s">
+        <v>26</v>
+      </c>
+      <c r="P93">
+        <v>39.966393500000002</v>
+      </c>
+      <c r="Q93">
+        <v>-75.134263699999991</v>
+      </c>
+      <c r="R93" s="2">
+        <v>45997</v>
+      </c>
+      <c r="S93" t="s">
         <v>575</v>
       </c>
-      <c r="I93" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" t="s">
-        <v>38</v>
-      </c>
-      <c r="O93">
-        <v>39.966393500000002</v>
-      </c>
-      <c r="P93">
-        <v>-75.134263699999991</v>
-      </c>
-      <c r="Q93" s="2">
-        <v>45997</v>
-      </c>
-      <c r="R93" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1793</v>
       </c>
       <c r="B94" t="s">
+        <v>576</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D94" t="s">
         <v>577</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
         <v>578</v>
       </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>579</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>580</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" t="s">
+        <v>587</v>
+      </c>
+      <c r="I94" t="s">
+        <v>588</v>
+      </c>
+      <c r="J94" t="s">
+        <v>26</v>
+      </c>
+      <c r="P94">
+        <v>39.956620099999988</v>
+      </c>
+      <c r="Q94">
+        <v>-75.146333400000003</v>
+      </c>
+      <c r="R94" s="2">
+        <v>45997</v>
+      </c>
+      <c r="S94" t="s">
         <v>581</v>
       </c>
-      <c r="G94" t="s">
-        <v>588</v>
-      </c>
-      <c r="H94" t="s">
-        <v>589</v>
-      </c>
-      <c r="I94" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" t="s">
-        <v>38</v>
-      </c>
-      <c r="O94">
-        <v>39.956620099999988</v>
-      </c>
-      <c r="P94">
-        <v>-75.146333400000003</v>
-      </c>
-      <c r="Q94" s="2">
-        <v>45997</v>
-      </c>
-      <c r="R94" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1794</v>
       </c>
       <c r="B95" t="s">
+        <v>582</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D95" t="s">
         <v>583</v>
       </c>
-      <c r="C95" t="s">
+      <c r="E95" t="s">
         <v>584</v>
       </c>
-      <c r="D95" t="s">
+      <c r="F95" t="s">
         <v>585</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>586</v>
       </c>
-      <c r="F95" t="s">
+      <c r="H95" t="s">
         <v>587</v>
       </c>
-      <c r="G95" t="s">
-        <v>588</v>
-      </c>
-      <c r="H95" t="s">
-        <v>179</v>
-      </c>
       <c r="I95" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" t="s">
-        <v>38</v>
-      </c>
-      <c r="O95">
+        <v>178</v>
+      </c>
+      <c r="J95" t="s">
+        <v>26</v>
+      </c>
+      <c r="P95">
         <v>39.927078799999997</v>
       </c>
-      <c r="P95">
+      <c r="Q95">
         <v>-75.16715219999999</v>
       </c>
-      <c r="Q95" s="2">
+      <c r="R95" s="2">
         <v>45998</v>
       </c>
     </row>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64e205e7bb0d9351/桌面/GitHubProjects/BYOB/philly_yelp_crawler/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24138D43-E156-43CE-8F23-A4ACD57D954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_71F152BDD300520CCDD3D7734B5ED87656CFA92A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D99753-9FAB-4856-927E-C678C5955C6C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="631">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -28,6 +28,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>cover_image_url</t>
+  </si>
+  <si>
     <t>Add</t>
   </si>
   <si>
@@ -82,9 +85,33 @@
     <t>Email_3</t>
   </si>
   <si>
+    <t>Email_4</t>
+  </si>
+  <si>
+    <t>Email_5</t>
+  </si>
+  <si>
+    <t>Email_6</t>
+  </si>
+  <si>
+    <t>Email_7</t>
+  </si>
+  <si>
+    <t>Email_8</t>
+  </si>
+  <si>
+    <t>Email_9</t>
+  </si>
+  <si>
+    <t>Email_10</t>
+  </si>
+  <si>
     <t>Burrata</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-3.webp</t>
+  </si>
+  <si>
     <t>1247 S 13th St, Philadelphia, PA 19147, United States</t>
   </si>
   <si>
@@ -118,6 +145,9 @@
     <t>White yak</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_georgian_byob_khachapuri-1.webp</t>
+  </si>
+  <si>
     <t> 6118 Ridge Ave, Philadelphia, PA 19128 </t>
   </si>
   <si>
@@ -139,6 +169,9 @@
     <t>La Nonna</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-1.webp</t>
+  </si>
+  <si>
     <t>214 South St, Philadelphia, PA 19147</t>
   </si>
   <si>
@@ -157,6 +190,9 @@
     <t>Vientiane Bistro</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_thai_byob_assorteddishes.webp</t>
+  </si>
+  <si>
     <t>2537 Kensington Ave, Philadelphia, PA 19125</t>
   </si>
   <si>
@@ -184,6 +220,9 @@
     <t>Yamitsuki</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_chinese_byob_hotpot.webp</t>
+  </si>
+  <si>
     <t>1028 Arch St , Philadelphia, PA 19107</t>
   </si>
   <si>
@@ -220,6 +259,9 @@
     <t>Sakartvelo</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_georgian_byob_khachapuri-2.webp</t>
+  </si>
+  <si>
     <t>705 Chestnut St, Philadelphia, PA 19106</t>
   </si>
   <si>
@@ -241,6 +283,9 @@
     <t>Apricot Stone</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_fishplate.webp</t>
+  </si>
+  <si>
     <t>428 W Girard Ave, Philadelphia, PA 19123 </t>
   </si>
   <si>
@@ -286,6 +331,9 @@
     <t>Yanako restaurant</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-chef-preparing-sushi-logo.webp</t>
+  </si>
+  <si>
     <t>4345 Main St, Philadelphia, PA 19127</t>
   </si>
   <si>
@@ -304,6 +352,9 @@
     <t>Fiorino</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-carbonara-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
     <t>3572 Indian Queen Ln, Philadelphia, PA 19129</t>
   </si>
   <si>
@@ -340,6 +391,9 @@
     <t>Han dynasty (manayunk)</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-japanese-ramen-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
     <t>4356 Main St, Philadelphia, PA 19127</t>
   </si>
   <si>
@@ -358,6 +412,9 @@
     <t>Casablanca Mediterranean Grill</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_meze.webp</t>
+  </si>
+  <si>
     <t>947 Federal St, Philadelphia, PA 19147</t>
   </si>
   <si>
@@ -412,6 +469,9 @@
     <t>June BYOB</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_french_byob_finedining-2.webp</t>
+  </si>
+  <si>
     <t> 690 Haddon Ave, Collingswood, NJ 08108 </t>
   </si>
   <si>
@@ -433,6 +493,9 @@
     <t>Scampi</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-2.webp</t>
+  </si>
+  <si>
     <t> 617 S 3rd St, Philadelphia, PA 19147 </t>
   </si>
   <si>
@@ -469,6 +532,9 @@
     <t>A Mano</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/italian-restaurant-logo-placeholder-3.webp</t>
+  </si>
+  <si>
     <t>2244 Fairmount Ave, Philadelphia, PA 19130</t>
   </si>
   <si>
@@ -541,6 +607,9 @@
     <t>Casa Nostra</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
     <t>775 S Front St, Philadelphia, PA 19147</t>
   </si>
   <si>
@@ -589,6 +658,9 @@
     <t>El Chingon Philly</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-1.webp</t>
+  </si>
+  <si>
     <t>1524 S 10th St, Philadelphia, PA 19147</t>
   </si>
   <si>
@@ -670,6 +742,9 @@
     <t>Hikari Sushi</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_japanese_byob_sushibar-2.webp</t>
+  </si>
+  <si>
     <t>1040 N American St #701, Philadelphia, PA 19123</t>
   </si>
   <si>
@@ -724,6 +799,9 @@
     <t>Kichi Omakase</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_seafood_byob-2.webp</t>
+  </si>
+  <si>
     <t>112 S 12th St, Philadelphia, PA 19107, United States</t>
   </si>
   <si>
@@ -1117,6 +1195,9 @@
     <t>Vic Sushi Bar</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-official-logo-coming-soon.webp</t>
+  </si>
+  <si>
     <t>2035 Sansom St, Philadelphia, PA 19103</t>
   </si>
   <si>
@@ -1306,6 +1387,9 @@
     <t>La Canasta Mexican Food</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-2.webp</t>
+  </si>
+  <si>
     <t>2341 S 4th St, Philadelphia, PA 19148</t>
   </si>
   <si>
@@ -1522,6 +1606,9 @@
     <t>Umai Umai</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_japanese_byob_sushibar-1.webp</t>
+  </si>
+  <si>
     <t>533 N 22nd St, Philadelphia, PA 19130</t>
   </si>
   <si>
@@ -1657,6 +1744,9 @@
     <t>Amma's South Indian Cuisine</t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-indian-curry-naan-byob-restaurant-philadelphia.webp</t>
+  </si>
+  <si>
     <t>103 S 39th St UNIT 3, PA 19104</t>
   </si>
   <si>
@@ -1714,6 +1804,9 @@
     <t>Tiffin Indian Cuisine Fairmount</t>
   </si>
   <si>
+    <t>https://example.com/placeholder/vegan-1.webp</t>
+  </si>
+  <si>
     <t>1921 Fairmount Ave, Philadelphia, PA 19130</t>
   </si>
   <si>
@@ -1726,12 +1819,21 @@
     <t>https://www.yelp.com/biz/tiffin-fairmount-philadelphia</t>
   </si>
   <si>
+    <t>Vegan, Indian, other</t>
+  </si>
+  <si>
+    <t>Desserts</t>
+  </si>
+  <si>
     <t>catering@tiffin.com</t>
   </si>
   <si>
     <t>Elwood </t>
   </si>
   <si>
+    <t>https://byobmap.com/wp-content/uploads/2025/11/byob-steak-medium-rare.webp</t>
+  </si>
+  <si>
     <t>1007 Frankford Ave, Philadelphia, PA 19125</t>
   </si>
   <si>
@@ -1744,6 +1846,9 @@
     <t>https://www.yelp.com/biz/elwood-philadelphia-2</t>
   </si>
   <si>
+    <t>American</t>
+  </si>
+  <si>
     <t>New American, Tea Rooms</t>
   </si>
   <si>
@@ -1765,6 +1870,12 @@
     <t>https://www.yelp.com/biz/radicchio-cafe-philadelphia</t>
   </si>
   <si>
+    <t>Italian, other</t>
+  </si>
+  <si>
+    <t>Cafes</t>
+  </si>
+  <si>
     <t>info@radicchiocafe.com</t>
   </si>
   <si>
@@ -1783,123 +1894,41 @@
     <t>https://www.yelp.com/biz/bucatini-caffe-philadelphia</t>
   </si>
   <si>
-    <t>Italian, other</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cafes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>American</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desserts</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vegan, Indian, other</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>other</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cover_image_url</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-3.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_georgian_byob_khachapuri-1.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-1.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_thai_byob_assorteddishes.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_chinese_byob_hotpot.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_georgian_byob_khachapuri-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_fishplate.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-chef-preparing-sushi-logo.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-carbonara-byob-restaurant-philadelphia.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-japanese-ramen-byob-restaurant-philadelphia.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_mediterranean_byob_meze.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_french_byob_finedining-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_italian_byob-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/italian-restaurant-logo-placeholder-3.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-italian-byob-restaurant-philadelphia.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-1.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/10/placeholder_logo_japanese_byob_sushibar-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_seafood_byob-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/omakase-official-logo-coming-soon.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_mexican_byob-2.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/placeholder_logo_japanese_byob_sushibar-1.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/12/placeholder-indian-curry-naan-byob-restaurant-philadelphia.webp</t>
-  </si>
-  <si>
-    <t>https://example.com/placeholder/vegan-1.webp</t>
-  </si>
-  <si>
-    <t>https://byobmap.com/wp-content/uploads/2025/11/byob-steak-medium-rare.webp</t>
+    <t>Susie's Mexican Grill</t>
+  </si>
+  <si>
+    <t>165 Dart Dr Unit B Hanover, PA 17331</t>
+  </si>
+  <si>
+    <t>(717) 634-9767</t>
+  </si>
+  <si>
+    <t>https://susiesmexicangrill.toast.site/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/susies-mexican-grill-hanover-2</t>
+  </si>
+  <si>
+    <t>2026/4/23</t>
+  </si>
+  <si>
+    <t>susiesmexicangrill165@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1917,7 +1946,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1925,34 +1954,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2255,111 +2263,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:AB96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="18" max="18" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1374</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>594</v>
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P2">
         <v>39.933934299999997</v>
@@ -2367,46 +2396,46 @@
       <c r="Q2">
         <v>-75.165249199999991</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45969</v>
       </c>
       <c r="S2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1376</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>595</v>
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P3">
         <v>40.033780200000002</v>
@@ -2414,40 +2443,40 @@
       <c r="Q3">
         <v>-75.21579659999999</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1377</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>596</v>
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P4">
         <v>39.941107500000001</v>
@@ -2455,46 +2484,46 @@
       <c r="Q4">
         <v>-75.146249400000002</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45969</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1383</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>597</v>
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P5">
         <v>39.988109899999998</v>
@@ -2502,55 +2531,55 @@
       <c r="Q5">
         <v>-75.1282341</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45987</v>
       </c>
       <c r="S5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1387</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>598</v>
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="N6" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="O6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="P6">
         <v>39.953542300000002</v>
@@ -2558,46 +2587,46 @@
       <c r="Q6">
         <v>-75.157455200000001</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45987</v>
       </c>
       <c r="S6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1388</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>599</v>
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P7">
         <v>39.949672</v>
@@ -2605,43 +2634,43 @@
       <c r="Q7">
         <v>-75.152562000000017</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45987</v>
       </c>
       <c r="S7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1389</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>600</v>
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P8">
         <v>39.969888599999997</v>
@@ -2649,43 +2678,43 @@
       <c r="Q8">
         <v>-75.144038499999994</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45987</v>
       </c>
       <c r="S8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1398</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>597</v>
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="O9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P9">
         <v>40.025693400000002</v>
@@ -2693,43 +2722,43 @@
       <c r="Q9">
         <v>-75.2233971</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1399</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>601</v>
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="O10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P10">
         <v>40.025600900000001</v>
@@ -2737,43 +2766,43 @@
       <c r="Q10">
         <v>-75.2234981</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1401</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>602</v>
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M11" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="O11" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P11">
         <v>40.009791999999997</v>
@@ -2781,40 +2810,40 @@
       <c r="Q11">
         <v>-75.190426099999996</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1402</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>596</v>
+        <v>115</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I12" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2825,43 +2854,43 @@
       <c r="Q12">
         <v>-75.159225399999997</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45985</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1404</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>603</v>
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M13" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="O13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P13">
         <v>40.025373700000003</v>
@@ -2869,43 +2898,43 @@
       <c r="Q13">
         <v>-75.223862799999992</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1407</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>604</v>
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F14" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="G14" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M14" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P14">
         <v>39.9346672</v>
@@ -2913,40 +2942,40 @@
       <c r="Q14">
         <v>-75.160286099999993</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>45987</v>
       </c>
       <c r="S14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1408</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>604</v>
+        <v>138</v>
+      </c>
+      <c r="C15" t="s">
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="P15">
         <v>39.941414799999997</v>
@@ -2954,43 +2983,43 @@
       <c r="Q15">
         <v>-75.149054199999995</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" s="1">
         <v>45987</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1409</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>602</v>
+        <v>142</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="H16" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P16">
         <v>39.910713899999998</v>
@@ -2998,7 +3027,7 @@
       <c r="Q16">
         <v>-75.084474200000002</v>
       </c>
-      <c r="R16" s="2">
+      <c r="R16" s="1">
         <v>45987</v>
       </c>
     </row>
@@ -3007,34 +3036,34 @@
         <v>1410</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>605</v>
+        <v>148</v>
+      </c>
+      <c r="C17" t="s">
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="G17" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M17" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="O17" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="P17">
         <v>39.916215800000003</v>
@@ -3042,11 +3071,11 @@
       <c r="Q17">
         <v>-75.069438599999998</v>
       </c>
-      <c r="R17" s="2">
+      <c r="R17" s="1">
         <v>45987</v>
       </c>
       <c r="S17" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -3054,31 +3083,31 @@
         <v>1412</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>606</v>
+        <v>156</v>
+      </c>
+      <c r="C18" t="s">
+        <v>157</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M18" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="O18" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="P18">
         <v>39.940898199999999</v>
@@ -3086,7 +3115,7 @@
       <c r="Q18">
         <v>-75.147503599999993</v>
       </c>
-      <c r="R18" s="2">
+      <c r="R18" s="1">
         <v>45987</v>
       </c>
     </row>
@@ -3095,37 +3124,37 @@
         <v>1417</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>603</v>
+        <v>163</v>
+      </c>
+      <c r="C19" t="s">
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="J19" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L19" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="M19" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="O19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P19">
         <v>39.954462199999988</v>
@@ -3133,7 +3162,7 @@
       <c r="Q19">
         <v>-75.156541500000003</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="1">
         <v>45987</v>
       </c>
     </row>
@@ -3142,28 +3171,28 @@
         <v>1555</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>607</v>
+        <v>169</v>
+      </c>
+      <c r="C20" t="s">
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="F20" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="G20" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P20">
         <v>39.967158499999996</v>
@@ -3171,11 +3200,11 @@
       <c r="Q20">
         <v>-75.1753073</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" s="1">
         <v>45969</v>
       </c>
       <c r="S20" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -3183,31 +3212,31 @@
         <v>1556</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>594</v>
+        <v>176</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="F21" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="H21" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I21" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J21" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P21">
         <v>39.938799099999997</v>
@@ -3215,7 +3244,7 @@
       <c r="Q21">
         <v>-75.152359599999997</v>
       </c>
-      <c r="R21" s="2">
+      <c r="R21" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3224,31 +3253,31 @@
         <v>1557</v>
       </c>
       <c r="B22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>594</v>
+        <v>182</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="F22" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G22" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I22" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="J22" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P22">
         <v>39.950006500000001</v>
@@ -3256,7 +3285,7 @@
       <c r="Q22">
         <v>-75.179640800000001</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3265,25 +3294,25 @@
         <v>1558</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>596</v>
+        <v>188</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H23" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P23">
         <v>39.945162000000003</v>
@@ -3291,11 +3320,11 @@
       <c r="Q23">
         <v>-75.170259099999996</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="1">
         <v>45969</v>
       </c>
       <c r="S23" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -3303,31 +3332,31 @@
         <v>1559</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>608</v>
+        <v>194</v>
+      </c>
+      <c r="C24" t="s">
+        <v>195</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="E24" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="F24" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="G24" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="I24" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="J24" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P24">
         <v>39.937890799999998</v>
@@ -3335,11 +3364,11 @@
       <c r="Q24">
         <v>-75.144517199999996</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="1">
         <v>45969</v>
       </c>
       <c r="S24" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
@@ -3347,31 +3376,31 @@
         <v>1560</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>599</v>
+        <v>203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I25" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="J25" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P25">
         <v>39.972437200000002</v>
@@ -3379,14 +3408,14 @@
       <c r="Q25">
         <v>-75.141018599999995</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" s="1">
         <v>45969</v>
       </c>
       <c r="S25" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="T25" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
@@ -3394,28 +3423,28 @@
         <v>1561</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>609</v>
+        <v>211</v>
+      </c>
+      <c r="C26" t="s">
+        <v>212</v>
       </c>
       <c r="D26" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="E26" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="H26" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="I26" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="J26" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P26">
         <v>39.930126299999998</v>
@@ -3423,11 +3452,11 @@
       <c r="Q26">
         <v>-75.161606300000003</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" s="1">
         <v>45969</v>
       </c>
       <c r="S26" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -3435,25 +3464,25 @@
         <v>1562</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>594</v>
+        <v>219</v>
+      </c>
+      <c r="C27" t="s">
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F27" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="G27" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J27" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P27">
         <v>39.970733099999997</v>
@@ -3461,11 +3490,11 @@
       <c r="Q27">
         <v>-75.129705099999995</v>
       </c>
-      <c r="R27" s="2">
+      <c r="R27" s="1">
         <v>45969</v>
       </c>
       <c r="S27" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
@@ -3473,31 +3502,31 @@
         <v>1563</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>594</v>
+        <v>224</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="E28" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="F28" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="G28" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I28" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P28">
         <v>39.945286199999998</v>
@@ -3505,7 +3534,7 @@
       <c r="Q28">
         <v>-75.164066699999992</v>
       </c>
-      <c r="R28" s="2">
+      <c r="R28" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3514,31 +3543,31 @@
         <v>1564</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>607</v>
+        <v>229</v>
+      </c>
+      <c r="C29" t="s">
+        <v>170</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="E29" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="F29" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="G29" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="H29" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I29" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P29">
         <v>39.945343899999997</v>
@@ -3546,7 +3575,7 @@
       <c r="Q29">
         <v>-75.164232699999999</v>
       </c>
-      <c r="R29" s="2">
+      <c r="R29" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3555,31 +3584,31 @@
         <v>1565</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>599</v>
+        <v>233</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="E30" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="F30" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="G30" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I30" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="J30" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P30">
         <v>39.971564299999997</v>
@@ -3587,7 +3616,7 @@
       <c r="Q30">
         <v>-75.144519399999993</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3596,31 +3625,31 @@
         <v>1566</v>
       </c>
       <c r="B31" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>610</v>
+        <v>239</v>
+      </c>
+      <c r="C31" t="s">
+        <v>240</v>
       </c>
       <c r="D31" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="E31" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="G31" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="H31" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P31">
         <v>39.967347200000013</v>
@@ -3628,11 +3657,11 @@
       <c r="Q31">
         <v>-75.140985200000003</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="1">
         <v>45969</v>
       </c>
       <c r="S31" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -3640,28 +3669,28 @@
         <v>1567</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>602</v>
+        <v>246</v>
+      </c>
+      <c r="C32" t="s">
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="G32" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="H32" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M32" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="P32">
         <v>39.944823399999997</v>
@@ -3669,11 +3698,11 @@
       <c r="Q32">
         <v>-75.180016899999998</v>
       </c>
-      <c r="R32" s="2">
+      <c r="R32" s="1">
         <v>45969</v>
       </c>
       <c r="S32" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
@@ -3681,31 +3710,31 @@
         <v>1568</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>600</v>
+        <v>252</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
       </c>
       <c r="D33" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="E33" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="F33" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="G33" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="H33" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P33">
         <v>39.944419500000002</v>
@@ -3713,7 +3742,7 @@
       <c r="Q33">
         <v>-75.170737899999992</v>
       </c>
-      <c r="R33" s="2">
+      <c r="R33" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3722,28 +3751,28 @@
         <v>1569</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>611</v>
+        <v>258</v>
+      </c>
+      <c r="C34" t="s">
+        <v>259</v>
       </c>
       <c r="D34" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E34" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="G34" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="H34" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="I34" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P34">
         <v>39.949910799999998</v>
@@ -3751,7 +3780,7 @@
       <c r="Q34">
         <v>-75.160454999999999</v>
       </c>
-      <c r="R34" s="2">
+      <c r="R34" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3760,31 +3789,31 @@
         <v>1570</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>601</v>
+        <v>263</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="E35" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="F35" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="G35" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J35" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P35">
         <v>39.947785699999997</v>
@@ -3792,7 +3821,7 @@
       <c r="Q35">
         <v>-75.160108000000008</v>
       </c>
-      <c r="R35" s="2">
+      <c r="R35" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3801,28 +3830,28 @@
         <v>1571</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>595</v>
+        <v>268</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="F36" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="H36" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J36" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P36">
         <v>39.9681268</v>
@@ -3830,7 +3859,7 @@
       <c r="Q36">
         <v>-75.134557399999991</v>
       </c>
-      <c r="R36" s="2">
+      <c r="R36" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3839,28 +3868,28 @@
         <v>1573</v>
       </c>
       <c r="B37" t="s">
-        <v>246</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>607</v>
+        <v>272</v>
+      </c>
+      <c r="C37" t="s">
+        <v>170</v>
       </c>
       <c r="D37" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="E37" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="F37" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="G37" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="H37" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P37">
         <v>39.947794299999998</v>
@@ -3868,7 +3897,7 @@
       <c r="Q37">
         <v>-75.167785299999991</v>
       </c>
-      <c r="R37" s="2">
+      <c r="R37" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3877,25 +3906,25 @@
         <v>1574</v>
       </c>
       <c r="B38" t="s">
-        <v>251</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>608</v>
+        <v>277</v>
+      </c>
+      <c r="C38" t="s">
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="E38" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="G38" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J38" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P38">
         <v>39.919627800000001</v>
@@ -3903,7 +3932,7 @@
       <c r="Q38">
         <v>-75.171386099999992</v>
       </c>
-      <c r="R38" s="2">
+      <c r="R38" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3912,28 +3941,28 @@
         <v>1575</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>606</v>
+        <v>281</v>
+      </c>
+      <c r="C39" t="s">
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="E39" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="F39" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="G39" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J39" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P39">
         <v>39.939477599999996</v>
@@ -3941,7 +3970,7 @@
       <c r="Q39">
         <v>-75.171194099999994</v>
       </c>
-      <c r="R39" s="2">
+      <c r="R39" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -3950,25 +3979,25 @@
         <v>1576</v>
       </c>
       <c r="B40" t="s">
-        <v>260</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>611</v>
+        <v>286</v>
+      </c>
+      <c r="C40" t="s">
+        <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="F40" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J40" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P40">
         <v>39.939990700000003</v>
@@ -3976,11 +4005,11 @@
       <c r="Q40">
         <v>-75.152963700000001</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R40" s="1">
         <v>45969</v>
       </c>
       <c r="S40" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
@@ -3988,28 +4017,28 @@
         <v>1577</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>607</v>
+        <v>292</v>
+      </c>
+      <c r="C41" t="s">
+        <v>170</v>
       </c>
       <c r="D41" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="E41" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="F41" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="G41" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="H41" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J41" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P41">
         <v>39.949691500000007</v>
@@ -4017,14 +4046,14 @@
       <c r="Q41">
         <v>-75.173786499999991</v>
       </c>
-      <c r="R41" s="2">
+      <c r="R41" s="1">
         <v>45969</v>
       </c>
       <c r="S41" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="T41" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
@@ -4032,28 +4061,28 @@
         <v>1578</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>599</v>
+        <v>299</v>
+      </c>
+      <c r="C42" t="s">
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="F42" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="G42" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I42" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="J42" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P42">
         <v>39.9399765</v>
@@ -4061,7 +4090,7 @@
       <c r="Q42">
         <v>-75.157853799999998</v>
       </c>
-      <c r="R42" s="2">
+      <c r="R42" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4070,28 +4099,28 @@
         <v>1579</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>606</v>
+        <v>304</v>
+      </c>
+      <c r="C43" t="s">
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="E43" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="G43" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="H43" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J43" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P43">
         <v>39.951250900000012</v>
@@ -4099,11 +4128,11 @@
       <c r="Q43">
         <v>-75.174123500000007</v>
       </c>
-      <c r="R43" s="2">
+      <c r="R43" s="1">
         <v>45969</v>
       </c>
       <c r="S43" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
@@ -4111,28 +4140,28 @@
         <v>1580</v>
       </c>
       <c r="B44" t="s">
-        <v>284</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>608</v>
+        <v>310</v>
+      </c>
+      <c r="C44" t="s">
+        <v>195</v>
       </c>
       <c r="D44" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="E44" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="F44" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="G44" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J44" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P44">
         <v>39.946499199999998</v>
@@ -4140,14 +4169,14 @@
       <c r="Q44">
         <v>-75.161768199999997</v>
       </c>
-      <c r="R44" s="2">
+      <c r="R44" s="1">
         <v>45969</v>
       </c>
       <c r="S44" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="T44" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
@@ -4155,31 +4184,31 @@
         <v>1581</v>
       </c>
       <c r="B45" t="s">
-        <v>291</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>599</v>
+        <v>317</v>
+      </c>
+      <c r="C45" t="s">
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="E45" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="F45" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="G45" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I45" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="J45" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P45">
         <v>39.953597799999997</v>
@@ -4187,7 +4216,7 @@
       <c r="Q45">
         <v>-75.160984799999994</v>
       </c>
-      <c r="R45" s="2">
+      <c r="R45" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4196,31 +4225,31 @@
         <v>1582</v>
       </c>
       <c r="B46" t="s">
-        <v>297</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>610</v>
+        <v>323</v>
+      </c>
+      <c r="C46" t="s">
+        <v>240</v>
       </c>
       <c r="D46" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="E46" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="F46" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="G46" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="H46" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I46" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P46">
         <v>39.944041200000001</v>
@@ -4228,7 +4257,7 @@
       <c r="Q46">
         <v>-75.170019699999997</v>
       </c>
-      <c r="R46" s="2">
+      <c r="R46" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4237,31 +4266,31 @@
         <v>1583</v>
       </c>
       <c r="B47" t="s">
-        <v>302</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>600</v>
+        <v>328</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
       </c>
       <c r="D47" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="G47" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="J47" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P47">
         <v>39.951949399999997</v>
@@ -4269,11 +4298,11 @@
       <c r="Q47">
         <v>-75.144386900000001</v>
       </c>
-      <c r="R47" s="2">
+      <c r="R47" s="1">
         <v>45969</v>
       </c>
       <c r="S47" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
@@ -4281,31 +4310,31 @@
         <v>1584</v>
       </c>
       <c r="B48" t="s">
-        <v>309</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>608</v>
+        <v>335</v>
+      </c>
+      <c r="C48" t="s">
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="F48" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="G48" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="H48" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I48" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="J48" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P48">
         <v>39.936869300000012</v>
@@ -4313,11 +4342,11 @@
       <c r="Q48">
         <v>-75.156515900000002</v>
       </c>
-      <c r="R48" s="2">
+      <c r="R48" s="1">
         <v>45969</v>
       </c>
       <c r="S48" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
@@ -4325,31 +4354,31 @@
         <v>1585</v>
       </c>
       <c r="B49" t="s">
-        <v>316</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>604</v>
+        <v>342</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="E49" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="F49" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="G49" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="H49" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="J49" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P49">
         <v>39.965340099999999</v>
@@ -4357,11 +4386,11 @@
       <c r="Q49">
         <v>-75.140709299999997</v>
       </c>
-      <c r="R49" s="2">
+      <c r="R49" s="1">
         <v>45969</v>
       </c>
       <c r="S49" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
@@ -4369,25 +4398,25 @@
         <v>1586</v>
       </c>
       <c r="B50" t="s">
-        <v>324</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>606</v>
+        <v>350</v>
+      </c>
+      <c r="C50" t="s">
+        <v>157</v>
       </c>
       <c r="D50" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="E50" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="G50" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="H50" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J50" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P50">
         <v>39.951353500000003</v>
@@ -4395,7 +4424,7 @@
       <c r="Q50">
         <v>-75.175115599999998</v>
       </c>
-      <c r="R50" s="2">
+      <c r="R50" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4404,31 +4433,31 @@
         <v>1587</v>
       </c>
       <c r="B51" t="s">
-        <v>328</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>603</v>
+        <v>354</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="E51" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="F51" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="G51" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I51" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="J51" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P51">
         <v>39.926275500000003</v>
@@ -4436,7 +4465,7 @@
       <c r="Q51">
         <v>-75.167463699999999</v>
       </c>
-      <c r="R51" s="2">
+      <c r="R51" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4445,28 +4474,28 @@
         <v>1588</v>
       </c>
       <c r="B52" t="s">
-        <v>334</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>594</v>
+        <v>360</v>
+      </c>
+      <c r="C52" t="s">
+        <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="E52" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="F52" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="G52" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="H52" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="J52" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P52">
         <v>39.919344799999998</v>
@@ -4474,7 +4503,7 @@
       <c r="Q52">
         <v>-75.171119699999991</v>
       </c>
-      <c r="R52" s="2">
+      <c r="R52" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4483,31 +4512,31 @@
         <v>1589</v>
       </c>
       <c r="B53" t="s">
-        <v>339</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>600</v>
+        <v>365</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
       </c>
       <c r="D53" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E53" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="F53" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G53" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="H53" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I53" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="J53" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P53">
         <v>39.925220400000001</v>
@@ -4515,11 +4544,11 @@
       <c r="Q53">
         <v>-75.174716699999991</v>
       </c>
-      <c r="R53" s="2">
+      <c r="R53" s="1">
         <v>45969</v>
       </c>
       <c r="S53" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
@@ -4527,31 +4556,31 @@
         <v>1590</v>
       </c>
       <c r="B54" t="s">
-        <v>346</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>609</v>
+        <v>372</v>
+      </c>
+      <c r="C54" t="s">
+        <v>212</v>
       </c>
       <c r="D54" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="E54" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="F54" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="G54" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="H54" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="I54" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="J54" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P54">
         <v>39.9339212</v>
@@ -4559,7 +4588,7 @@
       <c r="Q54">
         <v>-75.155556500000003</v>
       </c>
-      <c r="R54" s="2">
+      <c r="R54" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4568,28 +4597,28 @@
         <v>1591</v>
       </c>
       <c r="B55" t="s">
-        <v>352</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>597</v>
+        <v>378</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
       </c>
       <c r="D55" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="E55" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="F55" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="G55" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="H55" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J55" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P55">
         <v>39.942576899999999</v>
@@ -4597,11 +4626,11 @@
       <c r="Q55">
         <v>-75.185306799999992</v>
       </c>
-      <c r="R55" s="2">
+      <c r="R55" s="1">
         <v>45969</v>
       </c>
       <c r="S55" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
@@ -4609,28 +4638,28 @@
         <v>1592</v>
       </c>
       <c r="B56" t="s">
-        <v>358</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>594</v>
+        <v>384</v>
+      </c>
+      <c r="C56" t="s">
+        <v>29</v>
       </c>
       <c r="D56" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="E56" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="F56" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="G56" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="H56" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J56" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P56">
         <v>39.948765399999999</v>
@@ -4638,11 +4667,11 @@
       <c r="Q56">
         <v>-75.177968399999997</v>
       </c>
-      <c r="R56" s="2">
+      <c r="R56" s="1">
         <v>45969</v>
       </c>
       <c r="S56" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
@@ -4650,31 +4679,31 @@
         <v>1593</v>
       </c>
       <c r="B57" t="s">
-        <v>364</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>612</v>
+        <v>390</v>
+      </c>
+      <c r="C57" t="s">
+        <v>391</v>
       </c>
       <c r="D57" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="E57" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="F57" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="G57" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="H57" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I57" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J57" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P57">
         <v>39.9515782</v>
@@ -4682,7 +4711,7 @@
       <c r="Q57">
         <v>-75.174830900000003</v>
       </c>
-      <c r="R57" s="2">
+      <c r="R57" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4691,31 +4720,31 @@
         <v>1594</v>
       </c>
       <c r="B58" t="s">
-        <v>369</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>597</v>
+        <v>396</v>
+      </c>
+      <c r="C58" t="s">
+        <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="E58" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="F58" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="G58" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="H58" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I58" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J58" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P58">
         <v>39.948388199999997</v>
@@ -4723,7 +4752,7 @@
       <c r="Q58">
         <v>-75.217944799999998</v>
       </c>
-      <c r="R58" s="2">
+      <c r="R58" s="1">
         <v>45969</v>
       </c>
     </row>
@@ -4732,28 +4761,28 @@
         <v>1726</v>
       </c>
       <c r="B59" t="s">
-        <v>374</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>606</v>
+        <v>401</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
       </c>
       <c r="D59" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="E59" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="F59" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="G59" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J59" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P59">
         <v>39.931907000000002</v>
@@ -4761,7 +4790,7 @@
       <c r="Q59">
         <v>-75.149544399999996</v>
       </c>
-      <c r="R59" s="2">
+      <c r="R59" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -4770,28 +4799,28 @@
         <v>1727</v>
       </c>
       <c r="B60" t="s">
-        <v>379</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>599</v>
+        <v>406</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
       </c>
       <c r="D60" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="E60" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="G60" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="H60" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I60" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J60" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P60">
         <v>39.910426600000001</v>
@@ -4799,7 +4828,7 @@
       <c r="Q60">
         <v>-75.050069499999992</v>
       </c>
-      <c r="R60" s="2">
+      <c r="R60" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -4808,25 +4837,25 @@
         <v>1729</v>
       </c>
       <c r="B61" t="s">
-        <v>383</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>600</v>
+        <v>410</v>
+      </c>
+      <c r="C61" t="s">
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="E61" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="G61" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="H61" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="J61" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P61">
         <v>39.941114900000002</v>
@@ -4834,7 +4863,7 @@
       <c r="Q61">
         <v>-75.149088399999997</v>
       </c>
-      <c r="R61" s="2">
+      <c r="R61" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -4843,25 +4872,25 @@
         <v>1730</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>596</v>
+        <v>414</v>
+      </c>
+      <c r="C62" t="s">
+        <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="E62" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="G62" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="H62" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="J62" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P62">
         <v>39.939704499999998</v>
@@ -4869,7 +4898,7 @@
       <c r="Q62">
         <v>-75.156259599999998</v>
       </c>
-      <c r="R62" s="2">
+      <c r="R62" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -4878,31 +4907,31 @@
         <v>1731</v>
       </c>
       <c r="B63" t="s">
-        <v>392</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>600</v>
+        <v>419</v>
+      </c>
+      <c r="C63" t="s">
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="E63" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="F63" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="G63" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="H63" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I63" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="J63" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P63">
         <v>39.968518099999997</v>
@@ -4910,7 +4939,7 @@
       <c r="Q63">
         <v>-75.178519699999995</v>
       </c>
-      <c r="R63" s="2">
+      <c r="R63" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -4919,28 +4948,28 @@
         <v>1732</v>
       </c>
       <c r="B64" t="s">
-        <v>398</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>608</v>
+        <v>425</v>
+      </c>
+      <c r="C64" t="s">
+        <v>195</v>
       </c>
       <c r="D64" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="E64" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="F64" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="G64" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J64" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P64">
         <v>39.9413883</v>
@@ -4948,14 +4977,14 @@
       <c r="Q64">
         <v>-75.150354600000014</v>
       </c>
-      <c r="R64" s="2">
+      <c r="R64" s="1">
         <v>45977</v>
       </c>
       <c r="S64" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="T64" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.3">
@@ -4963,31 +4992,31 @@
         <v>1733</v>
       </c>
       <c r="B65" t="s">
-        <v>405</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>595</v>
+        <v>432</v>
+      </c>
+      <c r="C65" t="s">
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="E65" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="F65" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G65" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="H65" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I65" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="J65" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P65">
         <v>40.1219337</v>
@@ -4995,7 +5024,7 @@
       <c r="Q65">
         <v>-75.034327399999995</v>
       </c>
-      <c r="R65" s="2">
+      <c r="R65" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5004,28 +5033,28 @@
         <v>1734</v>
       </c>
       <c r="B66" t="s">
-        <v>411</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>598</v>
+        <v>438</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
       </c>
       <c r="D66" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="E66" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="G66" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I66" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="J66" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P66">
         <v>39.928446399999999</v>
@@ -5033,7 +5062,7 @@
       <c r="Q66">
         <v>-75.171258600000002</v>
       </c>
-      <c r="R66" s="2">
+      <c r="R66" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5042,25 +5071,25 @@
         <v>1735</v>
       </c>
       <c r="B67" t="s">
-        <v>416</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>607</v>
+        <v>443</v>
+      </c>
+      <c r="C67" t="s">
+        <v>170</v>
       </c>
       <c r="D67" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="G67" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="H67" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I67" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J67" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P67">
         <v>39.919901199999998</v>
@@ -5068,7 +5097,7 @@
       <c r="Q67">
         <v>-75.173383200000004</v>
       </c>
-      <c r="R67" s="2">
+      <c r="R67" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5077,31 +5106,31 @@
         <v>1736</v>
       </c>
       <c r="B68" t="s">
-        <v>419</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>600</v>
+        <v>446</v>
+      </c>
+      <c r="C68" t="s">
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="E68" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="F68" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="G68" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="H68" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I68" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="J68" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P68">
         <v>39.9463188</v>
@@ -5109,14 +5138,14 @@
       <c r="Q68">
         <v>-75.157960899999992</v>
       </c>
-      <c r="R68" s="2">
+      <c r="R68" s="1">
         <v>45977</v>
       </c>
       <c r="S68" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="T68" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
@@ -5124,28 +5153,28 @@
         <v>1737</v>
       </c>
       <c r="B69" t="s">
-        <v>427</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>613</v>
+        <v>454</v>
+      </c>
+      <c r="C69" t="s">
+        <v>455</v>
       </c>
       <c r="D69" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="E69" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="F69" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="G69" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="H69" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="J69" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P69">
         <v>39.918631400000002</v>
@@ -5153,7 +5182,7 @@
       <c r="Q69">
         <v>-75.153989299999992</v>
       </c>
-      <c r="R69" s="2">
+      <c r="R69" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5162,28 +5191,28 @@
         <v>1738</v>
       </c>
       <c r="B70" t="s">
-        <v>433</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>607</v>
+        <v>461</v>
+      </c>
+      <c r="C70" t="s">
+        <v>170</v>
       </c>
       <c r="D70" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="E70" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="F70" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="G70" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J70" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P70">
         <v>39.947769000000001</v>
@@ -5191,11 +5220,11 @@
       <c r="Q70">
         <v>-75.16970049999999</v>
       </c>
-      <c r="R70" s="2">
+      <c r="R70" s="1">
         <v>45977</v>
       </c>
       <c r="S70" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.3">
@@ -5203,28 +5232,28 @@
         <v>1739</v>
       </c>
       <c r="B71" t="s">
-        <v>439</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>606</v>
+        <v>467</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
       </c>
       <c r="D71" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="E71" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="G71" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="H71" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I71" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="J71" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P71">
         <v>39.943967499999999</v>
@@ -5232,7 +5261,7 @@
       <c r="Q71">
         <v>-75.169153299999991</v>
       </c>
-      <c r="R71" s="2">
+      <c r="R71" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5241,28 +5270,28 @@
         <v>1740</v>
       </c>
       <c r="B72" t="s">
-        <v>444</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>606</v>
+        <v>472</v>
+      </c>
+      <c r="C72" t="s">
+        <v>157</v>
       </c>
       <c r="D72" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="E72" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="F72" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="G72" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J72" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P72">
         <v>40.059318500000003</v>
@@ -5270,17 +5299,17 @@
       <c r="Q72">
         <v>-75.190036300000003</v>
       </c>
-      <c r="R72" s="2">
+      <c r="R72" s="1">
         <v>45977</v>
       </c>
       <c r="S72" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="T72" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="U72" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.3">
@@ -5288,28 +5317,28 @@
         <v>1741</v>
       </c>
       <c r="B73" t="s">
-        <v>452</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>613</v>
+        <v>480</v>
+      </c>
+      <c r="C73" t="s">
+        <v>455</v>
       </c>
       <c r="D73" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="E73" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="F73" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="G73" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="H73" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="J73" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P73">
         <v>39.921155900000002</v>
@@ -5317,11 +5346,11 @@
       <c r="Q73">
         <v>-75.163266499999992</v>
       </c>
-      <c r="R73" s="2">
+      <c r="R73" s="1">
         <v>45977</v>
       </c>
       <c r="S73" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.3">
@@ -5329,28 +5358,28 @@
         <v>1742</v>
       </c>
       <c r="B74" t="s">
-        <v>458</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>613</v>
+        <v>486</v>
+      </c>
+      <c r="C74" t="s">
+        <v>455</v>
       </c>
       <c r="D74" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="E74" t="s">
+        <v>488</v>
+      </c>
+      <c r="F74" t="s">
+        <v>489</v>
+      </c>
+      <c r="G74" t="s">
+        <v>490</v>
+      </c>
+      <c r="H74" t="s">
         <v>460</v>
       </c>
-      <c r="F74" t="s">
-        <v>461</v>
-      </c>
-      <c r="G74" t="s">
-        <v>462</v>
-      </c>
-      <c r="H74" t="s">
-        <v>432</v>
-      </c>
       <c r="J74" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P74">
         <v>39.926405699999997</v>
@@ -5358,7 +5387,7 @@
       <c r="Q74">
         <v>-75.157535600000003</v>
       </c>
-      <c r="R74" s="2">
+      <c r="R74" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5367,31 +5396,31 @@
         <v>1743</v>
       </c>
       <c r="B75" t="s">
-        <v>463</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>608</v>
+        <v>491</v>
+      </c>
+      <c r="C75" t="s">
+        <v>195</v>
       </c>
       <c r="D75" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="E75" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="F75" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="G75" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="H75" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="I75" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J75" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P75">
         <v>39.952112100000001</v>
@@ -5399,11 +5428,11 @@
       <c r="Q75">
         <v>-75.172149099999999</v>
       </c>
-      <c r="R75" s="2">
+      <c r="R75" s="1">
         <v>45977</v>
       </c>
       <c r="S75" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.3">
@@ -5411,31 +5440,31 @@
         <v>1744</v>
       </c>
       <c r="B76" t="s">
-        <v>469</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>595</v>
+        <v>497</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
       </c>
       <c r="D76" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="E76" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="F76" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="G76" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J76" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P76">
         <v>39.982485199999999</v>
@@ -5443,11 +5472,11 @@
       <c r="Q76">
         <v>-75.102839599999996</v>
       </c>
-      <c r="R76" s="2">
+      <c r="R76" s="1">
         <v>45977</v>
       </c>
       <c r="S76" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.3">
@@ -5455,31 +5484,31 @@
         <v>1745</v>
       </c>
       <c r="B77" t="s">
-        <v>475</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>610</v>
+        <v>503</v>
+      </c>
+      <c r="C77" t="s">
+        <v>240</v>
       </c>
       <c r="D77" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="E77" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="F77" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="G77" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="H77" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I77" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J77" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P77">
         <v>39.940707699999997</v>
@@ -5487,7 +5516,7 @@
       <c r="Q77">
         <v>-75.146044199999992</v>
       </c>
-      <c r="R77" s="2">
+      <c r="R77" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5496,31 +5525,31 @@
         <v>1746</v>
       </c>
       <c r="B78" t="s">
-        <v>480</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>603</v>
+        <v>508</v>
+      </c>
+      <c r="C78" t="s">
+        <v>123</v>
       </c>
       <c r="D78" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="E78" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="F78" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="G78" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I78" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="J78" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P78">
         <v>39.938333399999998</v>
@@ -5528,14 +5557,14 @@
       <c r="Q78">
         <v>-75.159783899999994</v>
       </c>
-      <c r="R78" s="2">
+      <c r="R78" s="1">
         <v>45977</v>
       </c>
       <c r="S78" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="T78" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.3">
@@ -5543,31 +5572,31 @@
         <v>1747</v>
       </c>
       <c r="B79" t="s">
-        <v>488</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>606</v>
+        <v>516</v>
+      </c>
+      <c r="C79" t="s">
+        <v>157</v>
       </c>
       <c r="D79" t="s">
-        <v>489</v>
+        <v>517</v>
       </c>
       <c r="E79" t="s">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="F79" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
       <c r="G79" t="s">
-        <v>492</v>
+        <v>520</v>
       </c>
       <c r="H79" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I79" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J79" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P79">
         <v>39.9803949</v>
@@ -5575,7 +5604,7 @@
       <c r="Q79">
         <v>-75.113133699999992</v>
       </c>
-      <c r="R79" s="2">
+      <c r="R79" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5584,31 +5613,31 @@
         <v>1748</v>
       </c>
       <c r="B80" t="s">
-        <v>493</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>599</v>
+        <v>521</v>
+      </c>
+      <c r="C80" t="s">
+        <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="E80" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="F80" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="G80" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="H80" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
       <c r="J80" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P80">
         <v>39.926336599999999</v>
@@ -5616,7 +5645,7 @@
       <c r="Q80">
         <v>-75.147412399999993</v>
       </c>
-      <c r="R80" s="2">
+      <c r="R80" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5625,31 +5654,31 @@
         <v>1749</v>
       </c>
       <c r="B81" t="s">
-        <v>499</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>614</v>
+        <v>527</v>
+      </c>
+      <c r="C81" t="s">
+        <v>528</v>
       </c>
       <c r="D81" t="s">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="E81" t="s">
-        <v>501</v>
+        <v>530</v>
       </c>
       <c r="F81" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="G81" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="H81" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I81" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J81" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P81">
         <v>39.964689399999997</v>
@@ -5657,7 +5686,7 @@
       <c r="Q81">
         <v>-75.174111199999999</v>
       </c>
-      <c r="R81" s="2">
+      <c r="R81" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5666,31 +5695,31 @@
         <v>1750</v>
       </c>
       <c r="B82" t="s">
-        <v>504</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>599</v>
+        <v>533</v>
+      </c>
+      <c r="C82" t="s">
+        <v>79</v>
       </c>
       <c r="D82" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
       <c r="E82" t="s">
-        <v>506</v>
+        <v>535</v>
       </c>
       <c r="F82" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="G82" t="s">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I82" t="s">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="J82" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P82">
         <v>39.947806000000007</v>
@@ -5698,7 +5727,7 @@
       <c r="Q82">
         <v>-75.160342099999994</v>
       </c>
-      <c r="R82" s="2">
+      <c r="R82" s="1">
         <v>45977</v>
       </c>
     </row>
@@ -5707,34 +5736,34 @@
         <v>1754</v>
       </c>
       <c r="B83" t="s">
-        <v>510</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>605</v>
+        <v>539</v>
+      </c>
+      <c r="C83" t="s">
+        <v>149</v>
       </c>
       <c r="D83" t="s">
-        <v>511</v>
+        <v>540</v>
       </c>
       <c r="E83" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="F83" t="s">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="G83" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="H83" t="s">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="I83" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
       <c r="J83" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L83" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="P83">
         <v>39.944972700000001</v>
@@ -5742,11 +5771,11 @@
       <c r="Q83">
         <v>-75.177395099999998</v>
       </c>
-      <c r="R83" s="2">
+      <c r="R83" s="1">
         <v>45978</v>
       </c>
       <c r="S83" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
@@ -5754,28 +5783,28 @@
         <v>1755</v>
       </c>
       <c r="B84" t="s">
-        <v>519</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>599</v>
+        <v>548</v>
+      </c>
+      <c r="C84" t="s">
+        <v>79</v>
       </c>
       <c r="D84" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="F84" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="G84" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="H84" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I84" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="J84" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P84">
         <v>39.974236699999999</v>
@@ -5783,11 +5812,11 @@
       <c r="Q84">
         <v>-75.182546800000011</v>
       </c>
-      <c r="R84" s="2">
+      <c r="R84" s="1">
         <v>45978</v>
       </c>
       <c r="S84" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
@@ -5795,31 +5824,31 @@
         <v>1756</v>
       </c>
       <c r="B85" t="s">
-        <v>524</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>610</v>
+        <v>553</v>
+      </c>
+      <c r="C85" t="s">
+        <v>240</v>
       </c>
       <c r="D85" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="E85" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="F85" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="G85" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="H85" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="I85" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="J85" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P85">
         <v>39.9798258</v>
@@ -5827,11 +5856,11 @@
       <c r="Q85">
         <v>-75.129835499999999</v>
       </c>
-      <c r="R85" s="2">
+      <c r="R85" s="1">
         <v>45978</v>
       </c>
       <c r="S85" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
@@ -5839,31 +5868,31 @@
         <v>1757</v>
       </c>
       <c r="B86" t="s">
-        <v>531</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>605</v>
+        <v>560</v>
+      </c>
+      <c r="C86" t="s">
+        <v>149</v>
       </c>
       <c r="D86" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="E86" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="F86" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
       <c r="G86" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="H86" t="s">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="I86" t="s">
-        <v>536</v>
+        <v>565</v>
       </c>
       <c r="J86" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P86">
         <v>39.944876200000003</v>
@@ -5871,11 +5900,11 @@
       <c r="Q86">
         <v>-75.160762800000001</v>
       </c>
-      <c r="R86" s="2">
+      <c r="R86" s="1">
         <v>45979</v>
       </c>
       <c r="S86" t="s">
-        <v>537</v>
+        <v>566</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
@@ -5883,31 +5912,31 @@
         <v>1786</v>
       </c>
       <c r="B87" t="s">
-        <v>538</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>599</v>
+        <v>567</v>
+      </c>
+      <c r="C87" t="s">
+        <v>79</v>
       </c>
       <c r="D87" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="E87" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="F87" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="G87" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="H87" t="s">
-        <v>592</v>
+        <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="J87" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P87">
         <v>40.022318299999988</v>
@@ -5915,7 +5944,7 @@
       <c r="Q87">
         <v>-75.319580799999997</v>
       </c>
-      <c r="R87" s="2">
+      <c r="R87" s="1">
         <v>45997</v>
       </c>
     </row>
@@ -5924,28 +5953,28 @@
         <v>1787</v>
       </c>
       <c r="B88" t="s">
-        <v>544</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>615</v>
+        <v>573</v>
+      </c>
+      <c r="C88" t="s">
+        <v>574</v>
       </c>
       <c r="D88" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="E88" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="F88" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="G88" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="H88" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="J88" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P88">
         <v>39.954628999999997</v>
@@ -5953,11 +5982,11 @@
       <c r="Q88">
         <v>-75.199683899999997</v>
       </c>
-      <c r="R88" s="2">
+      <c r="R88" s="1">
         <v>45997</v>
       </c>
       <c r="S88" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
@@ -5965,31 +5994,31 @@
         <v>1788</v>
       </c>
       <c r="B89" t="s">
-        <v>551</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
+      </c>
+      <c r="C89" t="s">
+        <v>79</v>
       </c>
       <c r="D89" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="E89" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="F89" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="G89" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="H89" t="s">
-        <v>592</v>
+        <v>46</v>
       </c>
       <c r="I89" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J89" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P89">
         <v>39.955408599999998</v>
@@ -5997,7 +6026,7 @@
       <c r="Q89">
         <v>-75.1544861</v>
       </c>
-      <c r="R89" s="2">
+      <c r="R89" s="1">
         <v>45997</v>
       </c>
     </row>
@@ -6006,31 +6035,31 @@
         <v>1789</v>
       </c>
       <c r="B90" t="s">
-        <v>551</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>595</v>
+        <v>581</v>
+      </c>
+      <c r="C90" t="s">
+        <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="E90" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="F90" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="G90" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="H90" t="s">
-        <v>592</v>
+        <v>46</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J90" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P90">
         <v>39.954715299999997</v>
@@ -6038,7 +6067,7 @@
       <c r="Q90">
         <v>-75.202095200000002</v>
       </c>
-      <c r="R90" s="2">
+      <c r="R90" s="1">
         <v>45997</v>
       </c>
     </row>
@@ -6047,25 +6076,25 @@
         <v>1790</v>
       </c>
       <c r="B91" t="s">
-        <v>559</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>598</v>
+        <v>589</v>
+      </c>
+      <c r="C91" t="s">
+        <v>66</v>
       </c>
       <c r="D91" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="E91" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="G91" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="H91" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="J91" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P91">
         <v>39.953813599999997</v>
@@ -6073,7 +6102,7 @@
       <c r="Q91">
         <v>-75.1558378</v>
       </c>
-      <c r="R91" s="2">
+      <c r="R91" s="1">
         <v>45997</v>
       </c>
     </row>
@@ -6082,31 +6111,31 @@
         <v>1791</v>
       </c>
       <c r="B92" t="s">
-        <v>563</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>616</v>
+        <v>593</v>
+      </c>
+      <c r="C92" t="s">
+        <v>594</v>
       </c>
       <c r="D92" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="E92" t="s">
-        <v>565</v>
+        <v>596</v>
       </c>
       <c r="F92" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="G92" t="s">
-        <v>567</v>
+        <v>598</v>
       </c>
       <c r="H92" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="I92" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="J92" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P92">
         <v>39.967475999999998</v>
@@ -6114,11 +6143,11 @@
       <c r="Q92">
         <v>-75.1694289</v>
       </c>
-      <c r="R92" s="2">
+      <c r="R92" s="1">
         <v>45997</v>
       </c>
       <c r="S92" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
@@ -6126,31 +6155,31 @@
         <v>1792</v>
       </c>
       <c r="B93" t="s">
-        <v>569</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>617</v>
+        <v>602</v>
+      </c>
+      <c r="C93" t="s">
+        <v>603</v>
       </c>
       <c r="D93" t="s">
-        <v>570</v>
+        <v>604</v>
       </c>
       <c r="E93" t="s">
-        <v>571</v>
+        <v>605</v>
       </c>
       <c r="F93" t="s">
-        <v>572</v>
+        <v>606</v>
       </c>
       <c r="G93" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="H93" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="I93" t="s">
-        <v>574</v>
+        <v>609</v>
       </c>
       <c r="J93" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P93">
         <v>39.966393500000002</v>
@@ -6158,11 +6187,11 @@
       <c r="Q93">
         <v>-75.134263699999991</v>
       </c>
-      <c r="R93" s="2">
+      <c r="R93" s="1">
         <v>45997</v>
       </c>
       <c r="S93" t="s">
-        <v>575</v>
+        <v>610</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
@@ -6170,31 +6199,31 @@
         <v>1793</v>
       </c>
       <c r="B94" t="s">
-        <v>576</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
+      </c>
+      <c r="C94" t="s">
+        <v>170</v>
       </c>
       <c r="D94" t="s">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="E94" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="F94" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="G94" t="s">
-        <v>580</v>
+        <v>615</v>
       </c>
       <c r="H94" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="I94" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="J94" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P94">
         <v>39.956620099999988</v>
@@ -6202,11 +6231,11 @@
       <c r="Q94">
         <v>-75.146333400000003</v>
       </c>
-      <c r="R94" s="2">
+      <c r="R94" s="1">
         <v>45997</v>
       </c>
       <c r="S94" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
@@ -6214,31 +6243,31 @@
         <v>1794</v>
       </c>
       <c r="B95" t="s">
-        <v>582</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>596</v>
+        <v>619</v>
+      </c>
+      <c r="C95" t="s">
+        <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="E95" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="F95" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="G95" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="H95" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="I95" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="J95" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P95">
         <v>39.927078799999997</v>
@@ -6246,12 +6275,48 @@
       <c r="Q95">
         <v>-75.16715219999999</v>
       </c>
-      <c r="R95" s="2">
+      <c r="R95" s="1">
         <v>45998</v>
       </c>
     </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>624</v>
+      </c>
+      <c r="D96" t="s">
+        <v>625</v>
+      </c>
+      <c r="E96" t="s">
+        <v>626</v>
+      </c>
+      <c r="F96" t="s">
+        <v>627</v>
+      </c>
+      <c r="G96" t="s">
+        <v>628</v>
+      </c>
+      <c r="H96" t="s">
+        <v>460</v>
+      </c>
+      <c r="J96" t="s">
+        <v>35</v>
+      </c>
+      <c r="P96">
+        <v>39.816530299999997</v>
+      </c>
+      <c r="Q96">
+        <v>-76.991277799999992</v>
+      </c>
+      <c r="R96" t="s">
+        <v>629</v>
+      </c>
+      <c r="S96" t="s">
+        <v>630</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>